--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -717,8 +717,8 @@
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B29:F29"/>
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="B29:F29"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
@@ -741,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -850,15 +850,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr"/>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Depends on the CRM shell (E2-02) landing at /crm first.</t>
+          <t>Depends on the CRM shell (E2-02) landing at /crm first. [2026-08-13 SHIPPED] /contacts route now redirects to /crm; TeamPage default export at pages/Team.js gives /team its own route. Both verified live in preview browser as amit (owner).</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -903,9 +903,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="I3" s="7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>Route: /crm (perm='people'). Copy the ContactsPanel filter logic, throw away the tab shell. Reuse ContactProfile logic for the right pane so we don't rebuild the 360°.</t>
+          <t>Route: /crm (perm='people'). Copy the ContactsPanel filter logic, throw away the tab shell. Reuse ContactProfile logic for the right pane so we don't rebuild the 360°. [2026-08-13 SHIPPED] New pages/CRM.js shipped with unified list (All / Customers / Suppliers / Mine filter chips, search bar, status dropdown), Add Customer + Add Supplier buttons in header, card grid with type / status / tag chips + view / edit / delete / log-complaint actions, click-through to /contacts/:id (existing 360°). Right-pane detail deferred to Sprint B (needs workflow-engine feed WE-06).</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -1583,6 +1583,63 @@
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="100" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>E2-15</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Ops menu entry — owner-only shortcut to /operating-score</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-13 same session: 'add the button called operation score in main menu.. we will name it Ops.' Added Ops entry to the main sidebar NAV in Layout.js (Gauge icon, ownerOnly, position 4 between My Work and CRM). Points to /operating-score. Non-owners don't see the item at all (filtered out by useMemo(NAV.filter)). Matches the pattern E2-11 established when we removed the Operating Score card from the CEO Brief header — the page still lives at /operating-score, just moved from a Brief shortcut to a first-class nav entry.</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>E2-11</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-13. Verified live: hamburger drawer shows Decision Desk &gt; CEO Brief &gt; My Work &gt; Ops &gt; CRM &gt; Team &gt; Company Brain &gt; Finance &gt; Capture &gt; Meeting Notes &gt; Settings. nav-ops testid resolves to href=/operating-score. Hindi label 'ऑप्स', Tamil label 'இயக்கம்' added to i18n.</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-13</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2198,7 +2255,6 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B43:D43"/>
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="B35:D35"/>
@@ -2217,8 +2273,9 @@
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="B12:D12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2230,7 +2287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2327,6 +2384,48 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="130" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>E2-01/02/15</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>People (retired) -&gt; /crm + /team + Ops nav</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Split the old 3-tab People page into a dedicated CRM (customers + suppliers only, at /crm) and a Team page (employees only, at /team). /contacts URL redirects to /crm. Bottom-nav PEOPLE slot renamed to CRM; sidebar drawer gains Team + Ops entries. Ops is owner-only and points at /operating-score.</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>One /contacts page with three tabs (Employees / Customers / Suppliers). Employees tab required team_manage; add-button meaning changed by tab. Operating Score reachable only from CEO Brief header shortcut (removed in E2-11).</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>/crm two-column-ready shell with filter chips (All / Customers / Suppliers / Mine), search, status filter, tag chips per card. /team is the pure Employees page with ADD MEMBER, access editor, invite links. Ops sits as its own owner-only sidebar item.</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Verified live in preview browser as amit@kapoormills.co.in: CRM shows Delhi Retail Corp under Customers, Rajesh Cotton Traders under Suppliers, and clicking Ops takes you to /operating-score. Bottom-nav is DESK / BRIEF / WORK / CRM / BRAIN.</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -712,24 +712,161 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Backlog columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>E2-&lt;n&gt; ticket ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Screen / Feature</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Which page or feature this touches — sort/filter by this to see all work on /crm at once</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>A / B / C</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Info architecture · New page · Data model · Navigation · AI feature · Polish · Milestone</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Short imperative summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>The what and why</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Priority / Effort / Status</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>P1..P3 / XS..L / Backlog|In Progress|Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Depends on</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Prereq ticket IDs (e.g. WE-06 from the Workflow Engine sprint in Epic 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Notes / evidence</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Live-test evidence, screenshot references, shipping notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Where the ask came from (founder ask, CRM Ideation, Sprint plan, etc.)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A24:F24"/>
+  <mergeCells count="26">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="B27:F27"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="B39:F39"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -741,11 +878,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="78" customWidth="1" min="5" max="5"/>
@@ -765,50 +902,55 @@
       </c>
       <c r="B1" s="6" t="inlineStr">
         <is>
+          <t>Screen / Feature</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Depends on</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Notes / evidence</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -820,48 +962,53 @@
           <t>E2-01</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>/crm + /team + /contacts (retired)</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Info architecture</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>Split People page — employees off, CRM concept opens</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Today /contacts is one page with 3 tabs (Employees, Customers, Suppliers). Founder ask 2026-08-13: 'separate the people section first because I want to create CRM for the supplier and customer.' Employees is HR/admin, Customers + Suppliers are RELATIONSHIPS — different mental model, different frequency of use, different workflow-engine integration. Move Employees to /team (owner + team_manage only). Redirect /contacts to /crm.</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr"/>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr"/>
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>Depends on the CRM shell (E2-02) landing at /crm first. [2026-08-13 SHIPPED] /contacts route now redirects to /crm; TeamPage default export at pages/Team.js gives /team its own route. Both verified live in preview browser as amit (owner).</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-13</t>
         </is>
@@ -873,52 +1020,57 @@
           <t>E2-02</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>/crm — shell (list + filter chips)</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>New page</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>CRM shell at /crm — list + detail layout, read-only v1</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Two-column shell: left = filterable relationship list, right = selected relationship 360° detail. See CRM Ideation sheet for the full spec. v1 reads existing contacts data (customer/dealer + vendor); write actions come in E2-05/06/07.</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>E2-01</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>Route: /crm (perm='people'). Copy the ContactsPanel filter logic, throw away the tab shell. Reuse ContactProfile logic for the right pane so we don't rebuild the 360°. [2026-08-13 SHIPPED] New pages/CRM.js shipped with unified list (All / Customers / Suppliers / Mine filter chips, search bar, status dropdown), Add Customer + Add Supplier buttons in header, card grid with type / status / tag chips + view / edit / delete / log-complaint actions, click-through to /contacts/:id (existing 360°). Right-pane detail deferred to Sprint B (needs workflow-engine feed WE-06).</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-13</t>
         </is>
@@ -930,52 +1082,57 @@
           <t>E2-03</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>/crm — lifecycle-stage chip (data)</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Data model</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Add relationship lifecycle_stage field</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Add contacts.lifecycle_stage. Enum differs by type: Customer = {lead, active, loyal, dormant, churned}; Supplier = {trial, active, preferred, strategic, blocked}. Renders as a stage chip on both the CRM list and detail. Read-only migration: default to 'active' for existing rows with any transactions, 'lead' for empty vendors, 'trial' for empty customers.</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>E2-02</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>Migrate via services/migrations.py ledger. Extend PATCH /contacts/:id to accept lifecycle_stage. Enum validation in the router.</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>CRM Ideation</t>
         </is>
@@ -987,52 +1144,57 @@
           <t>E2-04</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>/crm — owner_id per relationship (data)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Data model</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Add owner_id (team-member owner) on each contact</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Today contacts have assigned_id (single field, used loosely). Rename semantics: owner_id = the person responsible for this relationship. Renders as an avatar chip on every CRM list row + detail header. Dropdown to reassign. Filters at top of CRM list ('My relationships' toggle uses this).</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>E2-02</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Read-only for finance/sales, editable by role owner or team_manage. Cascade rename lives at server.py:update_contact (see FIX-003-C pattern).</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>CRM Ideation</t>
         </is>
@@ -1044,52 +1206,57 @@
           <t>E2-05</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>/crm — tags chips (data + UI)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Data model + UI</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Free-form tags on relationships (chips)</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Add contacts.tags[] (already exists, currently unused in UI). Show tag chips on CRM list row + detail. Add-tag affordance inline. Tag filter at top of the CRM list (multi-select). Suggestions from top-8 tags in tenant.</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>E2-02</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>Tag string sanity: lowercase, max 24 chars, trim. Cap at 15 tags per contact.</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>CRM Ideation</t>
         </is>
@@ -1101,52 +1268,57 @@
           <t>E2-06</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>/crm + /team (Sprint A exit)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Milestone</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Sprint A exit gate — CRM v1 shipped, People retired</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>End-of-Sprint-A verification. Both roles walked through: founder can browse Customers + Suppliers under /crm with lifecycle stage, owner, tags; /contacts redirects; /team shows only Employees. No regressions on ContactProfile 360° (still works, now navigated to from /crm).</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>E2-01..E2-05</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>Verify test coverage adjusted (test_iteration27 TestRBACContacts still asserts 403 for prod). Screenshot the new /crm surface into the Page Redesign Log sheet.</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>Sprint A</t>
         </is>
@@ -1158,52 +1330,57 @@
           <t>E2-07</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>/crm — right-pane workflow feed</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Workflow-Engine integration</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Live workflow feed on CRM detail</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Right pane of CRM detail shows every workflow linked to this contact_id with the LIVE stage read from workflow_engine (not the stale workflows.stage column). One row per workflow: pipeline label, counterparty, amount, current stage chip, days-in-stage, next-stage button (owner-only, same gate as workflow board). Depends on WE-06 landing so the engine is authoritative.</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>E2-02, WE-06</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>Reuse the workflow board's advance() call. Show a stale-warning chip if last_transition_at &gt; 5 days. Order rows by most-recent-transition desc.</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>Founder ask 'scoped under workflow engine'</t>
         </is>
@@ -1215,52 +1392,57 @@
           <t>E2-08</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>/crm — right-pane activity timeline</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>New feature</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>CRM activity log — call, meeting, note, WhatsApp</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>New crm_activities collection: {tenant_id, contact_id, kind (call|meeting|note|whatsapp_sent|whatsapp_received|email_sent|email_received|complaint_raised|task_added), body, actor_user_id, at, meta}. Renders as a timeline on the CRM detail. 'Log activity' modal on the detail header with kind toggle + free-text body. WhatsApp/email/complaint/task kinds are written automatically by existing handlers (server.py already fires those events).</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>E2-02</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>Extend brain_context.record_context to also write a crm_activity row when kind='decision' and decision has a contact_id link. Kills two birds — timeline stays populated without a separate write pass.</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>CRM Ideation</t>
         </is>
@@ -1272,52 +1454,57 @@
           <t>E2-09</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>/contacts/:id — AI Relationship Intelligence (supplier)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>AI feature</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>AI Relationship Intelligence for Suppliers (already on Customers)</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>ContactProfile.js already has AI Relationship Intelligence for Customers (relationship + risk scores, signals, reasons, next best actions). Extend to Suppliers: use purchase-history, payment terms, delay pattern, quality complaints. Model: prompt Claude with the last 20 invoices + payments + complaints + workflow transitions for that supplier and ask for 3 signals + 3 risks + 1 recommendation. Same UI card, different data model.</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>E2-07</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>Reuse services/ai/relationship.py (already exists for customers). Add a supplier prompt template. Cache per-contact for 24h to control cost.</t>
         </is>
       </c>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>CRM Ideation</t>
         </is>
@@ -1329,52 +1516,57 @@
           <t>E2-10</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Layout — bottom-nav rebalance (Brain? / Team? etc)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Replace PEOPLE bottom-nav with CRM; add Team under Settings</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Bottom-nav becomes: DESK / BRIEF / WORK / CRM / BRAIN. The Employees tab that used to live at /contacts moves under Settings &gt; Team (owner + team_manage only). Founder rarely opens Team weekly, so it doesn't earn a bottom-nav slot. Keeps the 5-tab bottom-nav pattern; no icon count changes.</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>E2-01, E2-02</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>Layout.js:47 and :60 both need updating. Keep the perm gate on the CRM tab as 'people' (post-FIX-FUP-51 opt-in).</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>Sprint A</t>
         </is>
@@ -1386,48 +1578,53 @@
           <t>E2-11</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>/brief — remove Operating Score card</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Page redesign</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Remove Operating Score card from CEOBrief header</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-13: 'remove the operating score from the brief to new page.' CEOBrief.js:215-232 owner-only row had two side-by-side buttons (Operating Score, CEO Journal); removed Operating Score, promoted CEO Journal to full-width (col-span-2). /operating-score page unchanged — still lives at that URL.</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>XS</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr"/>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr"/>
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>Shipped 2026-08-13 in the same session as this epic created. Also removed unused Gauge icon import. Verified live in browser as amit (owner): brief header now shows only CEO JOURNAL button.</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-13</t>
         </is>
@@ -1439,52 +1636,57 @@
           <t>E2-12</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Layout — per-role bottom-nav audit</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Bottom-nav ownership audit — which tab per role?</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Today all users see the same 5 tabs (subject to perm gates). Founder-vs-teammate flows are different: teammates almost never open BRIEF, founders rarely open MyWork task cards. Audit each of the 5 tabs and decide the target set for each role. Might land as a 'primary tab' per role config, or as simple reordering.</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>E2-10</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>Read-only audit first — no changes. Then propose.</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="100" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
@@ -1492,48 +1694,53 @@
           <t>E2-13</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Across screens — empty states with CTA</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>First-run empty states with clear next action</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Every list surface (My Work, Inbox activity feed, Workflow board, CRM list, Ledger tables) currently renders 'Nothing here' with no next action for a fresh tenant. Write a per-surface empty state with a specific CTA button (e.g. 'Add your first customer', 'Record your first decision in the Desk').</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr"/>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr"/>
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Blocks the moment a founder finishes onboarding — they land on empty dashboards and don't know where to start. High retention-value fix.</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="100" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -1541,48 +1748,53 @@
           <t>E2-14</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Across screens — skeleton loaders</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Polish</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Skeleton loaders instead of blank/'Loading...' text</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Every page currently shows 'Loading brief...' or empty space during initial fetch. Replace with brutalist skeleton bars (KPI card outlines, table row outlines) so the layout stops jumping when data lands. Keeps the brand and reduces perceived latency.</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>Backlog</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr"/>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>Reuse the existing skeleton component pattern from the brief details drill-down.</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="100" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
@@ -1590,52 +1802,57 @@
           <t>E2-15</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Layout — Ops nav entry → /operating-score</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Ops menu entry — owner-only shortcut to /operating-score</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-13 same session: 'add the button called operation score in main menu.. we will name it Ops.' Added Ops entry to the main sidebar NAV in Layout.js (Gauge icon, ownerOnly, position 4 between My Work and CRM). Points to /operating-score. Non-owners don't see the item at all (filtered out by useMemo(NAV.filter)). Matches the pattern E2-11 established when we removed the Operating Score card from the CEO Brief header — the page still lives at /operating-score, just moved from a Brief shortcut to a first-class nav entry.</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>XS</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>E2-11</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>SHIPPED 2026-08-13. Verified live: hamburger drawer shows Decision Desk &gt; CEO Brief &gt; My Work &gt; Ops &gt; CRM &gt; Team &gt; Company Brain &gt; Finance &gt; Capture &gt; Meeting Notes &gt; Settings. nav-ops testid resolves to href=/operating-score. Hindi label 'ऑप्स', Tamil label 'இயக்கம்' added to i18n.</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-13</t>
         </is>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +58,12 @@
     <font>
       <b val="1"/>
       <color rgb="00006100"/>
+    </font>
+    <font/>
+    <font>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="6">
@@ -118,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,6 +148,20 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -508,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -620,251 +640,512 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Sprint breakdown</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Sprint A — People split + CRM shell</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="38" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>E2-01 → E2-06. Ships the split (Employees off /contacts), stubs the new /crm surface, ships CRM v1 read-only (list + basic detail).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Sprint 1 -- CRM &amp; People split</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Sprint B — CRM workflow integration</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="38" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>E2-07 → E2-10. Wires the CRM detail to the Workflow Engine feed, activity log write endpoint, tags, per-relationship owner assignment. Depends on WE-06 (engine) landing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Sprint C — Brief + navigation cleanup</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="38" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>E2-11 (Operating Score off Brief — DONE 2026-08-13). E2-12/13/14/15 handle bottom-nav restructure, ownership of each page, page-load empty states.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Shipping (Sprint A partial live)</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>E2-01, E2-02, E2-03, E2-04, E2-05, E2-06, E2-07, E2-08, E2-09, E2-10</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="n"/>
+    </row>
+    <row r="23" ht="95" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Split the old three-tab /contacts People page into two purposeful surfaces: /crm (customers + suppliers, relationship-first, workflow-engine-integrated) and /team (employees only, HR/admin). Build the CRM v1 shell with filter chips, search, card grid; wire the right-pane detail feed to the Workflow Engine (depends on WE-06); ship activity log, lifecycle stage, owner-per-relationship, tags.</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="n"/>
+    </row>
+    <row r="24" ht="145" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-13: 'separate the people section first because I wanted to create CRM for the supplier and customer -- not high-level, manage the details, scoped under our workflow engine.' Today the People page tries to do two jobs and the Add button changes meaning by tab. Splitting also unlocks role-specific perm defaults (sales can see CRM without seeing Team). Every workflow-linked row on the CRM detail will read its live stage from the Workflow Engine -- kills the FUP-48 class of stale-copy bug at the source. SHIPPED so far: /crm shell + /team page + /contacts redirect + PEOPLE bottom-nav slot renamed to CRM.</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="13" t="n"/>
+      <c r="G25" s="13" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Sprint 2 -- Decision Desk redesign</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Backlog</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>The scoped work items (E2-01..). Single source of truth for what Epic 2 does.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Backlog -- ideating</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>CRM Ideation</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>The detailed CRM design — shell layout, data model, workflow-engine hooks, activities, tags, lifecycle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Page Redesign Log</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Running log of visual/UX changes shipped (E2-11 already logged).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>E2-16, E2-17, E2-18, E2-19, E2-20, E2-21, E2-22</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="n"/>
+    </row>
+    <row r="29" ht="95" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Rebuild /inbox as a decision-only surface with four chips exactly as the founder mocks show: Needs Your Decision, On Fire, Due Today, Important. Card anatomy matches the mocks (title + context line + amount + primary CTA). Ship a single /api/desk aggregation endpoint that replaces the three separate fetches (/inbox + /decisions + /tasks?mine=true). Migrate the 'Needs Your Attention' cards under the 'On Fire' chip with the reply composer preserved. Delete the mixed 'Tasks &amp; Activity' feed, the classification chips row, and the mic/text/file capture UI from the Desk. Move capture to /ingest as its single home. Add a Nudge / Chase primary action that sends WhatsApp (fallback email) to the person we are waiting on. Ship an AI ranker for the Important chip.</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="n"/>
+    </row>
+    <row r="30" ht="145" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14 with three annotated screenshots: the Decision Desk should surface only decisions the founder owes today -- nothing else. Today the /inbox page mixes a unified activity feed (invoices, payments, complaints, tasks, approvals, reminders) with capture UI and a Pending Approvals grid. Founder said 'I wanted to remove the task list from decision desk because I think we already have that in the work section' -- audit confirmed MyWork covers all task-management needs richer than the Desk feed; keeping tasks on the Desk is duplication that dilutes the founder's most important surface. Also 'we will have the approval of decision option here alone' -- the Desk earns its slot in the founder's cognitive map by being the single place for 'what decisions am I holding up?'. Consolidating capture at /ingest kills the 'two places to record a voice note' confusion. The 4-chip structure matches how a founder actually triages the day (urgent vs important vs today vs raised-to-me). Nudge/Chase turns a passive list into one-tap action -- one click sends the WhatsApp instead of 'I should follow up later'.</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="13" t="n"/>
+      <c r="G31" s="13" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Sprint 3 -- Brief &amp; Navigation polish</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>Partial (E2-11 + E2-15 Done)</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>E2-11 (Done), E2-12, E2-13, E2-14, E2-15 (Done)</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="n"/>
+    </row>
+    <row r="35" ht="95" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>Sharpen the surfaces the founder opens most. Remove the Operating Score shortcut from the CEO Brief header so the Brief stays a pure dashboard (E2-11, Done). Add Ops as a first-class owner-only sidebar entry pointing at /operating-score (E2-15, Done). Ship empty-state CTAs and skeleton loaders across every list page. Audit the bottom-nav ownership per role (founders and teammates open different tabs).</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="n"/>
+    </row>
+    <row r="36" ht="145" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-13: 'remove the operating score from the brief to new page.' The Brief header cards were competing with the KPI grid for attention. Operating Score deserves its own room. Also every list surface today shows 'Nothing here' on a fresh tenant with zero next-step CTA -- founders finish onboarding and land on empty dashboards not knowing where to start (retention-value fix). Skeleton loaders replace 'Loading...' text and stop layout jumping when data arrives.</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="13" t="n"/>
+      <c r="G37" s="13" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>Backlog columns</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="B38" s="16" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="13" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>E2-&lt;n&gt; ticket ID</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="G39" s="13" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Screen / Feature</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Which page or feature this touches — sort/filter by this to see all work on /crm at once</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Which page or feature this touches -- sort/filter by this to see all work on /inbox at once</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>A / B / C</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>1 / 2 / 3 (see blocks above)</t>
+        </is>
+      </c>
+      <c r="G41" s="13" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Info architecture · New page · Data model · Navigation · AI feature · Polish · Milestone</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Info architecture / New page / Data model / Navigation / AI feature / Polish / Milestone / Backend</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>Short imperative summary</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="G43" s="13" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>The what and why</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="G44" s="13" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Priority / Effort / Status</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>P1..P3 / XS..L / Backlog|In Progress|Done</t>
         </is>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="G45" s="13" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Depends on</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t>Prereq ticket IDs (e.g. WE-06 from the Workflow Engine sprint in Epic 1)</t>
         </is>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="G46" s="13" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Notes / evidence</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>Live-test evidence, screenshot references, shipping notes</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="G47" s="13" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>Where the ask came from (founder ask, CRM Ideation, Sprint plan, etc.)</t>
         </is>
       </c>
+      <c r="G48" s="13" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="13" t="n"/>
+      <c r="B49" s="13" t="n"/>
+      <c r="C49" s="13" t="n"/>
+      <c r="D49" s="13" t="n"/>
+      <c r="E49" s="13" t="n"/>
+      <c r="F49" s="13" t="n"/>
+      <c r="G49" s="13" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="13" t="n"/>
+      <c r="B50" s="13" t="n"/>
+      <c r="C50" s="13" t="n"/>
+      <c r="D50" s="13" t="n"/>
+      <c r="E50" s="13" t="n"/>
+      <c r="F50" s="13" t="n"/>
+      <c r="G50" s="13" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="13" t="n"/>
+      <c r="B51" s="13" t="n"/>
+      <c r="C51" s="13" t="n"/>
+      <c r="D51" s="13" t="n"/>
+      <c r="E51" s="13" t="n"/>
+      <c r="F51" s="13" t="n"/>
+      <c r="G51" s="13" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="13" t="n"/>
+      <c r="B52" s="13" t="n"/>
+      <c r="C52" s="13" t="n"/>
+      <c r="D52" s="13" t="n"/>
+      <c r="E52" s="13" t="n"/>
+      <c r="F52" s="13" t="n"/>
+      <c r="G52" s="13" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="13" t="n"/>
+      <c r="B53" s="13" t="n"/>
+      <c r="C53" s="13" t="n"/>
+      <c r="D53" s="13" t="n"/>
+      <c r="E53" s="13" t="n"/>
+      <c r="F53" s="13" t="n"/>
+      <c r="G53" s="13" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="13" t="n"/>
+      <c r="B54" s="13" t="n"/>
+      <c r="C54" s="13" t="n"/>
+      <c r="D54" s="13" t="n"/>
+      <c r="E54" s="13" t="n"/>
+      <c r="F54" s="13" t="n"/>
+      <c r="G54" s="13" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="13" t="n"/>
+      <c r="B55" s="13" t="n"/>
+      <c r="C55" s="13" t="n"/>
+      <c r="D55" s="13" t="n"/>
+      <c r="E55" s="13" t="n"/>
+      <c r="F55" s="13" t="n"/>
+      <c r="G55" s="13" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="13" t="n"/>
+      <c r="B56" s="13" t="n"/>
+      <c r="C56" s="13" t="n"/>
+      <c r="D56" s="13" t="n"/>
+      <c r="E56" s="13" t="n"/>
+      <c r="F56" s="13" t="n"/>
+      <c r="G56" s="13" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="13" t="n"/>
+      <c r="B57" s="13" t="n"/>
+      <c r="C57" s="13" t="n"/>
+      <c r="D57" s="13" t="n"/>
+      <c r="E57" s="13" t="n"/>
+      <c r="F57" s="13" t="n"/>
+      <c r="G57" s="13" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="13" t="n"/>
+      <c r="B58" s="13" t="n"/>
+      <c r="C58" s="13" t="n"/>
+      <c r="D58" s="13" t="n"/>
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="13" t="n"/>
+      <c r="G58" s="13" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="13" t="n"/>
+      <c r="B59" s="13" t="n"/>
+      <c r="C59" s="13" t="n"/>
+      <c r="D59" s="13" t="n"/>
+      <c r="E59" s="13" t="n"/>
+      <c r="F59" s="13" t="n"/>
+      <c r="G59" s="13" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="35">
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B46:F46"/>
     <mergeCell ref="A12:F12"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B21:F21"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B48:F48"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="B23:F23"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="B44:F44"/>
     <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B38:F38"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B37:F37"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="B30:F30"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B24:F24"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B45:F45"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
@@ -878,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -969,7 +1250,7 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -1027,7 +1308,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -1089,7 +1370,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1151,7 +1432,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -1213,7 +1494,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1275,7 +1556,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -1337,7 +1618,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1399,7 +1680,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -1461,7 +1742,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1523,7 +1804,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -1585,7 +1866,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1643,7 +1924,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -1701,7 +1982,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -1755,7 +2036,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1809,7 +2090,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -1855,6 +2136,432 @@
       <c r="L16" s="7" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="130" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>E2-16</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>/inbox -- 4-chip shell + counter subline</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Info architecture</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Rebuild Decision Desk as a decision-only 4-chip surface</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Replace the current mixed /inbox page with the founder's mock design: header 'Decision Desk' + counter subline ('6 decisions waiting on you / 8 on fire / 3 due today'), four mutually-exclusive chip tabs (Needs Your Decision, On Fire, Due Today, Important), card grid using the anatomy from the mocks (title + context line + amount + primary CTA). No task-list, no mixed feed, no capture UI. Chips are backed by client-side filtering on the /api/desk response; sort per chip: Needs Your Decision by waiting-days desc, On Fire by overdue days desc, Due Today by amount desc, Important by AI score desc.</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr"/>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Founder mocks 2026-08-14 (3 annotated screenshots). Card CTA copy per chip: Review / Respond / Chase / Nudge. Preserves ownerOnly gate on the Decision Approvals content -- non-owners see an empty 'Needs Your Decision' and still get 'On Fire' when they have escalations / handoffs.</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>Founder mocks 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="130" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>E2-17</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Backend -- /api/desk?chip=... aggregation endpoint</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>One /api/desk endpoint returns {counters, cards[]} per chip</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>New endpoint replaces the three fetches the Desk does today (/inbox + /decisions + /tasks?mine=true). Query param 'chip' in {needs_decision, on_fire, due_today, important}. Response: {counters:{needs_decision:N, on_fire:N, due_today:N, important:N}, cards:[{id, title, context_line, amount?, cta:'review|respond|chase|nudge', target_id, target_kind}]}. counters always returned so header subline can render without a second call. Tenant-scoped, user-scoped.</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>E2-16</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Backend logic: needs_decision = decisions.status=pending AND approver_id=me OR (owner_id=me AND approver_id=null). on_fire = task escalations/handoffs to me UNION overdue tasks I own. due_today = due_date=today in my column. important = AI-ranked (services/ai/priorities.py decision variant, E2-21).</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>Ideation 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="130" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>E2-18</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>/inbox -- 'On Fire' chip content</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Merge 'Needs Your Attention' cards into the On Fire chip</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Today the escalations + handoffs 'Needs Your Attention' cards render as a standalone section on /inbox with typed inline reply. Fold them into the On Fire chip alongside overdue-I-own cards. Reply composer preserved -- 'Respond' button on escalation/handoff cards opens the same POST /tasks/{id}/respond flow. Chase button on overdue cards is the new one, wired via E2-22.</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>E2-16, E2-17</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Card 'Respond' vs 'Chase' distinction: Respond = I owe someone a reply (they escalated/handed off to me). Chase = someone owes me completion (I own an overdue task). Two different verbs, same chip.</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Founder mocks 2026-08-14 (On Fire chip screenshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="130" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>E2-19</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>/inbox -- delete legacy sections</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Deletion</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Delete task feed + classification chips + capture UI from Desk</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Once E2-16/17/18 are green, delete: (a) the 'Tasks &amp; Activity' unified feed and its SwipeRow component, (b) the classification chips row (customer/supplier/invoice/payment/complaint/task/approval/reminder), (c) the mic/text/file capture UI. All three duplicate or dilute what MyWork + /ingest already do. Also delete the 'Structuring' sticky banner and the pre-submit AI clarify Q&amp;A -- those move to /ingest with the capture UI (E2-20).</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>E2-16, E2-17, E2-18, E2-20</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Deep-link safety: nothing in the codebase links '?task=' or '?focus=task:...' into the Desk. CEO Brief routes task notifications to /my-work?task=... (see CEOBrief.js:81, lib/notif.js:19). Zero deep-links break.</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14 'we will have the approval of decision option here alone'</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="130" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>E2-20</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>/ingest -- capture UX consolidated</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Move mic/text/file capture from Desk to /ingest</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>/ingest already has upload capabilities. Add the Desk's mic recorder (pause/resume/finalise/cancel, language auto-detect), text directive box (with pre-submit AI clarify Q&amp;A), and file/photo drop as first-class Import tabs on the /ingest page. Preserves 'Analyse &amp; structure' wording. Voice-notes POST endpoint stays the same.</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Can ship before E2-19; E2-19 depends on this landing so users don't lose the capture affordance. Nav 'Capture' item already points at /ingest -- no nav change needed.</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>Ideation 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="130" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>E2-21</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>/inbox -- 'Important' chip AI ranking</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>AI feature</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Extend services/ai/priorities.py for decision-level ranking</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>The 'Important' chip is meaningless without an AI ranker. Extend the existing services/ai/priorities.py (already scores tasks for MyWork AI-Priority) with a decision-level model that surfaces 'not urgent yet but worth your attention'. Signals: high monetary amount, strategic keyword match, pattern from prior founder-approved decisions (via brain_context), days since raised without action. Cache per tenant per user for 15 minutes.</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>E2-16, E2-17</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Uses the same LLM call pattern as MyWork AI-Priority. Fail-open: if the model call errors, Important chip returns empty (0) -- matches the founder mock where it shows 0.</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Founder mocks 2026-08-14 ('Important 0' chip)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="130" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>E2-22</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>/inbox -- decision card Nudge/Chase actions</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>New feature</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Nudge / Chase button -&gt; WhatsApp (fallback email) counterparty</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>New POST /api/desk/nudge/{item_id} sends a WhatsApp template to the person we're waiting on (from the item's target owner / counterparty). Falls back to email if WhatsApp isn't configured. Two copy variants: 'Nudge' for Due Today items ('hi, this is due today, when can you get it done?'), 'Chase' for overdue items ('hi, this was due N days ago, please prioritise'). One-tap action; success toast with 'Sent via WhatsApp' or 'Sent via email'. Logs to crm_activities (E2-08 collection, once landed).</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>E2-16, E2-17</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Wraps existing services/whatsapp.py send helper. For decisions, targets the person who raised it (from field). For overdue tasks, targets the current assignee. If neither has a phone number, button shows disabled tooltip 'No contact channel'.</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Founder mocks 2026-08-14 (Nudge / Chase CTAs)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +65,12 @@
       <color rgb="000F172A"/>
       <sz val="13"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +101,12 @@
         <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -124,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -162,6 +172,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2180,15 +2193,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr"/>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Founder mocks 2026-08-14 (3 annotated screenshots). Card CTA copy per chip: Review / Respond / Chase / Nudge. Preserves ownerOnly gate on the Decision Approvals content -- non-owners see an empty 'Needs Your Decision' and still get 'On Fire' when they have escalations / handoffs.</t>
+          <t>Founder mocks 2026-08-14 (3 annotated screenshots). Card CTA copy per chip: Review / Respond / Chase / Nudge. Preserves ownerOnly gate on the Decision Approvals content -- non-owners see an empty 'Needs Your Decision' and still get 'On Fire' when they have escalations / handoffs. [2026-08-14 SHIPPED] New pages/Desk.js live at /inbox. 4 chips + counter subline + card grid rendering /api/desk data. Capture bar (mic + text + file) preserved at top per founder confirmation. Verified in browser as amit (owner) with 6 seeded pending decisions -- header renders '6 decisions waiting on you · 0 on fire · 0 due today', chips show correct counters, cards render title/context/amount/REVIEW-&gt; exactly matching founder mocks.</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -2238,9 +2251,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
@@ -2250,7 +2263,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Backend logic: needs_decision = decisions.status=pending AND approver_id=me OR (owner_id=me AND approver_id=null). on_fire = task escalations/handoffs to me UNION overdue tasks I own. due_today = due_date=today in my column. important = AI-ranked (services/ai/priorities.py decision variant, E2-21).</t>
+          <t>Backend logic: needs_decision = decisions.status=pending AND approver_id=me OR (owner_id=me AND approver_id=null). on_fire = task escalations/handoffs to me UNION overdue tasks I own. due_today = due_date=today in my column. important = AI-ranked (services/ai/priorities.py decision variant, E2-21). [2026-08-14 SHIPPED] New backend/routers/desk.py with GET /api/desk?chip=...+ POST /api/desk/nudge/{id}. Wired into server.py alongside the other routers. Smoke-tested all 4 chip paths return 200 with structured {chip, counters, cards} response. Tenant + user scoped. Owner all-perms + non-owner approver_id=me both work.</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -2300,9 +2313,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
@@ -2312,7 +2325,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>Card 'Respond' vs 'Chase' distinction: Respond = I owe someone a reply (they escalated/handed off to me). Chase = someone owes me completion (I own an overdue task). Two different verbs, same chip.</t>
+          <t>Card 'Respond' vs 'Chase' distinction: Respond = I owe someone a reply (they escalated/handed off to me). Chase = someone owes me completion (I own an overdue task). Two different verbs, same chip. [2026-08-14 SHIPPED] Folded into E2-16/17: the /api/desk on_fire chip merges escalations + handoffs + overdue in a single card list. Card 'kind' is task_escalation | task_handoff | task_overdue so the front-end can pick 'Respond' vs 'Chase' CTA correctly. Front-end onCardAction routes 'respond' to /my-work?task=&lt;id&gt; for the full task detail context.</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -2362,9 +2375,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
@@ -2374,7 +2387,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>Deep-link safety: nothing in the codebase links '?task=' or '?focus=task:...' into the Desk. CEO Brief routes task notifications to /my-work?task=... (see CEOBrief.js:81, lib/notif.js:19). Zero deep-links break.</t>
+          <t>Deep-link safety: nothing in the codebase links '?task=' or '?focus=task:...' into the Desk. CEO Brief routes task notifications to /my-work?task=... (see CEOBrief.js:81, lib/notif.js:19). Zero deep-links break. [2026-08-14 SHIPPED] New Desk.js replaces the old Inbox.js rendering at /inbox. Old file kept alive at /inbox-legacy for one commit as a safety net; the user-facing surface is clean. Follow-up will delete Inbox.js entirely. No deep-link breakage -- CEO Brief already routes task notifs to /my-work?task=&lt;id&gt; (verified in the earlier Page Feature Map audit).</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -2424,15 +2437,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr"/>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>Can ship before E2-19; E2-19 depends on this landing so users don't lose the capture affordance. Nav 'Capture' item already points at /ingest -- no nav change needed.</t>
+          <t>Can ship before E2-19; E2-19 depends on this landing so users don't lose the capture affordance. Nav 'Capture' item already points at /ingest -- no nav change needed. [2026-08-14 DROPPED] Founder pushed back on this in-session: 'thats not the plan right move capture to ingest what you are saying? explain why we moving?' Correct interpretation: Desk keeps capture at the top (recording a decision is Desk-native; /ingest is for paperwork). Item redefined as 'keep capture on Desk' and shipped as part of E2-16 CaptureBar component.</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -2544,9 +2557,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
@@ -2556,7 +2569,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>Wraps existing services/whatsapp.py send helper. For decisions, targets the person who raised it (from field). For overdue tasks, targets the current assignee. If neither has a phone number, button shows disabled tooltip 'No contact channel'.</t>
+          <t>Wraps existing services/whatsapp.py send helper. For decisions, targets the person who raised it (from field). For overdue tasks, targets the current assignee. If neither has a phone number, button shows disabled tooltip 'No contact channel'. [2026-08-14 SHIPPED] POST /api/desk/nudge/{id} live. Writes a notification for the target user (assignee for tasks; created_by for decisions). Frontend Chase/Nudge buttons wired: POST + toast on success ('Nudged Priya -- sent via notification'). WhatsApp channel is a follow-up wire when WHATSAPP_API_KEY is provisioned -- response contract 'channel' field stays stable so no front-end change needed then.</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -3211,7 +3224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3350,6 +3363,48 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="145" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>E2-16/17/18/19/22</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Decision Desk (/inbox) -- full rebuild</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Rebuilt /inbox from a mixed activity feed into a decision-only surface with 4 chips (Needs Your Decision / On Fire / Due Today / Important) exactly per founder mocks 2026-08-14. Capture bar (mic + text + file) preserved at the top. New /api/desk aggregation endpoint replaces 3 separate fetches. Nudge/Chase action endpoint added.</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>906-line Inbox.js: capture UI + owner-only Decision Approvals grid + Needs Your Attention section + mixed classification chips row + Tasks &amp; Activity unified feed with SwipeRow. Three separate API calls. Task rows duplicated MyWork. Classification chips (customer/supplier/invoice/payment/complaint/task/approval/reminder) added noise.</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>New Desk.js (~300 lines): CaptureBar at top, header + counter subline, 4-chip filter, DeskCard grid. All content sourced from one /api/desk call per chip. Escalations/handoffs fold into On Fire chip; overdue tasks I own also go under On Fire. Decision approvals content is now the Needs Your Decision chip. Nudge/Chase primary CTAs fire /api/desk/nudge and toast on success.</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Verified live in preview browser as amit@kapoormills.co.in with 6 seeded pending decisions: header '6 decisions waiting on you · 0 on fire · 0 due today', NEEDS YOUR DECISION chip shows [6] and card grid renders each decision with 'Waiting N days · From &lt;person&gt; · Unblocks N tasks' context and amount / REVIEW-&gt; button. Old Inbox.js still alive at /inbox-legacy as a safety net.</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -2263,7 +2263,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Backend logic: needs_decision = decisions.status=pending AND approver_id=me OR (owner_id=me AND approver_id=null). on_fire = task escalations/handoffs to me UNION overdue tasks I own. due_today = due_date=today in my column. important = AI-ranked (services/ai/priorities.py decision variant, E2-21). [2026-08-14 SHIPPED] New backend/routers/desk.py with GET /api/desk?chip=...+ POST /api/desk/nudge/{id}. Wired into server.py alongside the other routers. Smoke-tested all 4 chip paths return 200 with structured {chip, counters, cards} response. Tenant + user scoped. Owner all-perms + non-owner approver_id=me both work.</t>
+          <t>Backend logic: needs_decision = decisions.status=pending AND approver_id=me OR (owner_id=me AND approver_id=null). on_fire = task escalations/handoffs to me UNION overdue tasks I own. due_today = due_date=today in my column. important = AI-ranked (services/ai/priorities.py decision variant, E2-21). [2026-08-14 SHIPPED] New backend/routers/desk.py with GET /api/desk?chip=...+ POST /api/desk/nudge/{id}. Wired into server.py alongside the other routers. Smoke-tested all 4 chip paths return 200 with structured {chip, counters, cards} response. Tenant + user scoped. Owner all-perms + non-owner approver_id=me both work. [2026-08-14 E2E FIX] on_fire overdue + due_today query semantics tightened: assignee_id != me AND (created_by=me OR user is owner). Kills 'nudge yourself' 400 that surfaced during the browser walkthrough. My own overdue stays on My Work.</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -3224,7 +3224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3405,6 +3405,48 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="155" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>E2-16..E2-22 (E2E)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>/inbox -- Sprint 2 E2E verification</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Full end-to-end walkthrough in the preview browser as amit (owner). Seeded 6 pending decisions + 9 tasks (3 escalations/handoffs to amit + 3 overdue on teammates + 3 due-today on teammates). Exercised every chip and every CTA. Found + fixed one semantics bug in the on_fire query.</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>On_fire overdue query was assignee_id=me -- surfaced my OWN overdue todos on the Desk. Clicking Chase returned 400 'Can't nudge yourself' because the nudge target = assignee = me. Semantic confusion: Chase is for teammates dragging on my work, not for my own todos (those live on My Work).</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>On_fire overdue + due_today queries now scope to assignee_id != me AND (created_by=me OR user is owner). Owner sees every non-owner overdue in the tenant (they're accountable for the whole company). Non-owners see overdue tasks they raised for a teammate. My own overdue stays visible on My Work. Chase button now hits a real target and returns 200. Verified live: Chase on 'Reconcile packaging invoice against the GRN' (assigned to Priya) fired 200 OK; notification count went from 11 -&gt; 14 as nudges landed.</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Verified all 4 chips render and switch correctly. Header counters '6 waiting on you / 6 on fire / 3 due today' match the founder mock language exactly. Cards render with 'Waiting N days · From X · Unblocks N tasks' (Needs Your Decision), 'Escalated by X · With Y' or 'N days overdue · With Y' (On Fire), 'With Y' (Due Today). REVIEW opens DecisionDialog. RESPOND (task escalation) jumps to /my-work?task=. CHASE and NUDGE both fire /api/desk/nudge and toast on success. Important chip shows empty state (fail-open per E2-21).</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -883,131 +883,85 @@
       <c r="G37" s="13" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Sprint 4 -- Finance + Capture merge</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Backlog -- ideating (founder ask 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>E2-23, E2-24, E2-25, E2-26, E2-27, E2-28, E2-29, E2-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="110" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Merge document-capture (/ingest) into Finance (/ledger, renamed to /finance). Add a hero drop-zone at the top of EVERY Finance tab -- 'Drop bills, take a photo, paste WhatsApp, or upload CSV' -- so the founder can capture from anywhere in Finance without navigating first. The Ingest Review Queue moves in as the 6th Inbox tab. WhatsApp QR + inbound logs move under the Overview sidebar. Sidebar 'Capture' nav entry retires. Old routes /ledger and /ingest redirect to /finance for bookmark safety. Note: DECISION capture (voice/text on Desk) is separate and stays on the Desk -- this sprint only consolidates DOCUMENT capture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="145" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14: 'finance + capture next sprint, we plan to integrate both are actually same, capture will be used mostly by the finance team only.' Correct read: document capture (PDF bills, CSV imports, WhatsApp photos of GST slips) is almost entirely finance-adjacent. The current split forces founders through two mental models ('did I capture that receipt?' vs 'did that expense make it into the ledger?') for what is really one flow. Hero drop-zone placement (founder pick 2026-08-14) keeps capture one click from any Finance tab -- matches the 'zero-click to record' principle that Desk capture already established. Compresses the top nav by one entry, matches the pattern established when we removed 'People' in favour of CRM + Team split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1"/>
+    <row r="44" ht="15" customHeight="1"/>
+    <row r="45" ht="15" customHeight="1"/>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Backlog columns</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="13" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>E2-&lt;n&gt; ticket ID</t>
-        </is>
-      </c>
-      <c r="G39" s="13" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Screen / Feature</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>Which page or feature this touches -- sort/filter by this to see all work on /inbox at once</t>
-        </is>
-      </c>
-      <c r="G40" s="13" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>1 / 2 / 3 (see blocks above)</t>
-        </is>
-      </c>
-      <c r="G41" s="13" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>Info architecture / New page / Data model / Navigation / AI feature / Polish / Milestone / Backend</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>Short imperative summary</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>The what and why</t>
-        </is>
-      </c>
-      <c r="G44" s="13" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Priority / Effort / Status</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="inlineStr">
-        <is>
-          <t>P1..P3 / XS..L / Backlog|In Progress|Done</t>
-        </is>
-      </c>
-      <c r="G45" s="13" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Depends on</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>Prereq ticket IDs (e.g. WE-06 from the Workflow Engine sprint in Epic 1)</t>
-        </is>
-      </c>
+      <c r="B46" s="16" t="n"/>
+      <c r="C46" s="13" t="n"/>
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="13" t="n"/>
       <c r="G46" s="13" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Notes / evidence</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>Live-test evidence, screenshot references, shipping notes</t>
+          <t>E2-&lt;n&gt; ticket ID</t>
         </is>
       </c>
       <c r="G47" s="13" t="n"/>
@@ -1015,86 +969,118 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
+          <t>Screen / Feature</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>Which page or feature this touches -- sort/filter by this to see all work on /inbox at once</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>1 / 2 / 3 (see blocks above)</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>Info architecture / New page / Data model / Navigation / AI feature / Polish / Milestone / Backend</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>Short imperative summary</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>The what and why</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Priority / Effort / Status</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>P1..P3 / XS..L / Backlog|In Progress|Done</t>
+        </is>
+      </c>
+      <c r="G53" s="13" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Depends on</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>Prereq ticket IDs (e.g. WE-06 from the Workflow Engine sprint in Epic 1)</t>
+        </is>
+      </c>
+      <c r="G54" s="13" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Notes / evidence</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="inlineStr">
+        <is>
+          <t>Live-test evidence, screenshot references, shipping notes</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B56" s="16" t="inlineStr">
         <is>
           <t>Where the ask came from (founder ask, CRM Ideation, Sprint plan, etc.)</t>
         </is>
       </c>
-      <c r="G48" s="13" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="13" t="n"/>
-      <c r="B49" s="13" t="n"/>
-      <c r="C49" s="13" t="n"/>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
-      <c r="F49" s="13" t="n"/>
-      <c r="G49" s="13" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="13" t="n"/>
-      <c r="B50" s="13" t="n"/>
-      <c r="C50" s="13" t="n"/>
-      <c r="D50" s="13" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="G50" s="13" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="13" t="n"/>
-      <c r="B51" s="13" t="n"/>
-      <c r="C51" s="13" t="n"/>
-      <c r="D51" s="13" t="n"/>
-      <c r="E51" s="13" t="n"/>
-      <c r="F51" s="13" t="n"/>
-      <c r="G51" s="13" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="13" t="n"/>
-      <c r="B52" s="13" t="n"/>
-      <c r="C52" s="13" t="n"/>
-      <c r="D52" s="13" t="n"/>
-      <c r="E52" s="13" t="n"/>
-      <c r="F52" s="13" t="n"/>
-      <c r="G52" s="13" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="13" t="n"/>
-      <c r="B53" s="13" t="n"/>
-      <c r="C53" s="13" t="n"/>
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
-      <c r="F53" s="13" t="n"/>
-      <c r="G53" s="13" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="13" t="n"/>
-      <c r="B54" s="13" t="n"/>
-      <c r="C54" s="13" t="n"/>
-      <c r="D54" s="13" t="n"/>
-      <c r="E54" s="13" t="n"/>
-      <c r="F54" s="13" t="n"/>
-      <c r="G54" s="13" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="13" t="n"/>
-      <c r="B55" s="13" t="n"/>
-      <c r="C55" s="13" t="n"/>
-      <c r="D55" s="13" t="n"/>
-      <c r="E55" s="13" t="n"/>
-      <c r="F55" s="13" t="n"/>
-      <c r="G55" s="13" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="13" t="n"/>
-      <c r="B56" s="13" t="n"/>
-      <c r="C56" s="13" t="n"/>
-      <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
       <c r="G56" s="13" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1">
@@ -1124,8 +1110,80 @@
       <c r="F59" s="13" t="n"/>
       <c r="G59" s="13" t="n"/>
     </row>
+    <row r="60">
+      <c r="A60" s="13" t="n"/>
+      <c r="B60" s="13" t="n"/>
+      <c r="C60" s="13" t="n"/>
+      <c r="D60" s="13" t="n"/>
+      <c r="E60" s="13" t="n"/>
+      <c r="F60" s="13" t="n"/>
+      <c r="G60" s="13" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="n"/>
+      <c r="B61" s="13" t="n"/>
+      <c r="C61" s="13" t="n"/>
+      <c r="D61" s="13" t="n"/>
+      <c r="E61" s="13" t="n"/>
+      <c r="F61" s="13" t="n"/>
+      <c r="G61" s="13" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="n"/>
+      <c r="B62" s="13" t="n"/>
+      <c r="C62" s="13" t="n"/>
+      <c r="D62" s="13" t="n"/>
+      <c r="E62" s="13" t="n"/>
+      <c r="F62" s="13" t="n"/>
+      <c r="G62" s="13" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="n"/>
+      <c r="B63" s="13" t="n"/>
+      <c r="C63" s="13" t="n"/>
+      <c r="D63" s="13" t="n"/>
+      <c r="E63" s="13" t="n"/>
+      <c r="F63" s="13" t="n"/>
+      <c r="G63" s="13" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="n"/>
+      <c r="B64" s="13" t="n"/>
+      <c r="C64" s="13" t="n"/>
+      <c r="D64" s="13" t="n"/>
+      <c r="E64" s="13" t="n"/>
+      <c r="F64" s="13" t="n"/>
+      <c r="G64" s="13" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="n"/>
+      <c r="B65" s="13" t="n"/>
+      <c r="C65" s="13" t="n"/>
+      <c r="D65" s="13" t="n"/>
+      <c r="E65" s="13" t="n"/>
+      <c r="F65" s="13" t="n"/>
+      <c r="G65" s="13" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="n"/>
+      <c r="B66" s="13" t="n"/>
+      <c r="C66" s="13" t="n"/>
+      <c r="D66" s="13" t="n"/>
+      <c r="E66" s="13" t="n"/>
+      <c r="F66" s="13" t="n"/>
+      <c r="G66" s="13" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="n"/>
+      <c r="B67" s="13" t="n"/>
+      <c r="C67" s="13" t="n"/>
+      <c r="D67" s="13" t="n"/>
+      <c r="E67" s="13" t="n"/>
+      <c r="F67" s="13" t="n"/>
+      <c r="G67" s="13" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="36">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B46:F46"/>
@@ -1145,6 +1203,7 @@
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="B44:F44"/>
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="B34:F34"/>
@@ -1172,7 +1231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2575,6 +2634,474 @@
       <c r="L23" s="7" t="inlineStr">
         <is>
           <t>Founder mocks 2026-08-14 (Nudge / Chase CTAs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="120" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>E2-23</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>/finance shell</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Info architecture</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Rename /ledger to /finance + capture hero bar at top of every tab</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Move the current /ledger surface under /finance (route rename, keep every existing tab: Overview, Revenue, Expenses, Assets, Inventory). Add a always-visible 'capture hero' bar at the top of every tab: 'Drop bills · take a photo · paste WhatsApp · upload CSV'. Founder pick 2026-08-14 -- hero placement over tab placement so capture is 1-click from anywhere.</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Router rename touches App.js + Layout.js nav labels only. Sidebar 'Finance' label unchanged; the underlying route changes.</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>E2-24</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>/finance/inbox (new 6th tab)</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Move Ingest Review Queue in as the Inbox tab</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>The current /ingest Review Queue (CaptureReview status tabs: Pending / Needs Attention / Clarification / Filed / Rejected) moves in as the 6th tab of /finance called 'Inbox'. Preserves per-capture edit, approve, reject, clarify, reassign actions. Required per-purchase Expense/Asset/Inventory bucketing stays intact. Escalated items still owner-only.</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Reuse CaptureReview component wholesale -- import it inside the new Inbox tab. Zero backend churn (existing /captures endpoints).</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="120" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>E2-25</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>/finance hero</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Port Import drop zones (PDF/photo/CSV) to the hero</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>The three drop zones from /ingest Import tab (PDF/photo single-document upload -&gt; POST /ingest/document; CSV/Excel bulk upload -&gt; POST /ingest/csv; the in-progress review panel with per-record edit/delete) collapse into the hero bar. Click Drop-bills opens a compact modal with the same three affordances. In-progress rows surface directly under the hero so founders see the extraction happen inline.</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Reuse the existing upload endpoints. UI compresses; backend unchanged.</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="120" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>E2-26</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>/finance/overview -- sidebar card</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Move WhatsApp QR + inbound logs to Overview sidebar</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>The 'WhatsApp status' card + owner-only inbound logs table (currently on /ingest) move into the Overview tab's right sidebar as a compact card. Rarely-touched but useful to see 'WhatsApp is connected · 12 messages today'. Owner-only for the logs table.</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr"/>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Reuse GET /whatsapp/status + GET /whatsapp/logs. Small card component.</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="120" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>E2-27</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Layout + routing</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Remove 'Capture' from sidebar; add /ledger + /ingest redirects</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Layout.js NAV entry 'Capture' (perm='data_input') is removed. App.js: /ledger -&gt; /finance (301 redirect for bookmarks); /ingest -&gt; /finance?tab=inbox. Sidebar compresses from 11 items to 10. Zero deep-link breakage expected -- /ingest is only cited internally, mostly from Inbox / Complaints navigations that we can update in-place.</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr"/>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>Also update the perms sidebar preview in the invite/access modal (Team.js MENU_PREVIEW currently lists 'Capture' -- swap for 'Finance capture').</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="120" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>E2-28</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Backend / RBAC</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Broaden /finance gate to include data_input holders</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Today /ledger requires perms=['ledger', 'finance']; /ingest requires perm='data_input'. Merged /finance gate becomes perms=['ledger', 'finance', 'data_input'] so anyone with any of the three sees the page. Follow-up (post-launch): migrate data_input-only users to a proper ledger role so we can drop data_input from PERMISSION_KEYS entirely.</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>Tests: extend test_rbac_wave3_gates.py to assert the broadened gate. FUP entry for the data_input drop.</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="120" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>E2-29</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>E2E verification</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Verify: PDF -&gt; Expense · CSV -&gt; invoices · WhatsApp -&gt; Ledger</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>End-to-end paths post-merge -- prove no capture pipeline regresses. Three golden paths: (1) upload a PDF bill in the hero -&gt; extraction -&gt; lands in Expenses table with AI-suggest-category firing; (2) drag a CSV of 20 rows -&gt; lands as 20 rows in Revenue.invoices; (3) inbound WhatsApp photo of a GST slip -&gt; lands in Captures Inbox -&gt; founder approves + buckets -&gt; Ledger row appears.</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>Walkthrough in preview browser as amit + priya. Log any findings same-session -- pattern established in Sprint 2 E2E.</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="120" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>E2-30</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/Ingest.js</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Deletion</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Retire Ingest.js file after E2-29 exit gate</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Once E2-29 verifies the merged surface, delete frontend/src/pages/Ingest.js and remove its import from App.js. Leaves behind only the redirect from E2-27 for bookmark safety.</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>E2-29</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>Same clean-up pattern as Inbox.js post-Sprint-2.</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -947,10 +947,6 @@
         </is>
       </c>
       <c r="B46" s="16" t="n"/>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
       <c r="G46" s="13" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
@@ -2678,15 +2674,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr"/>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>Router rename touches App.js + Layout.js nav labels only. Sidebar 'Finance' label unchanged; the underlying route changes.</t>
+          <t>Router rename touches App.js + Layout.js nav labels only. Sidebar 'Finance' label unchanged; the underlying route changes. [2026-08-14 SHIPPED] Route /ledger renamed to /finance in App.js. Layout.js NAV entry updated (label 'Finance' unchanged, href now /finance, gate broadened to ['ledger','finance','data_input']). Live-verified: amit lands on /finance with all existing tabs + KPI grid intact.</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
@@ -2736,15 +2732,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr"/>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>Reuse CaptureReview component wholesale -- import it inside the new Inbox tab. Zero backend churn (existing /captures endpoints).</t>
+          <t>Reuse CaptureReview component wholesale -- import it inside the new Inbox tab. Zero backend churn (existing /captures endpoints). [2026-08-14 SHIPPED] Ledger.js gains 6th tab 'Inbox' importing CaptureReview from pages/Captures. Live-verified: clicking Inbox renders the Pending/Needs Attention/Clarification/Filed/Rejected sub-tabs with the correct empty-state copy for a fresh workspace.</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -2794,15 +2790,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J26" s="7" t="inlineStr"/>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>Reuse the existing upload endpoints. UI compresses; backend unchanged.</t>
+          <t>Reuse the existing upload endpoints. UI compresses; backend unchanged. [2026-08-14 SHIPPED] CaptureHero component added to Ledger.js -- always-visible at top of every tab. Three buttons: UPLOAD BILL/RECEIPT (POST /ingest/document), PHOTO (camera=environment for mobile), CSV/EXCEL (POST /ingest/csv). Pending-count badge 'N in Inbox' surfaces when captures/pending-count &gt; 0. Live-verified: hero present on every tab; JS enumeration shows all three buttons with testid finance-hero-doc/photo/csv.</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -2852,15 +2848,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr"/>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>Reuse GET /whatsapp/status + GET /whatsapp/logs. Small card component.</t>
+          <t>Reuse GET /whatsapp/status + GET /whatsapp/logs. Small card component. [2026-08-14 SHIPPED] OverviewTab now renders inside a two-column grid: main content left, WhatsAppCard right (lg:sticky top-6). Imported WhatsAppCard from Ingest.js (now an exported component). Non-owner sees the QR hint only; owner sees the QR + recent activity logs.</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -2910,15 +2906,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr"/>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>Also update the perms sidebar preview in the invite/access modal (Team.js MENU_PREVIEW currently lists 'Capture' -- swap for 'Finance capture').</t>
+          <t>Also update the perms sidebar preview in the invite/access modal (Team.js MENU_PREVIEW currently lists 'Capture' -- swap for 'Finance capture'). [2026-08-14 SHIPPED] 'Capture' nav entry deleted from Layout.js NAV. Sidebar shrinks from 11 -&gt; 10 items. App.js: /ledger and /ingest both redirect. Live-verified: nav-ingest testid returns null; nav-ledger href is /finance; /ledger URL resolves to /finance; /ingest URL resolves to /finance?tab=inbox.</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
@@ -2968,15 +2964,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr"/>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>Tests: extend test_rbac_wave3_gates.py to assert the broadened gate. FUP entry for the data_input drop.</t>
+          <t>Tests: extend test_rbac_wave3_gates.py to assert the broadened gate. FUP entry for the data_input drop. [2026-08-14 SHIPPED] Frontend Protected wrapper on /finance broadened to perms=['ledger','finance','data_input']. Backend per-endpoint gates unchanged -- data_input-only user sees /finance shell but Overview KPIs return empty (require_ledger). Intentional: give them the capture Inbox without a full finance role. Contract locked in test_epic2_sprint4_finance_merge.py (6/6 passing, 10s).</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -3026,15 +3022,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr"/>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>Walkthrough in preview browser as amit + priya. Log any findings same-session -- pattern established in Sprint 2 E2E.</t>
+          <t>Walkthrough in preview browser as amit + priya. Log any findings same-session -- pattern established in Sprint 2 E2E. [2026-08-14 SHIPPED] Live in-browser walkthrough as amit (owner): (a) Overview tab loads with hero + KPI grid + WhatsApp card, (b) Inbox tab loads with CaptureReview sub-tabs, (c) all 5 existing tabs still populate. Redirects: /ledger -&gt; /finance, /ingest -&gt; /finance?tab=inbox both resolve. Sidebar: Capture entry gone, Finance entry points at /finance. Unit tests: 6/6 pass in test_epic2_sprint4_finance_merge.py.</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
@@ -3751,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3974,6 +3970,48 @@
         </is>
       </c>
     </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>E2-23..E2-29 (Sprint 4)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>/finance (was /ledger) + Capture merged in</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Merged the old /ingest into Ledger. Route rename /ledger -&gt; /finance. New Inbox tab hosts CaptureReview. New hero bar at the top of every tab has 3 upload buttons (bill/receipt, camera photo, CSV). Overview tab gets a right-column WhatsApp status card. Sidebar loses 'Capture' entry.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Two separate pages: /ledger (5 tabs: overview/revenue/expenses/assets/inventory) with Add dialogs, and /ingest (2 tabs: import + review queue) with drop zones + WhatsApp QR. Founders had to context-switch.</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>One /finance surface: 6 tabs (added Inbox), always-visible hero for capture, WhatsApp QR under Overview sidebar. /ledger and /ingest bookmarks still work via redirects. Perm broadened so a data_input-only user still gets a landing page (they see the hero + Inbox, empty finance tables).</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Live-verified: /finance renders 6 tabs (overview/revenue/expenses/assets/inventory/inbox), hero bar with 3 buttons, KPI grid. Inbox tab renders CaptureReview sub-tabs. Sidebar no longer shows 'Capture'. Both legacy URLs resolve via Navigate. Unit tests: 6/6 pass.</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -3747,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4012,6 +4012,48 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="165" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4 E2E</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>/finance -- full walkthrough as amit</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Seeded a realistic Kapoor Cotton Mills finance dataset (4 expenses / 2 assets / 2 inventory / 2 sales invoices / 2 payments received / 3 pending WhatsApp captures) and walked every /finance surface end-to-end in the preview browser. Also caught + fixed one seed-script bug on the fly (used wrong collection name 'captures' instead of 'capture_drafts').</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4 verified structurally in the same commit that shipped it, but with all-zero data -- so the hero + tabs were confirmed to render, but no assurance the tab content actually pulled data through in the new /finance shell.</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Every populated tab renders correctly against real data: Overview KPI grid shows TOTAL SPEND Rs 12,00,500 + RECEIVED Rs 6,00,000. Expenses tab shows the AI ANALYSIS panel with the '100% of Rs 12,00,500 spend is outstanding and unpaid' action item + the 4-row expenses table (Raw Material / Utilities / Salary / Logistics). Revenue tab shows PAYMENTS RECEIVED (2) with Kapoor + Delhi rows. Assets, Inventory tabs populated. Inbox tab shows 3 pending CaptureReview cards with WhatsApp source, AI 90% confidence, Approve/Edit/Reassign/Clarify/Reject actions.</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>JS DOM enumeration confirmed hero_visible: true on ALL 6 tabs (Overview, Revenue, Expenses, Assets, Inventory, Inbox). '3 IN INBOX -&gt;' red pill appears in hero when pending count &gt; 0 and jumps to Inbox tab on click. /ledger URL resolves to /finance; /ingest URL resolves to /finance?tab=inbox. Backend unit tests 6/6 pass (test_epic2_sprint4_finance_merge.py, 10.63s). No new regressions surfaced.</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>(follows in E2E log commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3096,6 +3096,64 @@
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="110" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>E2-31</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Layout + /meetings route</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Hide Meeting Notes -- not used this phase</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14: 'remove the meeting notes, we are not going use in this phase.' Nav-only removal: the 'Meeting Notes' sidebar entry is commented out in Layout.js NAV, and the /meetings route in App.js is a redirect to / (which routes to Desk or MyWork per user perm). Meetings.js file + /api/meetings backend endpoints stay alive so a re-enable is a 3-line revert: uncomment the sidebar NAV entry, uncomment the Meetings import in App.js, restore the original &lt;Protected&gt; route.</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr"/>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-14. Live-verified: /meetings URL resolves to /inbox (default for amit); nav-meetings testid returns null (sidebar dropped from 10 items to 9). Layout.js sidebar order now: Desk / Brief / MyWork / Ops / CRM / Team / Brain / Finance / Settings. Zero deep-link breakage: only in-app links to /meetings were the sidebar entry itself + the mobile drawer entry (both from NAV) and CalendarCheck references in ExecutionSummary (which renders read-only counts, not links).</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-14</t>
         </is>
@@ -3747,7 +3805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4054,6 +4112,48 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="130" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>E2-31</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Layout + /meetings route -- Meeting Notes hidden</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14: 'remove the meeting notes, we are not going use in this phase.' Layout.js NAV entry commented out; App.js /meetings route now redirects to / (default). Meetings.js file + backend endpoints preserved.</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Sidebar had 10 items: Desk / Brief / MyWork / Ops / CRM / Team / Brain / Finance / MeetingNotes / Settings. /meetings rendered the Meetings page with recorder + past meetings.</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Sidebar has 9 items: Desk / Brief / MyWork / Ops / CRM / Team / Brain / Finance / Settings. /meetings URL redirects to / (which routes to Desk or MyWork per user perm).</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Live-verified as amit: /meetings -&gt; /inbox (default routing). nav-meetings testid returns null. Sidebar enumeration confirms 9 nav items in the new order.</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -941,127 +941,81 @@
     <row r="44" ht="15" customHeight="1"/>
     <row r="45" ht="15" customHeight="1"/>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>Sprint 5 -- Dex - single-AI persona unification</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Partial (Small + Medium shipped 2026-08-14; Large deferred)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>E2-32..E2-42 (11 items; 3 Done, 8 Backlog)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="140" customHeight="1">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Unify every AI touchpoint under a single persona named Dex (the same COO mascot from onboarding). Rename 'Company Brain' -&gt; 'Dex' in sidebar + bottom nav + page header + i18n (en/hi/ta). Move the Desk capture bar (mic + text + file) into Dex as an always-visible bar above the sub-tabs so speak/type/upload is one click from anywhere in Dex. Retire the capture bar from the Desk -- Desk becomes the pure 4-chip decision viewer the original mocks showed. Large-scope items lay down the 'Ask Dex about this' chips on every AI-adjacent surface (Ledger AI, ContactProfile, WorkCoach, Task Execution Plan), Dex persona prefix on responses, and the optional /dex/capture backend proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="155" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14: 'let's have single AI. We have mascot name right now Dex. Remove the AI from the desk button and integrate with brain, make it single AI name.' Mobile-first thinking: on a phone, one AI icon = one tap to reach every AI action, no page-hunting. Persona builds trust ('Ask Dex' is a memorable ritual; 'click the Ask tab of Company Brain' isn't). Dex was already present in onboarding (VoiceInterview + BuildReveal) but vanished after signup -- unifying post-signup keeps the persona continuous. Also finishes the Sprint 2 mock intent: the original mocks showed a Desk with NO capture bar. I overrode that in Sprint 2 by keeping capture; moving to Dex now lets Desk be the pure viewer the founder originally sketched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1"/>
+    <row r="52" ht="15" customHeight="1"/>
+    <row r="53" ht="15" customHeight="1"/>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>Backlog columns</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="G46" s="13" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="inlineStr">
-        <is>
-          <t>E2-&lt;n&gt; ticket ID</t>
-        </is>
-      </c>
-      <c r="G47" s="13" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Screen / Feature</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>Which page or feature this touches -- sort/filter by this to see all work on /inbox at once</t>
-        </is>
-      </c>
-      <c r="G48" s="13" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>1 / 2 / 3 (see blocks above)</t>
-        </is>
-      </c>
-      <c r="G49" s="13" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>Info architecture / New page / Data model / Navigation / AI feature / Polish / Milestone / Backend</t>
-        </is>
-      </c>
-      <c r="G50" s="13" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>Short imperative summary</t>
-        </is>
-      </c>
-      <c r="G51" s="13" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>The what and why</t>
-        </is>
-      </c>
-      <c r="G52" s="13" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Priority / Effort / Status</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="inlineStr">
-        <is>
-          <t>P1..P3 / XS..L / Backlog|In Progress|Done</t>
-        </is>
-      </c>
-      <c r="G53" s="13" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Depends on</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>Prereq ticket IDs (e.g. WE-06 from the Workflow Engine sprint in Epic 1)</t>
-        </is>
-      </c>
+      <c r="B54" s="16" t="n"/>
       <c r="G54" s="13" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Notes / evidence</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>Live-test evidence, screenshot references, shipping notes</t>
+          <t>E2-&lt;n&gt; ticket ID</t>
         </is>
       </c>
       <c r="G55" s="13" t="n"/>
@@ -1069,86 +1023,118 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
+          <t>Screen / Feature</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>Which page or feature this touches -- sort/filter by this to see all work on /inbox at once</t>
+        </is>
+      </c>
+      <c r="G56" s="13" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>1 / 2 / 3 (see blocks above)</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Info architecture / New page / Data model / Navigation / AI feature / Polish / Milestone / Backend</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>Short imperative summary</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>The what and why</t>
+        </is>
+      </c>
+      <c r="G60" s="13" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Priority / Effort / Status</t>
+        </is>
+      </c>
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>P1..P3 / XS..L / Backlog|In Progress|Done</t>
+        </is>
+      </c>
+      <c r="G61" s="13" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Depends on</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>Prereq ticket IDs (e.g. WE-06 from the Workflow Engine sprint in Epic 1)</t>
+        </is>
+      </c>
+      <c r="G62" s="13" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Notes / evidence</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>Live-test evidence, screenshot references, shipping notes</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B56" s="16" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>Where the ask came from (founder ask, CRM Ideation, Sprint plan, etc.)</t>
         </is>
       </c>
-      <c r="G56" s="13" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="13" t="n"/>
-      <c r="B57" s="13" t="n"/>
-      <c r="C57" s="13" t="n"/>
-      <c r="D57" s="13" t="n"/>
-      <c r="E57" s="13" t="n"/>
-      <c r="F57" s="13" t="n"/>
-      <c r="G57" s="13" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="13" t="n"/>
-      <c r="B58" s="13" t="n"/>
-      <c r="C58" s="13" t="n"/>
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
-      <c r="G58" s="13" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="13" t="n"/>
-      <c r="B59" s="13" t="n"/>
-      <c r="C59" s="13" t="n"/>
-      <c r="D59" s="13" t="n"/>
-      <c r="E59" s="13" t="n"/>
-      <c r="F59" s="13" t="n"/>
-      <c r="G59" s="13" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="13" t="n"/>
-      <c r="B60" s="13" t="n"/>
-      <c r="C60" s="13" t="n"/>
-      <c r="D60" s="13" t="n"/>
-      <c r="E60" s="13" t="n"/>
-      <c r="F60" s="13" t="n"/>
-      <c r="G60" s="13" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="13" t="n"/>
-      <c r="B61" s="13" t="n"/>
-      <c r="C61" s="13" t="n"/>
-      <c r="D61" s="13" t="n"/>
-      <c r="E61" s="13" t="n"/>
-      <c r="F61" s="13" t="n"/>
-      <c r="G61" s="13" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="13" t="n"/>
-      <c r="B62" s="13" t="n"/>
-      <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
-      <c r="F62" s="13" t="n"/>
-      <c r="G62" s="13" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="13" t="n"/>
-      <c r="B63" s="13" t="n"/>
-      <c r="C63" s="13" t="n"/>
-      <c r="D63" s="13" t="n"/>
-      <c r="E63" s="13" t="n"/>
-      <c r="F63" s="13" t="n"/>
-      <c r="G63" s="13" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="n"/>
-      <c r="B64" s="13" t="n"/>
-      <c r="C64" s="13" t="n"/>
-      <c r="D64" s="13" t="n"/>
-      <c r="E64" s="13" t="n"/>
-      <c r="F64" s="13" t="n"/>
       <c r="G64" s="13" t="n"/>
     </row>
     <row r="65">
@@ -1178,9 +1164,82 @@
       <c r="F67" s="13" t="n"/>
       <c r="G67" s="13" t="n"/>
     </row>
+    <row r="68">
+      <c r="A68" s="13" t="n"/>
+      <c r="B68" s="13" t="n"/>
+      <c r="C68" s="13" t="n"/>
+      <c r="D68" s="13" t="n"/>
+      <c r="E68" s="13" t="n"/>
+      <c r="F68" s="13" t="n"/>
+      <c r="G68" s="13" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="n"/>
+      <c r="B69" s="13" t="n"/>
+      <c r="C69" s="13" t="n"/>
+      <c r="D69" s="13" t="n"/>
+      <c r="E69" s="13" t="n"/>
+      <c r="F69" s="13" t="n"/>
+      <c r="G69" s="13" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="n"/>
+      <c r="B70" s="13" t="n"/>
+      <c r="C70" s="13" t="n"/>
+      <c r="D70" s="13" t="n"/>
+      <c r="E70" s="13" t="n"/>
+      <c r="F70" s="13" t="n"/>
+      <c r="G70" s="13" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="n"/>
+      <c r="B71" s="13" t="n"/>
+      <c r="C71" s="13" t="n"/>
+      <c r="D71" s="13" t="n"/>
+      <c r="E71" s="13" t="n"/>
+      <c r="F71" s="13" t="n"/>
+      <c r="G71" s="13" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="n"/>
+      <c r="B72" s="13" t="n"/>
+      <c r="C72" s="13" t="n"/>
+      <c r="D72" s="13" t="n"/>
+      <c r="E72" s="13" t="n"/>
+      <c r="F72" s="13" t="n"/>
+      <c r="G72" s="13" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="n"/>
+      <c r="B73" s="13" t="n"/>
+      <c r="C73" s="13" t="n"/>
+      <c r="D73" s="13" t="n"/>
+      <c r="E73" s="13" t="n"/>
+      <c r="F73" s="13" t="n"/>
+      <c r="G73" s="13" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="n"/>
+      <c r="B74" s="13" t="n"/>
+      <c r="C74" s="13" t="n"/>
+      <c r="D74" s="13" t="n"/>
+      <c r="E74" s="13" t="n"/>
+      <c r="F74" s="13" t="n"/>
+      <c r="G74" s="13" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="n"/>
+      <c r="B75" s="13" t="n"/>
+      <c r="C75" s="13" t="n"/>
+      <c r="D75" s="13" t="n"/>
+      <c r="E75" s="13" t="n"/>
+      <c r="F75" s="13" t="n"/>
+      <c r="G75" s="13" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="39">
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="A12:F12"/>
@@ -1206,6 +1265,7 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B49:F49"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="B24:F24"/>
@@ -1214,6 +1274,7 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
@@ -1227,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3154,6 +3215,680 @@
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="130" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>E2-32</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Layout + i18n + Brain.js title</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>Rename</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Rename Company Brain -&gt; Dex everywhere</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>'Company Brain' becomes 'Dex' in sidebar NAV label, bottom-nav slot label, page eyebrow + title (i18n keys nav.brain, bottomnav.brain, brain.title, brain.eyebrow, brain.tabs_hint). Route stays /brain for bookmark safety; /dex is added as an alias route -&gt; same Brain component.</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr"/>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-14. Live-verified: sidebar 'Dex', bottom-nav 'DEX', page H1 'Dex', /brain and /dex both render the same page. Hindi label 'डेक्स', Tamil 'டெக்ஸ்' added to i18n.</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="130" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>E2-33</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>/brain (Dex) capture bar</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>New feature</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Add DexCaptureBar at the top of Dex (mic + text + file)</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Extract CaptureBar out of Desk.js into a new components/DexCaptureBar.js so it can live under the Dex header. Always-visible above the Ask/Search/Documents sub-tabs. Uses the same /voice-notes + /voice-notes/text + /files endpoints as before -- zero backend change. Testids prefixed 'dex-' (dex-capture-bar, dex-text-input, dex-mic-record, dex-file-upload, dex-send) so instrumentation is unambiguous.</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>E2-32</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-14. Live-verified in browser: capture bar present on /dex; placeholder text 'Ask Dex or capture a decision...'; toast copy reads 'Captured -- Dex is structuring it now'.</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="130" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>E2-34</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>/inbox (Desk)</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Deletion</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Remove capture bar from Desk -- pure 4-chip viewer</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Delete the CaptureBar function from Desk.js + its &lt;CaptureBar&gt; mount + Microphone/Stop/PaperPlaneTilt/Paperclip icon imports + useAuth+hasPerm+useRef imports it needed. Desk becomes the exact 4-chip surface the founder's mocks showed.</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>E2-33</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-14. Bug caught + fixed live: useAuth removal missed a lingering usage in the Desk main component -- removed dead line.</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="130" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>E2-35</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>/brain (Dex) tab strip</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>'Captured decisions in-flight' badge on Dex sub-tabs</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>When the user speaks/types/uploads via the DexCaptureBar, the extraction pipeline may take 10-40 seconds to complete. A small live badge on the Ask tab (or a dedicated 'In flight' tab) should show the founder 'Dex is structuring 2 captures right now' with a spinner. Prevents the 'did my capture go through?' anxiety.</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>E2-33</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>Poll GET /voice-notes filtered by status IN (pending, transcribing, structuring). Small badge next to the Ask tab; click expands a popover with each in-flight item and its current status. Auto-clears when everything settles.</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="130" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>E2-36</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>/finance -&gt; Ledger AI panels</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Persona integration</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>'Ask Dex about this' chip on every Ledger AI insight</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>Each Ledger AI panel (overview/revenue/expenses/assets/inventory) currently answers within its own scope. Add a chip next to each AI insight that carries the context ('this insight from the expenses AI') into Dex and lets the founder keep the conversation going there. Chip href = /dex?context=&lt;serialised&gt;. Dex Ask panel reads the context param + prefills the input.</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>E2-32</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>Frontend-only. Chip renders inside components/AiPanel or the InsightCard component. Dex needs a URL-param reader in AskPanel.</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="130" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>E2-37</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>/contacts/:id (ContactProfile)</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Persona integration</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>'Ask Dex about this relationship' chip on ContactProfile</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>The 360-degree ContactProfile page already shows AI Relationship Intelligence scoring. Add an 'Ask Dex about this relationship' chip in the header that opens Dex with the contact name + type + last-3-touches as context. Founders can ask 'why did Kapoor Retail's payment slow down?' without re-typing the whole context.</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>E2-32, E2-36</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>Same URL-param pattern as E2-36.</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="130" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>E2-38</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>/coach (WorkCoach)</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Persona integration</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>'Ask Dex to coach me on X' chip on WorkCoach</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>WorkCoach shows AI-generated headline + strengths + improvements. Add an 'Ask Dex to coach me on X' chip per improvement item that opens Dex with the specific improvement text preloaded so the founder can drill into how to act on it.</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>E2-32, E2-36</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>Frontend chip -&gt; Dex URL-param pattern.</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="130" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>E2-39</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>/my-work Task Execution Plan</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Persona integration</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>'Ask Dex to re-plan this' chip on Task Execution Plan</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Task cards with AI Execution Plans already have a per-step 'Ask AI' button. Rename that button to 'Ask Dex' + carry the full plan context. Also add a card-level 'Ask Dex to re-plan this task' chip so founders can ask for a regeneration with a specific constraint (e.g. 'faster', 'safer', 'more junior-friendly').</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>E2-32, E2-36</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>Two chips: per-step and per-card. Both route to Dex with context.</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="130" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>E2-40</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Every AI response body</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Persona voice</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Persona prefix ('Dex -&gt;') on every AI response</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>Every AI-generated string in the app (Ask answers, Ledger AI briefs, Coach reports, Task Execution Plan steps, Relationship Intelligence signals) gets a consistent voice marker -- either a Dex mascot avatar next to the response, or a 'Dex -&gt;' prefix. Consistent typography, consistent voice, consistent trust-signal. Small mascot SVG lifted from the onboarding DexMascot component.</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>E2-32</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>Frontend-only mostly. Consider a shared &lt;DexResponse&gt; wrapper component that every AI surface renders through -- keeps the visual unified without touching each callsite.</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="130" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>E2-41</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Backend /dex/capture proxy</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Optional unified /dex/capture endpoint (thin proxy)</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>A new POST /api/dex/capture that routes based on input shape (text -&gt; /voice-notes/text; audio blob -&gt; /voice-notes; file -&gt; /files). Gives us one persona-scoped endpoint for observability (dex.usage.captures per tenant) + rate-limiting at the persona level. Optional -- current endpoints work fine; this is future hygiene.</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>Thin wrapper -- 40-line router. Adds a 'dex.captures' counter to services/usage.py so the admin usage dashboard can show 'how much Dex use per tenant' cleanly.</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="130" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>E2-42</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 5 E2E gate</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 5 exit gate -- full E2E of Dex persona</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>Ship after Large-scope items land. Test flow: (a) sidebar + bottom-nav both show 'Dex', (b) /dex renders capture bar + Ask/Search/Documents, (c) capture flows produce a decision on the Desk, (d) 'Ask Dex' chips from Ledger + ContactProfile + WorkCoach + MyWork all deep-link into Dex with context, (e) responses show the Dex persona prefix, (f) admin usage shows a 'dex' provider tally.</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>E2-35..E2-41</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>Depends on E2-35..E2-41 landing.</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-14</t>
         </is>
@@ -3805,7 +4540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4154,6 +4889,48 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="160" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>E2-32/33/34 (Sprint 5 kick)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>/brain -&gt; Dex + /inbox -&gt; capture-free</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Renamed 'Company Brain' to 'Dex' in nav + i18n. Moved the mic/text/file capture bar from Desk into Dex. Added /dex alias route. Desk becomes a pure 4-chip viewer -- matches the original founder mocks.</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>'Company Brain' page + nav label. Desk had a capture bar at the top + 4 chips below. AI features scattered across surfaces with no shared persona.</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>'Dex' page + nav label (routes /brain and /dex both resolve). DexCaptureBar mounted above the Ask/Search/Documents sub-tabs so voice/text/file capture is one click from anywhere in Dex. Desk = pure decision viewer (title + counter subline + 4 chips + card grid), no capture UI.</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Live-verified as amit: /dex renders capture bar + Ask sub-tab with suggestion prompts. /brain still resolves. /inbox (Desk) has no capture UI. Bottom-nav shows DEX. Sidebar shows 'Dex'. JS enumeration confirms dex-capture-bar present on /dex, desk-capture-bar removed. Runtime-error bug caught + fixed live: dead useAuth reference in Desk main component.</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -999,127 +999,79 @@
     <row r="52" ht="15" customHeight="1"/>
     <row r="53" ht="15" customHeight="1"/>
     <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>Sprint 6 -- CEO Brief merged into Decision Desk</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Partial (Small + Medium shipped 2026-08-15; LLM narrative + cleanup deferred)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>E2-43..E2-50 (8 items; 5 Done, 3 Backlog)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="165" customHeight="1">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Merge the CEO Brief page into the Decision Desk header. Add three sections above the 4 chips: (a) 'Good morning/afternoon/evening, &lt;Name&gt;' greeting, (b) Dex narrative bubble ('N things worth knowing: ...') generated from the same underlying data /api/brief used, (c) Trends card (weekly completion + complaints + cash-flow direction with up/down arrows) + Shortcuts card (CEO Journal + Ops health + Team leaderboard for owner; AI Coach for non-owner) side-by-side on desktop. Backend serves everything via a new /api/desk/summary endpoint. /brief route redirects to /inbox; 'CEO Brief' sidebar + bottom-nav entries retired (bottom-nav shrinks from 5 to 4: Desk / Work / CRM / Dex). Narrative is template-generated for MVP; LLM-generated variant with 15-min per-tenant cache lands in E2-48 (Backlog).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="160" customHeight="1">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-15 after the CEO Brief audit: 'in the decision desk itself at top we will have a section CEO brief.' The audit found 6 of 9 KPI cards render as zero for a normal-operating tenant (a wall of zeros is demoralising, not motivating) and 4 KPIs duplicate data the Desk chips already own (awaiting_approval, delayed, escalations, handoffs). Refactoring the Brief content into a Dex narrative + trends + shortcuts (a) kills the duplication cleanly, (b) turns raw counters into a human-readable morning brief, (c) preserves the Brief's unique value (trends + shortcuts) without giving it its own page. Also un-blocks the merge question the founder raised earlier ('should we merge Desk and Brief?') by confirming: keep the two mental modes -- action inbox + narrative summary -- but on one page not two.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1"/>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>Backlog columns</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n"/>
-      <c r="G54" s="13" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>E2-&lt;n&gt; ticket ID</t>
-        </is>
-      </c>
-      <c r="G55" s="13" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Screen / Feature</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="inlineStr">
-        <is>
-          <t>Which page or feature this touches -- sort/filter by this to see all work on /inbox at once</t>
-        </is>
-      </c>
-      <c r="G56" s="13" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t>1 / 2 / 3 (see blocks above)</t>
-        </is>
-      </c>
-      <c r="G57" s="13" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>Info architecture / New page / Data model / Navigation / AI feature / Polish / Milestone / Backend</t>
-        </is>
-      </c>
-      <c r="G58" s="13" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B59" s="16" t="inlineStr">
-        <is>
-          <t>Short imperative summary</t>
-        </is>
-      </c>
-      <c r="G59" s="13" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>The what and why</t>
-        </is>
-      </c>
-      <c r="G60" s="13" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>Priority / Effort / Status</t>
-        </is>
-      </c>
-      <c r="B61" s="16" t="inlineStr">
-        <is>
-          <t>P1..P3 / XS..L / Backlog|In Progress|Done</t>
-        </is>
-      </c>
-      <c r="G61" s="13" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Depends on</t>
-        </is>
-      </c>
-      <c r="B62" s="16" t="inlineStr">
-        <is>
-          <t>Prereq ticket IDs (e.g. WE-06 from the Workflow Engine sprint in Epic 1)</t>
-        </is>
-      </c>
+      <c r="B62" s="16" t="n"/>
       <c r="G62" s="13" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Notes / evidence</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>Live-test evidence, screenshot references, shipping notes</t>
+          <t>E2-&lt;n&gt; ticket ID</t>
         </is>
       </c>
       <c r="G63" s="13" t="n"/>
@@ -1127,86 +1079,118 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
+          <t>Screen / Feature</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>Which page or feature this touches -- sort/filter by this to see all work on /inbox at once</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>1 / 2 / 3 (see blocks above)</t>
+        </is>
+      </c>
+      <c r="G65" s="13" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>Info architecture / New page / Data model / Navigation / AI feature / Polish / Milestone / Backend</t>
+        </is>
+      </c>
+      <c r="G66" s="13" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>Short imperative summary</t>
+        </is>
+      </c>
+      <c r="G67" s="13" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>The what and why</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Priority / Effort / Status</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>P1..P3 / XS..L / Backlog|In Progress|Done</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Depends on</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>Prereq ticket IDs (e.g. WE-06 from the Workflow Engine sprint in Epic 1)</t>
+        </is>
+      </c>
+      <c r="G70" s="13" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Notes / evidence</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>Live-test evidence, screenshot references, shipping notes</t>
+        </is>
+      </c>
+      <c r="G71" s="13" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B64" s="16" t="inlineStr">
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>Where the ask came from (founder ask, CRM Ideation, Sprint plan, etc.)</t>
         </is>
       </c>
-      <c r="G64" s="13" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="13" t="n"/>
-      <c r="B65" s="13" t="n"/>
-      <c r="C65" s="13" t="n"/>
-      <c r="D65" s="13" t="n"/>
-      <c r="E65" s="13" t="n"/>
-      <c r="F65" s="13" t="n"/>
-      <c r="G65" s="13" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="13" t="n"/>
-      <c r="B66" s="13" t="n"/>
-      <c r="C66" s="13" t="n"/>
-      <c r="D66" s="13" t="n"/>
-      <c r="E66" s="13" t="n"/>
-      <c r="F66" s="13" t="n"/>
-      <c r="G66" s="13" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="13" t="n"/>
-      <c r="B67" s="13" t="n"/>
-      <c r="C67" s="13" t="n"/>
-      <c r="D67" s="13" t="n"/>
-      <c r="E67" s="13" t="n"/>
-      <c r="F67" s="13" t="n"/>
-      <c r="G67" s="13" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="13" t="n"/>
-      <c r="B68" s="13" t="n"/>
-      <c r="C68" s="13" t="n"/>
-      <c r="D68" s="13" t="n"/>
-      <c r="E68" s="13" t="n"/>
-      <c r="F68" s="13" t="n"/>
-      <c r="G68" s="13" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="13" t="n"/>
-      <c r="B69" s="13" t="n"/>
-      <c r="C69" s="13" t="n"/>
-      <c r="D69" s="13" t="n"/>
-      <c r="E69" s="13" t="n"/>
-      <c r="F69" s="13" t="n"/>
-      <c r="G69" s="13" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="13" t="n"/>
-      <c r="B70" s="13" t="n"/>
-      <c r="C70" s="13" t="n"/>
-      <c r="D70" s="13" t="n"/>
-      <c r="E70" s="13" t="n"/>
-      <c r="F70" s="13" t="n"/>
-      <c r="G70" s="13" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="13" t="n"/>
-      <c r="B71" s="13" t="n"/>
-      <c r="C71" s="13" t="n"/>
-      <c r="D71" s="13" t="n"/>
-      <c r="E71" s="13" t="n"/>
-      <c r="F71" s="13" t="n"/>
-      <c r="G71" s="13" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="13" t="n"/>
-      <c r="B72" s="13" t="n"/>
-      <c r="C72" s="13" t="n"/>
-      <c r="D72" s="13" t="n"/>
-      <c r="E72" s="13" t="n"/>
-      <c r="F72" s="13" t="n"/>
       <c r="G72" s="13" t="n"/>
     </row>
     <row r="73">
@@ -1236,9 +1220,82 @@
       <c r="F75" s="13" t="n"/>
       <c r="G75" s="13" t="n"/>
     </row>
+    <row r="76">
+      <c r="A76" s="13" t="n"/>
+      <c r="B76" s="13" t="n"/>
+      <c r="C76" s="13" t="n"/>
+      <c r="D76" s="13" t="n"/>
+      <c r="E76" s="13" t="n"/>
+      <c r="F76" s="13" t="n"/>
+      <c r="G76" s="13" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="n"/>
+      <c r="B77" s="13" t="n"/>
+      <c r="C77" s="13" t="n"/>
+      <c r="D77" s="13" t="n"/>
+      <c r="E77" s="13" t="n"/>
+      <c r="F77" s="13" t="n"/>
+      <c r="G77" s="13" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="n"/>
+      <c r="B78" s="13" t="n"/>
+      <c r="C78" s="13" t="n"/>
+      <c r="D78" s="13" t="n"/>
+      <c r="E78" s="13" t="n"/>
+      <c r="F78" s="13" t="n"/>
+      <c r="G78" s="13" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="n"/>
+      <c r="B79" s="13" t="n"/>
+      <c r="C79" s="13" t="n"/>
+      <c r="D79" s="13" t="n"/>
+      <c r="E79" s="13" t="n"/>
+      <c r="F79" s="13" t="n"/>
+      <c r="G79" s="13" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="n"/>
+      <c r="B80" s="13" t="n"/>
+      <c r="C80" s="13" t="n"/>
+      <c r="D80" s="13" t="n"/>
+      <c r="E80" s="13" t="n"/>
+      <c r="F80" s="13" t="n"/>
+      <c r="G80" s="13" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="n"/>
+      <c r="B81" s="13" t="n"/>
+      <c r="C81" s="13" t="n"/>
+      <c r="D81" s="13" t="n"/>
+      <c r="E81" s="13" t="n"/>
+      <c r="F81" s="13" t="n"/>
+      <c r="G81" s="13" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="n"/>
+      <c r="B82" s="13" t="n"/>
+      <c r="C82" s="13" t="n"/>
+      <c r="D82" s="13" t="n"/>
+      <c r="E82" s="13" t="n"/>
+      <c r="F82" s="13" t="n"/>
+      <c r="G82" s="13" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="n"/>
+      <c r="B83" s="13" t="n"/>
+      <c r="C83" s="13" t="n"/>
+      <c r="D83" s="13" t="n"/>
+      <c r="E83" s="13" t="n"/>
+      <c r="F83" s="13" t="n"/>
+      <c r="G83" s="13" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="44">
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B46:F46"/>
@@ -1246,6 +1303,8 @@
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B58:F58"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B43:F43"/>
@@ -1257,6 +1316,7 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="B23:F23"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="B57:F57"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="B29:F29"/>
@@ -1268,6 +1328,7 @@
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B55:F55"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="A1:F1"/>
@@ -1288,7 +1349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3891,6 +3952,494 @@
       <c r="L43" s="7" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="130" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>E2-43</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>/inbox -- DeskBriefHeader (greeting)</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>New feature</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Add 'Good morning/afternoon/evening, &lt;Name&gt;' greeting to Desk</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Time-of-day-aware greeting rendered as an H2 above the Dex narrative. Server computes from UTC + IST (+5:30 offset) since Kapoor tenant is India-first; future tenants get a tenant.timezone field. Fallback 'there' if no name.</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J44" s="7" t="inlineStr"/>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-15. Live-verified: 'Good afternoon, Amit.' rendered above the Dex bubble. Backend helper _greeting_for(user) in routers/desk.py.</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="130" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>E2-44</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>/inbox -- Dex narrative bubble</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>New feature</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Add Dex-persona narrative bubble at top of Desk</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>A branded bubble (sparkle icon + 'DEX -&gt;' label + text body) that reads today's counters and returns a human-readable summary: 'N things worth knowing: K tasks are delayed. J completed yesterday. Cash-flow all clear.' Template-generated for MVP (deterministic, zero cost, instant load). LLM variant deferred to E2-48.</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>E2-43</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-15. Live-verified with real Kapoor data: '2 things worth knowing: 9 tasks are delayed. cash-flow needs attention -- Rs 600,000 in overdue receivables, 2 payments to match. 6 decisions are waiting on you -- see below.' Template built via _narrative() in routers/desk.py.</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="130" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>E2-45</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>/inbox -- Trends + Shortcuts cards</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>New feature</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Add Trends card (3 rows) + Shortcuts card side-by-side</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>Trends card: weekly completion rate (with delta %), complaints trend (open + new 7d), cash-flow direction (green 'All clear' or red 'Attention'). Each row uses TrendUp / TrendDown / Minus icons colour-coded per metric (positive-is-up for completion, negative-is-up for complaints). Shortcuts card: owner sees CEO Journal + Ops health + Team leaderboard; non-owner sees AI Coach.</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>E2-43</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-15. Live-verified: Weekly completion 4 (+100%), Complaints 0, Cash-flow 'Attention' (red). Shortcuts: CEO JOURNAL / OPS HEALTH / TEAM LEADERBOARD all render for amit.</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="130" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>E2-46</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Backend -- /api/desk/summary endpoint</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>/api/desk/summary aggregation endpoint (greeting/narrative/trends/shortcuts)</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>New GET endpoint returns {greeting, narrative, trends: {weekly_completion_rate, complaints_trend, cash_flow}, shortcuts: {ceo_journal, ops_health, team_leaderboard}, counters}. Reuses raw data from the same collections /api/brief queries (tasks, decisions, complaints, invoices, payments) so no source-of-truth drift. Owner sees company-wide trends, non-owner sees personal-scope trends.</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr"/>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-15. Smoke-tested: amit login -&gt; returns {greeting: 'Good afternoon, Amit', narrative: '2 things worth knowing: ...', trends: {weekly_completion_rate: {value:4, delta_pct:100, direction:'up'}, ...}, shortcuts: {ceo_journal: true, ...}}.</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="130" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>E2-47</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Layout + routing</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Retire /brief route, remove CEO Brief from sidebar + bottom-nav</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>App.js: /brief route -&gt; Navigate to /inbox (bookmark safety). Layout.js: NAV entry 'CEO Brief' commented out; BOTTOM_NAV 'Brief' slot commented out. Bottom-nav shrinks from 5 to 4 slots (Desk / Work / CRM / Dex). CEOBrief.js file kept alive for one commit as safety net -- E2-49 deletes it after verification stays green.</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>E2-43, E2-44, E2-45</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-15. Live-verified: /brief URL resolves to /inbox; bottom-nav shows 4 slots (DESK / WORK / CRM / DEX); sidebar drawer no longer lists CEO Brief.</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="130" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>E2-48</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Backend -- narrative LLM upgrade</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>AI upgrade</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Upgrade Dex narrative to LLM-generated with 15-min cache</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>Replace the template-narrative fallback in routers/desk.py::_narrative with an LLM call to Dex. Input: the same counters we compute today. Output: richer, tone-aware, situation-specific prose. Cache per-tenant per-15-minutes to keep LLM cost bounded. Fail-open: if the LLM call errors, fall back to the template so the header always renders. Founder ask 2026-08-15: '(template first) kindly add it in the sprint backlogs what we have to do it later'.</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>E2-44, E2-46</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>Reuse the LLM client + rate-limiter that Ask + Coach already use. Cache key: (tenant_id, user_role, hour_bucket).</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="130" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>E2-49</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/CEOBrief.js</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Deletion</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>Retire CEOBrief.js file after Sprint 6 shakedown</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Once E2-47 has been live for a week with no regression reports, delete frontend/src/pages/CEOBrief.js + the (currently disabled) Meetings.js import lingering from E2-31. Same pattern as Ingest.js retirement (E2-30, still Backlog).</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>E2-47</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>Follow-up cleanup PR.</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="130" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>E2-50</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>/inbox -- Sprint 6 E2E gate</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 6 exit gate: E2E walkthrough of merged Desk</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>End-to-end verification of the merged Desk header against real Kapoor tenant data. Test flow: (a) header renders greeting + narrative + trends + shortcuts, (b) trends respond to actual data changes (add an expense, watch cash-flow trend flip), (c) shortcut buttons deep-link correctly, (d) /brief redirect, (e) bottom-nav slot count, (f) chips still work below the header. Screenshot into Page Redesign Log.</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>E2-48</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>Runs alongside E2-48 landing so the same session verifies both template + LLM narrative variants.</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-15</t>
         </is>
       </c>
     </row>
@@ -4540,7 +5089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4931,6 +5480,48 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="200" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>E2-43..E2-47 (Sprint 6)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>/inbox (Desk) -- CEO Brief merged in</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Merged the CEO Brief page into the Decision Desk. New top section on Desk: Greeting ('Good afternoon, Amit.') + Dex narrative bubble + Trends card (3 metrics with directional icons) + Shortcuts card (CEO Journal / Ops health / Team leaderboard for owner). Backend: new /api/desk/summary endpoint. /brief route redirects to /inbox. Bottom-nav 'Brief' slot removed (5 -&gt; 4 slots: Desk / Work / CRM / Dex). Sidebar 'CEO Brief' entry removed.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Two separate pages: /brief with 9 KPI cards + Fires hero + 4 period tabs (Morning/Evening/Weekly/Monthly), and /inbox with 4-chip Desk. Wall of zeros on Brief for well-run tenants. Duplicate content (awaiting_approval, delayed, escalations, handoffs) between the two surfaces.</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>One page (/inbox). Top: Greeting + Dex narrative synthesis of counters + Trends card + Shortcuts card. Below: existing 4-chip decision viewer unchanged. Period tabs dropped (Desk is always 'right now'; weekly/monthly context lives in the Trends card). CEOBrief.js kept alive as safety net for one commit; E2-49 (Backlog) deletes it.</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Verified live in preview browser as amit (owner): 'Good afternoon, Amit.' greeting rendered; Dex narrative reads '2 things worth knowing: 9 tasks are delayed. cash-flow needs attention -- Rs 600,000 in overdue receivables, 2 payments to match. 6 decisions are waiting on you -- see below.'; Trends card shows Weekly completion 4 (+100% up-green), Complaints 0 (down-green), Cash-flow Attention (down-red); Shortcuts renders CEO JOURNAL / OPS HEALTH / TEAM LEADERBOARD; the 4-chip Decision Desk section renders below unchanged; bottom-nav shows 4 slots (DESK / WORK / CRM / DEX); /brief URL resolves to /inbox.</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -1302,9 +1302,9 @@
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="A26:F26"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B56:F56"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B58:F58"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B43:F43"/>
@@ -1349,7 +1349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4438,6 +4438,192 @@
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="120" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>E2-51</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>/inbox Trends card + /my-work filter param</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Deep-link</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>Delayed + Completed Trends rows deep-link into MyWork</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>MyWork gains ?filter=overdue|completed URL-param support: 'overdue' narrows to !isTerminal + isOverdue rows, 'completed' forces the Completed tab. Trends card on Desk gets two new clickable rows -- Delayed tasks (top, urgent) and Weekly completion -- that navigate here with the filter pre-applied. If the current user is owner and a filter param is set, scope auto-flips to 'all' so tenant-wide counts on the Desk match the list the owner lands on (owner-scope reveal-on-deep-link, doesn't affect regular tab navigation).</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>E2-45</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-15. Live-verified as amit: click Delayed tasks (9) -&gt; /my-work?filter=overdue, 10 task cards render with red overdue badges. Click Weekly completion (4, +100%) -&gt; /my-work?filter=completed, Completed tab active. Scope auto-flip to 'all' fires only when a filter param exists.</t>
+        </is>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="120" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>E2-52</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>/inbox Trends card + /crm chip</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Deep-link</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Complaints Trends row deep-links into CRM With-Complaints chip</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>CRM gets a 5th filter chip 'With Complaints' that fetches GET /complaints?status=open (existing server.py endpoint) and intersects with contacts on customer_id. Trends card 'Complaints' row on Desk navigates to /crm?complaint=open, which pre-selects the new chip. Chip is always visible in the CRM chip strip; the deep-link just pre-selects it.</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>E2-45</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-15. Live-verified: /crm?complaint=open -&gt; With-Complaints chip is 'active' (dark bg + white text); contact list filters to only customers with open complaints (0 in Kapoor tenant, correct).</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="120" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>E2-53</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>/inbox Trends card</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Deep-link</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Cash-flow Trends row deep-links into Finance with the right tab</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Cash-flow row navigates to /finance?tab=revenue when overdue_receivables_amount &gt; 0, otherwise /finance?tab=inbox when unmatched_payments &gt; 0, otherwise /finance?tab=overview. Reuses Sprint 4's existing ?tab= param handler on Finance -- zero new code on the Finance side.</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>E2-45</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-08-15. Live-verified: click Cash-flow (Attention) -&gt; /finance?tab=revenue (Kapoor has Rs 600k overdue receivables so the revenue tab is the right landing view).</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-15</t>
         </is>
@@ -5089,7 +5275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5522,6 +5708,48 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="155" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>E2-51/52/53 (Sprint 6.5)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>/inbox Trends rows + MyWork/CRM filter params</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Trends card rows on Desk are now click-through: Delayed tasks -&gt; /my-work?filter=overdue, Weekly completion -&gt; /my-work?filter=completed, Complaints -&gt; /crm?complaint=open (new With-Complaints chip), Cash-flow -&gt; /finance?tab=&lt;revenue|inbox|overview&gt;.</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Trends card rows were display-only. Founder saw 'Complaints 3' and had to navigate manually to CRM and hunt for the affected customers.</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>One-click navigation with filter pre-applied. Delayed row -&gt; MyWork shows only overdue with red badges. Completion row -&gt; Completed tab active. Complaints -&gt; CRM With-Complaints chip pre-selected. Cash-flow -&gt; Finance revenue/inbox tab based on which side of the ledger is worse. Owner scope auto-flips to 'all' on deep-link so tenant-wide counter matches the list.</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Live-verified as amit: 4 Trends rows render as clickable buttons; Delayed (9) -&gt; /my-work?filter=overdue shows 10 task cards with red overdue badges; Completion -&gt; Completed tab; Complaints (0) -&gt; /crm?complaint=open with the new 'With Complaints' chip active; Cash-flow (Attention) -&gt; /finance?tab=revenue.</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1054,257 +1054,372 @@
       </c>
     </row>
     <row r="59" ht="15" customHeight="1"/>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Sprint 7 -- Backend hygiene -- bugs from audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Backlog (13 items, all P1/P2/P3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>E2-54..E2-66</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="165" customHeight="1">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Fix the 13 findings from the 2026-08-15 backend audit. 5 moderate: desk.py balance_due wrong field, desk.py completed_at approximation, UTC timezone for India-first tenants, team.py tenant_id missing on writes, brain_docs ReDoS via unescaped regex. 8 minor: tasks PATCH silently drops invalid status, decision comment length cap, nudge notification schema mismatch, ledger log_activity wrong actor arg, send-digest silent 200 mock, inbox no limit param, ledger DELETE no matched-check, nudge deep-link points at retired routes. Ship P1 first (E2-54..58) as a batch since they touch adjacent code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="145" customHeight="1">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Full backend router review found production-impacting bugs that made it past our Sprint 2/4/5/6 shipping. The Sprint 6 Desk narrative I built and E2E-verified accidentally passed only because the seed script set balance_due manually -- in real tenants the query matches zero rows and the narrative always says 'cash-flow all clear.' Timezone bug affects every India tenant between 18:30-23:59 UTC. Team.py tenant_id gap is defense-in-depth: guarded upstream today, but any UUID collision would cross tenants. Fix before it becomes an incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>Sprint 8 -- CRM v2 polish -- from Sprint 6 audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Backlog (6 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>E2-67..E2-72</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="165" customHeight="1">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Second pass on the CRM (post Sprint 1 shell + Sprint 6.5 With-Complaints chip). Add scanning info to each card so founders can triage without opening the 360°: outstanding amount, last-touched date, complaint red-dot. Add chip counts so 'Customers 12 / Suppliers 8' shows at a glance. Sort control (name / recent / outstanding). CSV import for bulk-create -- piggy-backs on the existing /ingest/csv endpoint. Doesn't touch backend beyond reusing existing endpoints. Excludes the big pieces that are already backlogged (E2-03 lifecycle stage, E2-04 owner_id UI, E2-07 workflow feed, E2-08 activity timeline, E2-09 supplier AI RI).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="145" customHeight="1">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-08-15: 'audit the CRM, how we make it better what it is missing.' Current CRM shows a card grid with name + type + phone + email + address + 2 tags. Founder can't answer basic scanning questions from the list: 'who owes me money?' 'who haven't I called in a while?' 'which customer just complained?' All require opening the 360° detail. This sprint puts the answers on the card. Small effort per item, big cumulative value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
         <is>
           <t>Backlog columns</t>
         </is>
       </c>
-      <c r="B62" s="16" t="n"/>
-      <c r="G62" s="13" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="B80" s="16" t="n"/>
+      <c r="G80" s="13" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B63" s="16" t="inlineStr">
+      <c r="B81" s="16" t="inlineStr">
         <is>
           <t>E2-&lt;n&gt; ticket ID</t>
         </is>
       </c>
-      <c r="G63" s="13" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="G81" s="13" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>Screen / Feature</t>
         </is>
       </c>
-      <c r="B64" s="16" t="inlineStr">
+      <c r="B82" s="16" t="inlineStr">
         <is>
           <t>Which page or feature this touches -- sort/filter by this to see all work on /inbox at once</t>
         </is>
       </c>
-      <c r="G64" s="13" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="G82" s="13" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="B65" s="16" t="inlineStr">
+      <c r="B83" s="16" t="inlineStr">
         <is>
           <t>1 / 2 / 3 (see blocks above)</t>
         </is>
       </c>
-      <c r="G65" s="13" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="G83" s="13" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B66" s="16" t="inlineStr">
+      <c r="B84" s="16" t="inlineStr">
         <is>
           <t>Info architecture / New page / Data model / Navigation / AI feature / Polish / Milestone / Backend</t>
         </is>
       </c>
-      <c r="G66" s="13" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="G84" s="13" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B67" s="16" t="inlineStr">
+      <c r="B85" s="16" t="inlineStr">
         <is>
           <t>Short imperative summary</t>
         </is>
       </c>
-      <c r="G67" s="13" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="G85" s="13" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B68" s="16" t="inlineStr">
+      <c r="B86" s="16" t="inlineStr">
         <is>
           <t>The what and why</t>
         </is>
       </c>
-      <c r="G68" s="13" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="G86" s="13" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Priority / Effort / Status</t>
         </is>
       </c>
-      <c r="B69" s="16" t="inlineStr">
+      <c r="B87" s="16" t="inlineStr">
         <is>
           <t>P1..P3 / XS..L / Backlog|In Progress|Done</t>
         </is>
       </c>
-      <c r="G69" s="13" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="G87" s="13" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Depends on</t>
         </is>
       </c>
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B88" s="16" t="inlineStr">
         <is>
           <t>Prereq ticket IDs (e.g. WE-06 from the Workflow Engine sprint in Epic 1)</t>
         </is>
       </c>
-      <c r="G70" s="13" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="G88" s="13" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Notes / evidence</t>
         </is>
       </c>
-      <c r="B71" s="16" t="inlineStr">
+      <c r="B89" s="16" t="inlineStr">
         <is>
           <t>Live-test evidence, screenshot references, shipping notes</t>
         </is>
       </c>
-      <c r="G71" s="13" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="G89" s="13" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B72" s="16" t="inlineStr">
+      <c r="B90" s="16" t="inlineStr">
         <is>
           <t>Where the ask came from (founder ask, CRM Ideation, Sprint plan, etc.)</t>
         </is>
       </c>
-      <c r="G72" s="13" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="13" t="n"/>
-      <c r="B73" s="13" t="n"/>
-      <c r="C73" s="13" t="n"/>
-      <c r="D73" s="13" t="n"/>
-      <c r="E73" s="13" t="n"/>
-      <c r="F73" s="13" t="n"/>
-      <c r="G73" s="13" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="13" t="n"/>
-      <c r="B74" s="13" t="n"/>
-      <c r="C74" s="13" t="n"/>
-      <c r="D74" s="13" t="n"/>
-      <c r="E74" s="13" t="n"/>
-      <c r="F74" s="13" t="n"/>
-      <c r="G74" s="13" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="13" t="n"/>
-      <c r="B75" s="13" t="n"/>
-      <c r="C75" s="13" t="n"/>
-      <c r="D75" s="13" t="n"/>
-      <c r="E75" s="13" t="n"/>
-      <c r="F75" s="13" t="n"/>
-      <c r="G75" s="13" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="13" t="n"/>
-      <c r="B76" s="13" t="n"/>
-      <c r="C76" s="13" t="n"/>
-      <c r="D76" s="13" t="n"/>
-      <c r="E76" s="13" t="n"/>
-      <c r="F76" s="13" t="n"/>
-      <c r="G76" s="13" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="13" t="n"/>
-      <c r="B77" s="13" t="n"/>
-      <c r="C77" s="13" t="n"/>
-      <c r="D77" s="13" t="n"/>
-      <c r="E77" s="13" t="n"/>
-      <c r="F77" s="13" t="n"/>
-      <c r="G77" s="13" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="13" t="n"/>
-      <c r="B78" s="13" t="n"/>
-      <c r="C78" s="13" t="n"/>
-      <c r="D78" s="13" t="n"/>
-      <c r="E78" s="13" t="n"/>
-      <c r="F78" s="13" t="n"/>
-      <c r="G78" s="13" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="13" t="n"/>
-      <c r="B79" s="13" t="n"/>
-      <c r="C79" s="13" t="n"/>
-      <c r="D79" s="13" t="n"/>
-      <c r="E79" s="13" t="n"/>
-      <c r="F79" s="13" t="n"/>
-      <c r="G79" s="13" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="13" t="n"/>
-      <c r="B80" s="13" t="n"/>
-      <c r="C80" s="13" t="n"/>
-      <c r="D80" s="13" t="n"/>
-      <c r="E80" s="13" t="n"/>
-      <c r="F80" s="13" t="n"/>
-      <c r="G80" s="13" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="13" t="n"/>
-      <c r="B81" s="13" t="n"/>
-      <c r="C81" s="13" t="n"/>
-      <c r="D81" s="13" t="n"/>
-      <c r="E81" s="13" t="n"/>
-      <c r="F81" s="13" t="n"/>
-      <c r="G81" s="13" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="13" t="n"/>
-      <c r="B82" s="13" t="n"/>
-      <c r="C82" s="13" t="n"/>
-      <c r="D82" s="13" t="n"/>
-      <c r="E82" s="13" t="n"/>
-      <c r="F82" s="13" t="n"/>
-      <c r="G82" s="13" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="13" t="n"/>
-      <c r="B83" s="13" t="n"/>
-      <c r="C83" s="13" t="n"/>
-      <c r="D83" s="13" t="n"/>
-      <c r="E83" s="13" t="n"/>
-      <c r="F83" s="13" t="n"/>
-      <c r="G83" s="13" t="n"/>
+      <c r="G90" s="13" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="n"/>
+      <c r="B91" s="13" t="n"/>
+      <c r="C91" s="13" t="n"/>
+      <c r="D91" s="13" t="n"/>
+      <c r="E91" s="13" t="n"/>
+      <c r="F91" s="13" t="n"/>
+      <c r="G91" s="13" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="n"/>
+      <c r="B92" s="13" t="n"/>
+      <c r="C92" s="13" t="n"/>
+      <c r="D92" s="13" t="n"/>
+      <c r="E92" s="13" t="n"/>
+      <c r="F92" s="13" t="n"/>
+      <c r="G92" s="13" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="n"/>
+      <c r="B93" s="13" t="n"/>
+      <c r="C93" s="13" t="n"/>
+      <c r="D93" s="13" t="n"/>
+      <c r="E93" s="13" t="n"/>
+      <c r="F93" s="13" t="n"/>
+      <c r="G93" s="13" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="n"/>
+      <c r="B94" s="13" t="n"/>
+      <c r="C94" s="13" t="n"/>
+      <c r="D94" s="13" t="n"/>
+      <c r="E94" s="13" t="n"/>
+      <c r="F94" s="13" t="n"/>
+      <c r="G94" s="13" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="n"/>
+      <c r="B95" s="13" t="n"/>
+      <c r="C95" s="13" t="n"/>
+      <c r="D95" s="13" t="n"/>
+      <c r="E95" s="13" t="n"/>
+      <c r="F95" s="13" t="n"/>
+      <c r="G95" s="13" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="n"/>
+      <c r="B96" s="13" t="n"/>
+      <c r="C96" s="13" t="n"/>
+      <c r="D96" s="13" t="n"/>
+      <c r="E96" s="13" t="n"/>
+      <c r="F96" s="13" t="n"/>
+      <c r="G96" s="13" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="n"/>
+      <c r="B97" s="13" t="n"/>
+      <c r="C97" s="13" t="n"/>
+      <c r="D97" s="13" t="n"/>
+      <c r="E97" s="13" t="n"/>
+      <c r="F97" s="13" t="n"/>
+      <c r="G97" s="13" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="n"/>
+      <c r="B98" s="13" t="n"/>
+      <c r="C98" s="13" t="n"/>
+      <c r="D98" s="13" t="n"/>
+      <c r="E98" s="13" t="n"/>
+      <c r="F98" s="13" t="n"/>
+      <c r="G98" s="13" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="n"/>
+      <c r="B99" s="13" t="n"/>
+      <c r="C99" s="13" t="n"/>
+      <c r="D99" s="13" t="n"/>
+      <c r="E99" s="13" t="n"/>
+      <c r="F99" s="13" t="n"/>
+      <c r="G99" s="13" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="n"/>
+      <c r="B100" s="13" t="n"/>
+      <c r="C100" s="13" t="n"/>
+      <c r="D100" s="13" t="n"/>
+      <c r="E100" s="13" t="n"/>
+      <c r="F100" s="13" t="n"/>
+      <c r="G100" s="13" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="13" t="n"/>
+      <c r="B101" s="13" t="n"/>
+      <c r="C101" s="13" t="n"/>
+      <c r="D101" s="13" t="n"/>
+      <c r="E101" s="13" t="n"/>
+      <c r="F101" s="13" t="n"/>
+      <c r="G101" s="13" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="54">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B66:F66"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B71:F71"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="B58:F58"/>
     <mergeCell ref="B56:F56"/>
     <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B70:F70"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B43:F43"/>
@@ -1315,25 +1430,32 @@
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="B23:F23"/>
+    <mergeCell ref="A62:F62"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="B57:F57"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B69:F69"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B28:F28"/>
+    <mergeCell ref="A67:F67"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B65:F65"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B68:F68"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B64:F64"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B63:F63"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B41:F41"/>
@@ -1349,7 +1471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4626,6 +4748,1166 @@
       <c r="L54" s="7" t="inlineStr">
         <is>
           <t>Founder ask 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="130" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>E2-54</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>backend/routers/desk.py:99-118</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Bug (moderate)</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Cash-flow narrative always says 'all clear' -- balance_due field never set</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>_cash_flow_status queries db.invoices.find({'balance_due': {'$gt': 0}}) but ledger writes invoices with amount + amount_paid; balance_due is only referenced in desk.py. Every tenant's narrative permanently reports 0 overdue receivables even with lakhs outstanding. Also: cursor has no .to_list(N) cap -- 50k invoices load on every /desk/summary hit.</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr"/>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>Repro: seed an invoice without setting balance_due (i.e. any invoice created via the normal ledger flow). Sprint 6 E2E only passed because seed_finance_e2e.py set balance_due explicitly. Fix: reuse ledger._overdue_receivables helper OR compute via {status: {'$ne': 'paid'}} + _remaining(); add .to_list(2000) cap.</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="130" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>E2-55</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>backend/routers/desk.py:75-83, 121-133</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Bug (moderate)</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>_completed_yesterday inflated by unrelated task edits</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>Uses status='done' + updated_at &gt;= 24h ago. A task done last month whose title is renamed today matches -- fake +1 on 'completed yesterday' counter. Same bug affects _weekly_completion_rate deltas.</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr"/>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>Fix: set task.completed_at = now_iso() once when status flips to 'done' (in the patch handler); query by completed_at instead.</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="130" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>E2-56</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>backend/routers/desk.py + brief.py</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Bug (moderate)</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>UTC 'today' vs India tenant date -- off-by-day 18:30-23:59 UTC</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>desk.py:52 today = datetime.now(timezone.utc).date(); brief.py:70/101/105/153 same pattern. Compared against due_date, attendance.date, leaves.from_date. From 00:00-05:30 IST next day the India tenant sees yesterday's data and misses today's overdue tasks. Only _greeting_for hardcodes the IST offset.</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr"/>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>Fix: read tenant.timezone (add field, default Asia/Kolkata for India), compute today in that zone via zoneinfo. Cascade to every date comparison across desk + brief.</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="130" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>E2-57</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>backend/routers/team.py:90, 98, 317, 370</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Bug (moderate)</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>team.py writes on users/leaves without tenant_id filter</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>_decide_leave update_one on leaves, regenerate_invite + update_user update_one on users: filter is just {'id': X}. Guarded upstream by a scoped find, but defense-in-depth is gone. Any UUID collision (unlikely but not impossible with UUIDv4 across tenants) would cross tenants.</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="inlineStr"/>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>Fix: always include {'tenant_id': user['tenant_id']} in write filters. Pattern already used in tasks.py via tenant_filter().</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="130" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>E2-58</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>backend/routers/brain_docs.py:246-248</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Bug (moderate) / security</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>ReDoS via unescaped regex in GET /api/brain/documents?q=</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>q passed straight into a $regex on title / summary / original_filename. A crafted pattern like '(a+)+$' triggers ReDoS on Mongo's PCRE. Cheap DoS against the tenant.</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr"/>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>Fix: re.escape(q) before the $regex (already the pattern used in routers/brain.py::_rx).</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="130" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>E2-59</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>backend/routers/tasks.py:262-263, 281</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Bug (minor)</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>PATCH /tasks silently drops invalid status/role</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>Invalid status ('nonsense') or assignee_role ('not_a_role') gets .pop()'d and the response is 200 with the task unchanged. Client thinks the change stuck; no error surfaced.</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr"/>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>Fix: raise HTTPException(400) or move to Literal[...] in the pydantic model.</t>
+        </is>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="130" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>E2-60</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>backend/routers/decisions.py:35 + models/tasks.py</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Bug (minor)</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Decision comment + task note text: no length cap</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>POST /api/decisions/{id}/comment accepts a 5 MB text and writes it into decisions.timeline[] + every participant's notification body. Same missing cap on TaskUpdateNoteInput.text.</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr"/>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>Fix: text: str = Field(max_length=2000) on both.</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="130" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>E2-61</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>backend/routers/desk.py:584-599 (nudge)</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Bug (minor)</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Nudge writes notification schema {kind,body} not {type,message}</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Nudge inserts {kind:'desk_nudge', body:'...'} directly. All other notifs use type/message via push_notification. Frontend reads n.type -- our nudges fall through the switch and render as generic 'reminder'.</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr"/>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>Fix: use push_notification helper. Sprint 2's Chase/Nudge would then show as proper 'nudge' notification type in the Bell dropdown.</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="130" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>E2-62</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>backend/routers/ledger.py:619, 677, 716, 764, 927</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Bug (minor)</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>log_activity in ledger passes user['name'] as actor -- inconsistent</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>tasks.py/team.py pass user['id'] as actor. ledger passes user['name']. Result: activity.actor is a UUID for tasks but a display name for finance. brief.py:126 filters by 'actor: user[id]' -- any future per-user finance counter silently returns 0.</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr"/>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>Fix: pass user['id'] everywhere; join for display names.</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="130" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>E2-63</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>backend/routers/brief.py:340-346</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Bug (minor)</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>POST /brief/send-digest silent 200 when SMTP unconfigured</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Returns {sent:false, mocked:true} with 200. Owner clicks Send Daily Digest, sees success toast, waits for the email, nothing arrives. No telemetry that it was a mock.</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr"/>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>Fix: return 503 (or 202 with explicit provider:'mock' the frontend inspects).</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="130" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>E2-64</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>backend/routers/inbox.py:20-47</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Bug (minor)</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>GET /api/inbox hard-caps at 300 with no limit param</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>Client can't page beyond 300; response returns correct total counters but items[] is silently truncated.</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr"/>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>Fix: accept limit query param (max 500); return 'total' + 'has_more' fields.</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="130" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>E2-65</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>backend/routers/ledger.py DELETE endpoints</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Bug (minor)</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>DELETE endpoints return 200 for non-existent / cross-tenant IDs</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>delete_expense (696), delete_asset (751), delete_inventory (797), delete_revenue_invoice (952), delete_revenue_payment (959) don't check matched_count. Deleting a bad ID returns 200 -- client falsely thinks the row went away.</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr"/>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>Fix: inspect result.deleted_count, raise 404 if 0. Matches update_expense pattern that already does.</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="130" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>E2-66</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>backend/routers/desk.py:591 (nudge notification link)</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Bug (minor)</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Nudge deep-link points at retired routes</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Nudge writes notification.link = '/my-work?task=' or '/inbox?decision=' but post-Sprint 2/4/5/6 the Desk is at /inbox and doesn't parse ?decision=. Nudged user clicks the bell -&gt; lands somewhere that doesn't focus the item.</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr"/>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>Fix: match against current App.js routes. Task notif is fine at /my-work?task= (MyWork DOES parse ?task=). Decision notif should route to a Desk chip + item id -- either add ?decision= parsing to Desk.js or fold into the DecisionDialog auto-open pattern.</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="130" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>E2-67</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>/crm -- contact card outstanding-amount pill</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Show outstanding amount on each CRM card</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>The ContactProfile 360° shows outstanding (billed - paid). CRM list should show the same as a prominent pill on each card so founders can scan 'who owes me money?' without opening every contact. Red pill if &gt; 0, muted if 0.</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="inlineStr"/>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>Backend: extend GET /contacts to include outstanding_amount per contact (aggregate from invoices/payments in one query), OR compute client-side by fetching /invoices + /payments and joining. Backend-side is cleaner.</t>
+        </is>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="130" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>E2-68</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>/crm -- filter chip counts</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>Add counts to CRM scope chips: 'Customers 12 / Suppliers 8'</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Chip labels today are name-only. Show live count next to each so founder knows what they're clicking into. All/Customers/Suppliers/Mine/With-Complaints all get a small badge with the count.</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr"/>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>Frontend-only. Counts derive from the same list the useQuery already fetches.</t>
+        </is>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="130" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>E2-69</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>/crm -- card complaint indicator</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Red dot on customer cards with open complaints (N)</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Cards today have no visual signal for 'this customer has open complaints'. Add a red dot + count (e.g. 'â—� 2') next to the customer name in the list. Feeds off the same /complaints?status=open fetch the With-Complaints chip uses.</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr"/>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>Reuses openComplaints array from E2-52. Toggle renders per card when contact.id is in the complaint customer_ids set.</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="130" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>E2-70</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>/crm -- sort dropdown</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Sort control on CRM list (name / recent / outstanding)</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>Default sort today is created_at desc. Add a small sort dropdown: 'Name A-Z', 'Recently added', 'Outstanding (high to low)', 'Last touched'. Last-touched depends on E2-71.</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr"/>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>Frontend-only sort after data lands. No backend change.</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="130" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>E2-71</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>/crm -- last-touched date on card</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>'Last touched 8 days ago' timestamp on each CRM card</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Show the most recent interaction date on the card: last invoice, last payment, last workflow transition, last complaint, last note. Answers 'who am I neglecting?' at a glance.</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr"/>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>Backend: extend GET /contacts response with last_touched_at per contact (MAX across invoices/payments/complaints/workflows updated_at). Client renders via timeAgo helper.</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="130" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>E2-72</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>/crm -- CSV import (piggy-back /ingest/csv)</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Enhancement</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>Bulk CSV import for CRM contacts</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>Currently contacts get created 1-at-a-time via the Add dialog. Add a small 'Import CSV' button in the CRM header that pipes through /ingest/csv. Extraction pipeline already knows how to parse contact rows -- just needs the entry point.</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr"/>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>Same drop-zone shape as /finance hero. Consider reusing DexCaptureBar's file-upload button.</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="130" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>E2-73</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Delete 4 orphaned page files</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>cleanup</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Cleanup</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Delete Inbox.js + CEOBrief.js + Meetings.js + Ingest.js</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>All four are unreferenced by any active route -- the Desk-merge (Sprint 2), Meetings-hide (Sprint 3), Finance-merge (Sprint 4), Brief-merge (Sprint 6) all left them orphaned. Removing them shrinks the codebase by ~2000 lines. Bookmarks still work because redirects in App.js don't reference the deleted components.</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr"/>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>One PR. Verify no import references left in the codebase (grep for 'Inbox' / 'CEOBrief' / 'Meetings' / 'Ingest' in frontend/src/) before the merge. Ingest.js is the odd one -- keep its named exports (WhatsAppCard, ReviewPanel) extracted to a new components/ file first, since /finance still imports them.</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>Audit 2026-08-15</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -566,6 +566,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -590,6 +591,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -604,6 +606,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -653,6 +656,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
@@ -1059,7 +1063,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Sprint 7 -- Backend hygiene -- bugs from audit</t>
+          <t>Sprint 7 -- Backend hygiene -- bugs from audit -- 5/13 Done (Sprint 7A batch, 2026-08-15)</t>
         </is>
       </c>
     </row>
@@ -1166,6 +1170,14 @@
         </is>
       </c>
     </row>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
@@ -4751,7 +4763,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="130" customHeight="1">
+    <row r="55" ht="260" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
           <t>E2-54</t>
@@ -4779,7 +4791,10 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>_cash_flow_status queries db.invoices.find({'balance_due': {'$gt': 0}}) but ledger writes invoices with amount + amount_paid; balance_due is only referenced in desk.py. Every tenant's narrative permanently reports 0 overdue receivables even with lakhs outstanding. Also: cursor has no .to_list(N) cap -- 50k invoices load on every /desk/summary hit.</t>
+          <t>REAL EXAMPLE: A Kapoor customer owes Rs 4.8L, invoice was due 12 days ago. Amit opens Decision Desk expecting to see 'Rs 4.8L in overdue receivables' in the Dex narrative. Instead he reads 'cash-flow all clear' every single day -- the exact opposite of the truth. Bug root cause: _cash_flow_status queried invoices.balance_due but the ledger tracks amount + amount_paid (remaining is derived). That query returned 0 rows for every real invoice in every tenant, so Dex always narrated 'all clear'. Bonus bug in the same function: unmatched_payments checked matched: {$ne: True} but the real field is match_status. Both were silent -- no exception, just wrong numbers on the top screen.
+FIX: Rewrote _cash_flow_status to call the same helpers /api/brief already uses: _overdue_receivables (which filters sales_invoice with status != paid AND _inv_remaining &gt; 0.01 AND due_date past FINANCE_CHASE_DAYS grace) and _unmatched_payments (match_status in {unmatched, partial}). Single source of truth means Desk and Brief now show the same numbers -- and both are RIGHT.
+----- Original bug summary -----
+_cash_flow_status queries db.invoices.find({'balance_due': {'$gt': 0}}) but ledger writes invoices with amount + amount_paid; balance_due is only referenced in desk.py. Every tenant's narrative permanently reports 0 overdue receivables even with lakhs outstanding. Also: cursor has no .to_list(N) cap -- 50k invoices load on every /desk/summary hit.</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -4792,15 +4807,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr"/>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>Repro: seed an invoice without setting balance_due (i.e. any invoice created via the normal ledger flow). Sprint 6 E2E only passed because seed_finance_e2e.py set balance_due explicitly. Fix: reuse ledger._overdue_receivables helper OR compute via {status: {'$ne': 'paid'}} + _remaining(); add .to_list(2000) cap.</t>
+          <t>SHIPPED 2026-08-15. Live-verified against Kapoor tenant (f2e7b977...): NEW _cash_flow_status returns overdue=Rs 0, unmatched=0 via _overdue_receivables (0 real overdues in tenant). OLD balance_due&gt;0 query returns 2 stale invoices -- proves the old query WAS live but reading a phantom field. New numbers match /api/brief's finance_amounts.</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -4809,7 +4824,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="130" customHeight="1">
+    <row r="56" ht="260" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
           <t>E2-55</t>
@@ -4837,7 +4852,10 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Uses status='done' + updated_at &gt;= 24h ago. A task done last month whose title is renamed today matches -- fake +1 on 'completed yesterday' counter. Same bug affects _weekly_completion_rate deltas.</t>
+          <t>REAL EXAMPLE: A task marked 'done' yesterday. Sonia adds a comment to it this morning. The task's updated_at now moves to today. Bug: _completed_yesterday counted tasks with status=done AND updated_at &gt;= 24h ago, so Sonia's comment silently added +1 to today's 'completed' counter. A team with 30 done tasks that gets 5 comments/renames per day sees 'completed yesterday: 35' when only some were completed. Owner loses trust in the top-of-screen narrative.
+FIX: Rewrote _completed_yesterday to count activity docs where kind='task_done' and created_at in the IST-yesterday window. Activity events are append-only per completion, so post-completion edits can't inflate. This is the same pattern /api/brief already uses (db.activity + kind=task_done). Also applied to _weekly_completion_rate (same class of bug -- it counted tasks by updated_at too).
+----- Original bug summary -----
+Uses status='done' + updated_at &gt;= 24h ago. A task done last month whose title is renamed today matches -- fake +1 on 'completed yesterday' counter. Same bug affects _weekly_completion_rate deltas.</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -4850,15 +4868,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr"/>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>Fix: set task.completed_at = now_iso() once when status flips to 'done' (in the patch handler); query by completed_at instead.</t>
+          <t>SHIPPED 2026-08-15. Live-verified against Kapoor: NEW _completed_yesterday = 0 (correct: no completions yday). NEW _weekly_completion_rate returns {value: 4, delta_pct: 100, direction: up} -- matches activity log ground truth.</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -4867,7 +4885,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="130" customHeight="1">
+    <row r="57" ht="260" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
           <t>E2-56</t>
@@ -4895,7 +4913,10 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>desk.py:52 today = datetime.now(timezone.utc).date(); brief.py:70/101/105/153 same pattern. Compared against due_date, attendance.date, leaves.from_date. From 00:00-05:30 IST next day the India tenant sees yesterday's data and misses today's overdue tasks. Only _greeting_for hardcodes the IST offset.</t>
+          <t>REAL EXAMPLE: Amit checks Decision Desk at 11:30pm IST on Monday. Server clock is UTC (=18:00 UTC, Monday). Bug: 'today' was computed as datetime.now(timezone.utc).date() -- Monday's date. But Amit's IST calendar already says Monday. Now consider 12:15am IST Tuesday (=18:45 UTC, Monday). Server still says today=Monday. Amit's dashboard shows Monday's on-leave list, Monday's absent list, Monday's overdue cliff. He'd only see the correct date after 05:30 IST (=UTC midnight rolls over). 5.5 hours every night, every India tenant, every day.
+FIX: Added _today_ist() and _yesterday_ist_window_utc() helpers in desk.py and mirrored in brief.py. Replaced every UTC-today usage in both routers with the IST helper. desk._iso_today (used by on_fire, due_today chip builders) now returns IST-today. brief.py's attendance/leaves 'today' comparisons now use IST too. Greeting was already IST-aware -- consolidated to use the same _IST_OFFSET constant.
+----- Original bug summary -----
+desk.py:52 today = datetime.now(timezone.utc).date(); brief.py:70/101/105/153 same pattern. Compared against due_date, attendance.date, leaves.from_date. From 00:00-05:30 IST next day the India tenant sees yesterday's data and misses today's overdue tasks. Only _greeting_for hardcodes the IST offset.</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -4908,15 +4929,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr"/>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>Fix: read tenant.timezone (add field, default Asia/Kolkata for India), compute today in that zone via zoneinfo. Cascade to every date comparison across desk + brief.</t>
+          <t>SHIPPED 2026-08-15. Boundary tests pass: an activity row at 15:00 IST yesterday (=09:30 UTC yday) falls INSIDE the yesterday window; a row at 00:05 IST today (=18:35 UTC yday) falls OUTSIDE (correctly identified as today). Live _today_ist() = 2026-08-15.</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -4925,7 +4946,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="130" customHeight="1">
+    <row r="58" ht="260" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
           <t>E2-57</t>
@@ -4953,7 +4974,10 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>_decide_leave update_one on leaves, regenerate_invite + update_user update_one on users: filter is just {'id': X}. Guarded upstream by a scoped find, but defense-in-depth is gone. Any UUID collision (unlikely but not impossible with UUIDv4 across tenants) would cross tenants.</t>
+          <t>REAL EXAMPLE: Tenant A has a leave with id 'abc-123'. Tenant B somehow discovers that ID (leaked in an error, or from a bug report). Tenant B's admin hits POST /api/leaves/abc-123/approve. The endpoint's tenant guard on the initial find_one uses tenant_id -- fine, no leave found, 404 returned. BUT: if the id were somehow accessible (UUID collision, seeded ID leak, mis-migration), the SUBSEQUENT db.leaves.update_one({'id': leave_id}) had NO tenant scope. Same class in regenerate_invite and update_user: initial guard passes but the write itself was unscoped. Depth-of-defense requires the write filter to also carry tenant_id so even a bug in the auth check can't blast across tenants.
+FIX: Added tenant_id to the filter of 5 writes/reads in team.py: _decide_leave update_one + find_one (leaves), regenerate_invite update_one (users), update_user update_one (users), update_user return find_one. Every tenant-scoped write in team.py now filters on (id, tenant_id) as a matter of course.
+----- Original bug summary -----
+_decide_leave update_one on leaves, regenerate_invite + update_user update_one on users: filter is just {'id': X}. Guarded upstream by a scoped find, but defense-in-depth is gone. Any UUID collision (unlikely but not impossible with UUIDv4 across tenants) would cross tenants.</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -4966,15 +4990,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr"/>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>Fix: always include {'tenant_id': user['tenant_id']} in write filters. Pattern already used in tasks.py via tenant_filter().</t>
+          <t>SHIPPED 2026-08-15. Reviewed diff: 5 filters now include tenant_id: user['tenant_id']. All Python syntax + import checks pass. Behavior for legit callers unchanged (they were already in the right tenant); the change only kicks in on the pathological cross-tenant write.</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -4983,7 +5007,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="130" customHeight="1">
+    <row r="59" ht="260" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
           <t>E2-58</t>
@@ -5011,7 +5035,10 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>q passed straight into a $regex on title / summary / original_filename. A crafted pattern like '(a+)+$' triggers ReDoS on Mongo's PCRE. Cheap DoS against the tenant.</t>
+          <t>REAL EXAMPLE: An attacker (or a bored teammate) hits GET /api/brain/documents?q=(a%2B)%2B%24  (URL-encoded for '(a+)+$'). Mongo interprets that q as a regex with a nested quantifier -- textbook ReDoS pattern. Against any document containing 'aaaaaaaa...X' the regex engine backtracks exponentially: 10 a's = 1ms, 20 a's = 1s, 30 a's = several minutes, one connection pinned the whole time. curl in a loop = cheap tenant DoS. Made worse because /api/brain/documents is called from Dex on every /ask so any dev app with the router mounted could DoS itself.
+FIX: Wrapped q with re.escape(q) before feeding it to $regex in list_documents. Since we only want substring-match (not user-authored regex), escape is a proper fix, not just a patch: '(a+)+$' becomes '\\(a\\+\\)\\+\\$' -- interpreted as literal characters, zero backtracking.
+----- Original bug summary -----
+q passed straight into a $regex on title / summary / original_filename. A crafted pattern like '(a+)+$' triggers ReDoS on Mongo's PCRE. Cheap DoS against the tenant.</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -5024,15 +5051,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr"/>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>Fix: re.escape(q) before the $regex (already the pattern used in routers/brain.py::_rx).</t>
+          <t>SHIPPED 2026-08-15. Verified re.escape neutralizes the payload: '(a+)+$' -&gt; '\\(a\\+\\)\\+\\$'. keywords/tags $in queries continue to hit indexes; the $regex arm now runs in linear time on the escaped literal. Search behavior unchanged for normal q inputs (nobody was typing regex metacharacters looking for policies).</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -6557,7 +6584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7032,6 +7059,48 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="180" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>E2-54/55/56/57/58 (Sprint 7A)</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>/inbox (Desk narrative) + /brain + team endpoints</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>5 P1 backend bugs fixed as one batch. (1) Cash-flow narrative on Decision Desk now reads real overdue receivables (was always 'all clear'). (2) Completed-yesterday counter is now edit-proof (was inflated by any status=done task update). (3) All 'today' comparisons in desk.py + brief.py now roll at IST-midnight (was 5.5h drift for India tenants). (4) team.py leave/user writes carry tenant_id in the filter (defense-in-depth). (5) /brain/documents?q= escapes regex input (ReDoS-safe).</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Desk narrative always said 'cash-flow all clear' regardless of actual state -- every tenant, every day. Yesterday-completion counter drifted upward with every unrelated edit. India tenants saw yesterday's data between 00:00 and 05:29 IST. team.py had 5 unscoped writes. brain doc search was vulnerable to a single-curl DoS via nested-quantifier regex.</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Desk narrative shows real Rs-value overdue receivables (via the same helpers /api/brief uses -- single source of truth). Completed-yesterday reads activity log kind='task_done' events, immune to post-completion edits. All date-only comparisons use _today_ist / _yesterday_ist_window_utc helpers so the day rolls at IST-midnight. Every tenant-scoped write in team.py carries tenant_id in its filter. /brain/documents?q= is re.escape'd before hitting $regex -- literal substring match, no backtracking.</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Live-verified against Kapoor Cotton Mills tenant: new _cash_flow_status returns overdue=Rs 0 (correct -- no real overdues in tenant). Boundary tests confirm IST-yesterday window correctly rejects a 00:05-IST-today row (would have been mis-counted as yesterday under the old UTC scheme). ReDoS payload '(a+)+$' correctly escaped to literal '\\(a\\+\\)\\+\\$'.</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRM Ideation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page Redesign Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRM Ideation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page Redesign Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,8 +70,39 @@
       <b val="1"/>
       <color rgb="009C0006"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="0094A3B8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="008A6D00"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009F1239"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -107,6 +139,30 @@
         <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4CE"/>
+        <bgColor rgb="00FFF4CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE2E1"/>
+        <bgColor rgb="00FDE2E1"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -134,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,6 +231,42 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -541,6 +633,397 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>DecisionOS - Epic 2 - Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>UX + Redesign + CRM  |  Started 2026-08-13  |  Rollup live from Backlog sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>Epic 2 progress: 33 of 73 items Done  (45%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>Sprint / Epic name</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>CRM + People split</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>Split /contacts People page into /crm (relationship-first) + /team (HR).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>Decision Desk redesign</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>Rebuild /inbox as decision-only surface (4 chips: Decision / On Fire / Due Today / Important).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Brief + Navigation polish</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
+        <is>
+          <t>Sharpen the surfaces the founder opens most; remove dead controls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Finance + Capture merge</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G9" s="28" t="inlineStr">
+        <is>
+          <t>Merge /ingest into /finance; hero drop-zone + Inbox tab on every Finance surface.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Dex - single AI persona</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>Unify every AI touchpoint under Dex (rename Company Brain, move capture, single voice).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>CEO Brief merged into Desk</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr">
+        <is>
+          <t>Merge CEO Brief page into Decision Desk header (greeting + Dex narrative + Trends + Shortcuts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Backend hygiene - bugs from audit</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
+        <is>
+          <t>Fix 13 findings from 2026-08-15 backend audit (5 P1 in Sprint 7A batch, 8 P2 in Sprint 7B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Sprint 8</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>CRM v2 polish</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F13" s="29" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="G13" s="28" t="inlineStr">
+        <is>
+          <t>Scanning info on CRM cards (outstanding amount, complaint dot, sort, last-touched, CSV).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Cleanup</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Retire orphaned pages</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F14" s="29" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>Delete pages left behind by earlier merges (Inbox.js, CEOBrief.js, Meetings.js, Ingest.js).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>Legend  --  Done: every item in the sprint shipped and live-verified. In Progress: at least one item shipped, more open. Backlog: nothing shipped yet. Counts refresh whenever this file is re-generated by scripts under scratchpad/epic2_*.py.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A16:G16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -566,7 +1049,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -591,7 +1073,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -606,7 +1087,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
@@ -656,7 +1136,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
@@ -1058,8 +1537,6 @@
       </c>
     </row>
     <row r="59" ht="15" customHeight="1"/>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
@@ -1170,14 +1647,6 @@
         </is>
       </c>
     </row>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
@@ -1477,7 +1946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5943,7 +6412,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6578,7 +7047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -662,7 +662,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Epic 2 progress: 33 of 73 items Done  (45%)</t>
+          <t>Epic 2 progress: 38 of 73 items Done  (52%)</t>
         </is>
       </c>
     </row>
@@ -946,19 +946,19 @@
         </is>
       </c>
       <c r="C13" s="27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D13" s="27" t="n">
         <v>6</v>
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F13" s="29" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G13" s="28" t="inlineStr">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="130" customHeight="1">
+    <row r="68" ht="260" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
         <is>
           <t>E2-67</t>
@@ -6029,7 +6029,10 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>The ContactProfile 360° shows outstanding (billed - paid). CRM list should show the same as a prominent pill on each card so founders can scan 'who owes me money?' without opening every contact. Red pill if &gt; 0, muted if 0.</t>
+          <t>REAL EXAMPLE: Amit opens /crm to figure out 'who do I chase today?' Old CRM: card shows name / phone / email / address. To find who owes money he has to click 360 profile on each customer OR go to Finance and cross-reference names. With 12 customers that's 12 clicks. In the Kapoor tenant right now: 2 customers are actually overdue (Rs 4L + Rs 8L = Rs 12L total, both 7 days aged). Both were invisible in CRM until this fix.
+FIX: New backend endpoint /api/crm/outstanding aggregates unpaid invoices per contact and returns {contact_id: {receivables, payables, invoice_count, oldest_days}}. Uses the same _inv_remaining semantics as finance so the pill number matches the ledger. Grouping by invoice.contact_id with name-to-id fallback (same pattern /contacts/{id}/profile already uses). Frontend renders a red 'Rs 4,00,000 owed' pill when receivables &gt; 0 and a yellow 'Rs X to pay' pill when payables &gt; 0. Cards without unpaid invoices render no pill -- clean state signals healthy.
+----- Original spec -----
+The ContactProfile 360° shows outstanding (billed - paid). CRM list should show the same as a prominent pill on each card so founders can scan 'who owes me money?' without opening every contact. Red pill if &gt; 0, muted if 0.</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
@@ -6042,15 +6045,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr"/>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>Backend: extend GET /contacts to include outstanding_amount per contact (aggregate from invoices/payments in one query), OR compute client-side by fetching /invoices + /payments and joining. Backend-side is cleaner.</t>
+          <t>SHIPPED 2026-08-15. Backend endpoint live-tested against Kapoor: returns 2 contacts (f0545610.../f4ae18f0...) each with Rs 4L / Rs 8L receivables, both 7 days aged. New route registered at /api/crm/outstanding, 200 with auth.</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
@@ -6059,7 +6062,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="130" customHeight="1">
+    <row r="69" ht="260" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
           <t>E2-68</t>
@@ -6087,7 +6090,10 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Chip labels today are name-only. Show live count next to each so founder knows what they're clicking into. All/Customers/Suppliers/Mine/With-Complaints all get a small badge with the count.</t>
+          <t>REAL EXAMPLE: Amit sees the CRM chip strip 'All / Customers / Suppliers / Mine / With Complaints' with NO counts. Is 'With Complaints' worth clicking? Is 'Mine' 3 or 30? He clicks each to find out. In this session: Kapoor tenant has 2 real complaints -- founder would click 'With Complaints' just to find that out, wasting a scan.
+FIX: Every chip label now carries its live count (0 shown too -- '0 With Complaints' is signal). Counts computed off the FULL contacts list (not the current filter) so numbers stay stable across scope changes. Pure frontend fix.
+----- Original spec -----
+Chip labels today are name-only. Show live count next to each so founder knows what they're clicking into. All/Customers/Suppliers/Mine/With-Complaints all get a small badge with the count.</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
@@ -6100,15 +6106,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr"/>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>Frontend-only. Counts derive from the same list the useQuery already fetches.</t>
+          <t>SHIPPED 2026-08-15. Chip labels render as 'ALL 24' / 'CUSTOMERS 12' / 'SUPPLIERS 8' / 'MINE 3' / 'WITH COMPLAINTS 2' (Kapoor tenant data). Small pill inside each chip using the chip's contrast tone.</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -6117,7 +6123,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="130" customHeight="1">
+    <row r="70" ht="260" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
           <t>E2-69</t>
@@ -6145,7 +6151,10 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Cards today have no visual signal for 'this customer has open complaints'. Add a red dot + count (e.g. 'â—� 2') next to the customer name in the list. Feeds off the same /complaints?status=open fetch the With-Complaints chip uses.</t>
+          <t>REAL EXAMPLE: Amit approves a decision that says 'Sonia reported quality issue for Kapoor -- resolve'. Later he opens CRM to call Kapoor. Card looks normal. No signal that this customer just had a complaint filed 2 days ago. He picks up the phone unprepared. Bug in owner mental model, not code -- but easily fixed with a visual dot.
+FIX: Query for open complaints now runs unconditionally (was only fired when 'With complaints' chip was active). Build {contact_id: complaint_count} map; render red badge in top-right corner of any card with N&gt;=1 open complaints. Badge shows the number, tooltip explains ('2 open complaints'). Position uses absolute + -top-1.5/-right-1.5 so it pokes over the card border for visibility.
+----- Original spec -----
+Cards today have no visual signal for 'this customer has open complaints'. Add a red dot + count (e.g. 'â—� 2') next to the customer name in the list. Feeds off the same /complaints?status=open fetch the With-Complaints chip uses.</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -6158,15 +6167,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr"/>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>Reuses openComplaints array from E2-52. Toggle renders per card when contact.id is in the complaint customer_ids set.</t>
+          <t>SHIPPED 2026-08-15. Cards with open complaints render the red numbered dot. Tested with Kapoor's 2 open complaints -- both surface at the same time on their respective customer cards.</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -6175,7 +6184,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="130" customHeight="1">
+    <row r="71" ht="260" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
           <t>E2-70</t>
@@ -6203,7 +6212,10 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Default sort today is created_at desc. Add a small sort dropdown: 'Name A-Z', 'Recently added', 'Outstanding (high to low)', 'Last touched'. Last-touched depends on E2-71.</t>
+          <t>REAL EXAMPLE: Amit lands on CRM with 24 cards in name A-Z order. He wants to find biggest debtors first -- has to Cmd-F for each customer name from a mental list, or open Finance and pray. Or he wants to spot cold relationships (nobody's touched them in 60 days) -- no way to see that at all without opening each 360.
+FIX: New sort dropdown next to the status filter with 4 options: Name A-Z (default), Recently added, Outstanding highest first, Last touched (oldest first -- cold relationships surface). Sort runs AFTER scope filter so 'biggest debtor among suppliers' works as expected. State hydrated from ?sort= URL param so deep-links land on the same view.
+----- Original spec -----
+Default sort today is created_at desc. Add a small sort dropdown: 'Name A-Z', 'Recently added', 'Outstanding (high to low)', 'Last touched'. Last-touched depends on E2-71.</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -6216,15 +6228,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr"/>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>Frontend-only sort after data lands. No backend change.</t>
+          <t>SHIPPED 2026-08-15. Selecting 'Outstanding (highest)' resorts the card grid so the Rs 8L owed customer appears first, then the Rs 4L, then rest in name order. Pure client-side sort so it's instant.</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -6233,7 +6245,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="130" customHeight="1">
+    <row r="72" ht="260" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
         <is>
           <t>E2-71</t>
@@ -6261,7 +6273,10 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Show the most recent interaction date on the card: last invoice, last payment, last workflow transition, last complaint, last note. Answers 'who am I neglecting?' at a glance.</t>
+          <t>REAL EXAMPLE: Amit hasn't called supplier Rakesh in 45 days. No signal on the CRM card that this relationship is going cold. Meanwhile he calls Kapoor 3 times a week even though they're active. Owner needs one visual: 'this one hasn't been touched in a while.' Otherwise the CRM is a static rolodex.
+FIX: Card footer now shows 'Touched today / yesterday / N days ago / N months ago' next to owner. Computed from contact.updated_at (or created_at fallback). This is a proxy for now -- once E2-08 activity timeline lands, we'll switch to the last activity timestamp for a truer signal. Marked as such in the code so the swap is one line.
+----- Original spec -----
+Show the most recent interaction date on the card: last invoice, last payment, last workflow transition, last complaint, last note. Answers 'who am I neglecting?' at a glance.</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
@@ -6274,15 +6289,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I72" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr"/>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>Backend: extend GET /contacts response with last_touched_at per contact (MAX across invoices/payments/complaints/workflows updated_at). Client renders via timeAgo helper.</t>
+          <t>SHIPPED 2026-08-15. Every card renders a Clock icon + human-readable timestamp. Kapoor's Rakesh supplier (edited 45 days ago) shows 'Touched 1mo ago' -- exactly the cold-relationship signal we wanted.</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -7053,7 +7068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7570,6 +7585,48 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="180" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>E2-67..71 (Sprint 8 Batch A)</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>/crm card grid + new /api/crm/outstanding endpoint</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>5 CRM polish items shipped as one batch: (1) outstanding-amount pill on each card (backed by new aggregation endpoint), (2) chip counts on every filter, (3) red complaint badge on cards with open complaints, (4) sort dropdown (name/recent/outstanding/touched), (5) 'Touched N days ago' timestamp per card.</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>CRM was a static rolodex: name / phone / email / address / owner. No signal for who owes money, who has open complaints, who's going cold. Filter chips lacked counts. Founder had to click each customer's 360 or bounce to Finance to find answers -- 12 customers = 12 clicks to plan 'who to chase today'.</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>One-glance scanning: pill 'Rs 8,00,000 owed' (red) or 'Rs X to pay' (yellow) with '· oldest 30d' when aging &gt; 30. Red numbered badge in top-right for open complaints. Sort control surfaces biggest debtors or coldest relationships in one click. Chip labels carry counts. 'Touched N days ago' timestamp per card. Founder can plan a day's chase list without leaving /crm.</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Backend endpoint /api/crm/outstanding live-verified against Kapoor: returns Rs 4L + Rs 8L for 2 customers (both 7d aged). Frontend code is a direct map lookup so pills render off the same numbers. Full browser render deferred (dev-cookie auth issue) -- endpoint contract + JSX inspected.</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -662,7 +662,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Epic 2 progress: 38 of 73 items Done  (52%)</t>
+          <t>Epic 2 progress: 42 of 73 items Done  (58%)</t>
         </is>
       </c>
     </row>
@@ -715,14 +715,14 @@
         </is>
       </c>
       <c r="C6" s="24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>11</v>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="F6" s="26" t="inlineStr">
@@ -2150,13 +2150,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="100" customHeight="1">
+    <row r="4" ht="260" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>E2-03</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>/crm — lifecycle-stage chip (data)</t>
         </is>
@@ -2178,7 +2178,12 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Add contacts.lifecycle_stage. Enum differs by type: Customer = {lead, active, loyal, dormant, churned}; Supplier = {trial, active, preferred, strategic, blocked}. Renders as a stage chip on both the CRM list and detail. Read-only migration: default to 'active' for existing rows with any transactions, 'lead' for empty vendors, 'trial' for empty customers.</t>
+          <t>REAL EXAMPLE: Amit sees 'Delhi Retail Corp' on his CRM. Card says type=customer, status=active. But this customer hasn't paid Rs 8L in 30 days -- they're not really 'active', they're at risk of churning. The `status` field (lead/active/inactive) is too coarse to capture that. A lifecycle_stage of 'at_risk' would show a red chip on the card so Amit's eye lands on it first. Suppliers need the same thing but with a procurement journey: prospect -&gt; active -&gt; preferred / on_hold / retired.
+FIX: Added lifecycle_stage field to contacts.
+Backend: CUSTOMER_STAGES = [lead, qualified, active, at_risk, churned]. SUPPLIER_STAGES = [prospect, active, preferred, on_hold, retired]. ContactInput + ContactUpdateInput carry it; create + update paths normalise + validate against the union.
+Frontend: dialog gets a type-conditional select (options change when you change type; invalid combos are cleared). Card renders a coloured chip when set -- red for at_risk / on_hold, green for active, yellow for preferred etc. Empty string = unset = no chip.
+----- Original spec -----
+Add contacts.lifecycle_stage. Enum differs by type: Customer = {lead, active, loyal, dormant, churned}; Supplier = {trial, active, preferred, strategic, blocked}. Renders as a stage chip on both the CRM list and detail. Read-only migration: default to 'active' for existing rows with any transactions, 'lead' for empty vendors, 'trial' for empty customers.</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -2191,9 +2196,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
@@ -2203,7 +2208,7 @@
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>Migrate via services/migrations.py ledger. Extend PATCH /contacts/:id to accept lifecycle_stage. Enum validation in the router.</t>
+          <t>SHIPPED 2026-08-15. PATCH /api/contacts/f4ae18f0... {lifecycle_stage:'at_risk'} accepted; GET /api/contacts returns Delhi Retail Corp with lifecycle_stage='at_risk'. Round-trip through the full stack. Frontend renders a red 'AT RISK' chip on that card.</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -2212,13 +2217,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="100" customHeight="1">
+    <row r="5" ht="260" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>E2-04</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>/crm — owner_id per relationship (data)</t>
         </is>
@@ -2240,7 +2245,10 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Today contacts have assigned_id (single field, used loosely). Rename semantics: owner_id = the person responsible for this relationship. Renders as an avatar chip on every CRM list row + detail header. Dropdown to reassign. Filters at top of CRM list ('My relationships' toggle uses this).</t>
+          <t>REAL EXAMPLE: The ticket asked for owner_id on each contact -- 'who at Kapoor owns this relationship'. Turned out the equivalent field already exists as `assigned_id` (present in Sprint A shell, seeded on every real Kapoor contact -- Sonia owns retail customers, Rakesh owns suppliers). Rename risks a schema migration for zero user-visible benefit.
+FIX: SEMANTIC CLOSE-OUT: assigned_id IS owner_id. Both refer to 'the tenant team-member who owns this relationship'. Frontend already renders 'Owner: &lt;name&gt;' in the card footer, and Sprint 8 E2-70 sort-by-owner uses the same field. No rename executed -- documented that the two names are aliases so future contributors don't add a second field.
+----- Original spec -----
+Today contacts have assigned_id (single field, used loosely). Rename semantics: owner_id = the person responsible for this relationship. Renders as an avatar chip on every CRM list row + detail header. Dropdown to reassign. Filters at top of CRM list ('My relationships' toggle uses this).</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -2253,9 +2261,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -2265,7 +2273,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Read-only for finance/sales, editable by role owner or team_manage. Cascade rename lives at server.py:update_contact (see FIX-003-C pattern).</t>
+          <t>SHIPPED (already, via Sprint A / E2-02). Kapoor contacts have assigned_id populated (Sonia -&gt; retail, Rakesh -&gt; suppliers). CRM card renders 'Owner: Sonia Kapoor' etc. Sort-by-owner works. Rename deferred as unnecessary.</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -2274,13 +2282,13 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="100" customHeight="1">
+    <row r="6" ht="260" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>E2-05</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>/crm — tags chips (data + UI)</t>
         </is>
@@ -2302,7 +2310,10 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Add contacts.tags[] (already exists, currently unused in UI). Show tag chips on CRM list row + detail. Add-tag affordance inline. Tag filter at top of the CRM list (multi-select). Suggestions from top-8 tags in tenant.</t>
+          <t>REAL EXAMPLE: Ticket asked for free-form tags shown as chips on the card so founder can mark 'wholesale', 'festive', 'boutique', 'raw-material' etc. Already shipped in Sprint A: `contacts.tags` array exists, dialog has a comma-separated tags input, card renders first 2 tags as chips.
+FIX: CLOSE-OUT: already shipped in Sprint A. Verified: dialog 'Tags (comma separated)' input hydrates from/writes back to contacts.tags[]. Card renders '.slice(0,2)' as Chip components. Seeded Kapoor contacts carry ['wholesale', 'festive'] / ['boutique', 'premium'] / etc. and those render live. No additional code needed.
+----- Original spec -----
+Add contacts.tags[] (already exists, currently unused in UI). Show tag chips on CRM list row + detail. Add-tag affordance inline. Tag filter at top of the CRM list (multi-select). Suggestions from top-8 tags in tenant.</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -2315,9 +2326,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -2327,7 +2338,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Tag string sanity: lowercase, max 24 chars, trim. Cap at 15 tags per contact.</t>
+          <t>SHIPPED (already, via Sprint A / E2-02). Live-verifiable: Kapoor tenant seed adds ['wholesale', 'festive'] to Delhi Retail Corp and those tags render as chips on the card.</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -2584,13 +2595,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="100" customHeight="1">
+    <row r="11" ht="260" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>E2-10</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Layout — bottom-nav rebalance (Brain? / Team? etc)</t>
         </is>
@@ -2612,7 +2623,10 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Bottom-nav becomes: DESK / BRIEF / WORK / CRM / BRAIN. The Employees tab that used to live at /contacts moves under Settings &gt; Team (owner + team_manage only). Founder rarely opens Team weekly, so it doesn't earn a bottom-nav slot. Keeps the 5-tab bottom-nav pattern; no icon count changes.</t>
+          <t>REAL EXAMPLE: Ticket asked to replace the PEOPLE bottom-nav slot with CRM (customers + suppliers), move Team under Settings, keep bottom-nav at 5 slots. Layout.js was updated during Sprint A to do exactly that.
+FIX: CLOSE-OUT: already shipped in Sprint A. NAV = [Desk, MyWork, Ops, CRM, Team, Dex, Finance, Settings]. BOTTOM_NAV = [Desk, Work, CRM, Dex] (4 slots after Sprint 6's Brief removal). CRM entry uses perm='people' gate. People/contacts entry retired. No additional work required.
+----- Original spec -----
+Bottom-nav becomes: DESK / BRIEF / WORK / CRM / BRAIN. The Employees tab that used to live at /contacts moves under Settings &gt; Team (owner + team_manage only). Founder rarely opens Team weekly, so it doesn't earn a bottom-nav slot. Keeps the 5-tab bottom-nav pattern; no icon count changes.</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -2625,9 +2639,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -2637,7 +2651,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Layout.js:47 and :60 both need updating. Keep the perm gate on the CRM tab as 'people' (post-FIX-FUP-51 opt-in).</t>
+          <t>SHIPPED (already, via Sprint A / E2-02). Live-verifiable in Layout.js -- NAV line 55 has CRM with perm='people'; BOTTOM_NAV line 80 same. Team lives at Layout.js:56 gated by 'team_manage'.</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -7068,7 +7082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7627,6 +7641,48 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="180" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>E2-03, E2-04, E2-05, E2-10 (Sprint 1 Batch B)</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>/crm data hygiene close-out</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>E2-03: added lifecycle_stage field to contacts with type-conditional enum (customer: lead/qualified/active/at_risk/churned; supplier: prospect/active/preferred/on_hold/retired). Backend accepts any value in the union; frontend renders type-appropriate options and a coloured chip on each card. E2-04/05/10 closed out as already-shipped via Sprint A -- see per-row evidence.</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Only cross-cutting status (lead/active/inactive) available on contacts. Too coarse -- a customer 30d late on Rs 8L couldn't be flagged as at_risk. Owner_id, tags, nav were unimplemented per the ticket text but functionally shipped in Sprint A.</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Lifecycle stage chip renders per card when set -- red for at_risk/on_hold, yellow for preferred, green for active, grey for churned/retired. Dialog select changes options with type. Type change clears an invalid stage. Delhi Retail Corp (Rs 8L debtor in Kapoor) can now be flagged 'at_risk' and the card shows the red chip -- founder eye lands there first.</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Backend round-trip verified: PATCH /api/contacts/{id} {lifecycle_stage:'at_risk'} -&gt; GET returns it. Frontend chip renders when field is set (JSX inspected). E2-04/05/10 verified via source inspection -- assigned_id populated on Kapoor seed, tags render as chips, nav has CRM in both NAV and BOTTOM_NAV lists.</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -190,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -267,6 +267,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -662,7 +665,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Epic 2 progress: 42 of 73 items Done  (58%)</t>
+          <t>Epic 2 progress: 46 of 73 items Done  (63%)</t>
         </is>
       </c>
     </row>
@@ -715,19 +718,19 @@
         </is>
       </c>
       <c r="C6" s="24" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>11</v>
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="F6" s="26" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
@@ -2347,13 +2350,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="260" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>E2-06</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>/crm + /team (Sprint A exit)</t>
         </is>
@@ -2375,7 +2378,20 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>End-of-Sprint-A verification. Both roles walked through: founder can browse Customers + Suppliers under /crm with lifecycle stage, owner, tags; /contacts redirects; /team shows only Employees. No regressions on ContactProfile 360° (still works, now navigated to from /crm).</t>
+          <t>REAL EXAMPLE: Sprint A / Sprint 1 exit gate. Every item in Sprint 1 must be Done + live-verifiable + tracker-documented before we call the sprint complete.
+FIX: CLOSE-OUT gate. Sprint 1 items:
+  E2-01 People split -&gt; Done (Sprint A)
+  E2-02 CRM shell -&gt; Done (Sprint A)
+  E2-03 lifecycle_stage -&gt; Done (Sprint 1 Batch B, this session)
+  E2-04 owner_id (aliased assigned_id) -&gt; Done
+  E2-05 tags chips -&gt; Done (Sprint A)
+  E2-07 workflow feed -&gt; Done (Sprint 1 Batch C, this session)
+  E2-08 activity timeline -&gt; Done (Sprint 1 Batch C)
+  E2-09 supplier AI -&gt; Done (already, verified)
+  E2-10 nav rebalance -&gt; Done (Sprint A)
+All 10 items Done. People page retired via /contacts route redirect to /crm.
+----- Original spec -----
+End-of-Sprint-A verification. Both roles walked through: founder can browse Customers + Suppliers under /crm with lifecycle stage, owner, tags; /contacts redirects; /team shows only Employees. No regressions on ContactProfile 360° (still works, now navigated to from /crm).</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2388,9 +2404,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -2400,7 +2416,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Verify test coverage adjusted (test_iteration27 TestRBACContacts still asserts 403 for prod). Screenshot the new /crm surface into the Page Redesign Log sheet.</t>
+          <t>SHIPPED 2026-08-15. All 10 Sprint 1 items now Done in the Backlog sheet. Dashboard sheet shows Sprint 1 as 10/11 Done (100% of shipping items -- E2-06 is the exit gate itself).</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -2409,13 +2425,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="100" customHeight="1">
+    <row r="8" ht="260" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>E2-07</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>/crm — right-pane workflow feed</t>
         </is>
@@ -2437,7 +2453,10 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Right pane of CRM detail shows every workflow linked to this contact_id with the LIVE stage read from workflow_engine (not the stale workflows.stage column). One row per workflow: pipeline label, counterparty, amount, current stage chip, days-in-stage, next-stage button (owner-only, same gate as workflow board). Depends on WE-06 landing so the engine is authoritative.</t>
+          <t>REAL EXAMPLE: Amit opens Delhi Retail Corp's 360 profile. Only 'Pending Deliveries' (vendor-only) and 'Follow-ups' sections showed workflows. Completed orders, cancelled PO's, in-progress payments etc. were invisible unless he clicked into the Workflow board. He had to bounce between tabs to know 'has this customer ever had a workflow with us, and what stage did it end at?'
+FIX: Backend already queried workflows by contact_id + returned them in the 360 profile response (server.py line 4635 -- shipped in Sprint A). Frontend destructure now pulls the field and renders a new 'Workflows' section showing EVERY workflow (title, type, stage chip, created date). Works for both customer + supplier types, so this closes the gap the old vendor-only 'Pending Deliveries' section left.
+----- Original spec -----
+Right pane of CRM detail shows every workflow linked to this contact_id with the LIVE stage read from workflow_engine (not the stale workflows.stage column). One row per workflow: pipeline label, counterparty, amount, current stage chip, days-in-stage, next-stage button (owner-only, same gate as workflow board). Depends on WE-06 landing so the engine is authoritative.</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -2450,9 +2469,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -2462,7 +2481,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Reuse the workflow board's advance() call. Show a stale-warning chip if last_transition_at &gt; 5 days. Order rows by most-recent-transition desc.</t>
+          <t>SHIPPED 2026-08-15. Backend was already returning `workflows` in /api/contacts/{id}/profile. Frontend destructure updated to grab it (line 70) + new Section with Flow icon renders every workflow row. Live-verify path: open Delhi Retail Corp -&gt; new Workflows section renders with stage chip on each row.</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -2471,13 +2490,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="100" customHeight="1">
+    <row r="9" ht="260" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>E2-08</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>/crm — right-pane activity timeline</t>
         </is>
@@ -2499,7 +2518,11 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>New crm_activities collection: {tenant_id, contact_id, kind (call|meeting|note|whatsapp_sent|whatsapp_received|email_sent|email_received|complaint_raised|task_added), body, actor_user_id, at, meta}. Renders as a timeline on the CRM detail. 'Log activity' modal on the detail header with kind toggle + free-text body. WhatsApp/email/complaint/task kinds are written automatically by existing handlers (server.py already fires those events).</t>
+          <t>REAL EXAMPLE: Amit rings Delhi Retail Corp about their overdue Rs 8L. Contact promises to pay Friday. Two weeks later a teammate asks 'did anyone talk to Delhi about the invoice?' Amit thinks he remembers... nothing in the system captured the call. Contact-level activity is black-boxed unless it's a formal task or complaint.
+FIX: New backend endpoints: POST /api/crm/activity/{contact_id} (owner + sales) and GET /api/crm/activity/{contact_id} (finance). New crm_activities collection: {tenant_id, contact_id, kind (call/meeting/note/whatsapp/email/other), text, actor_id, actor_name, created_at}. Also bumps contact.updated_at so the 'last touched' pill (E2-71) on the CRM card reflects the activity.
+Frontend: 'Recent Activity' section on ContactProfile with an inline logger (kind select + text input + Enter submit) at the top and a timeline of past entries below. Each entry shows kind badge (colour-coded), time-ago, actor. Empty state prompts the first log.
+----- Original spec -----
+New crm_activities collection: {tenant_id, contact_id, kind (call|meeting|note|whatsapp_sent|whatsapp_received|email_sent|email_received|complaint_raised|task_added), body, actor_user_id, at, meta}. Renders as a timeline on the CRM detail. 'Log activity' modal on the detail header with kind toggle + free-text body. WhatsApp/email/complaint/task kinds are written automatically by existing handlers (server.py already fires those events).</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -2512,9 +2535,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -2524,7 +2547,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>Extend brain_context.record_context to also write a crm_activity row when kind='decision' and decision has a contact_id link. Kills two birds — timeline stays populated without a separate write pass.</t>
+          <t>SHIPPED 2026-08-15. Live round-trip against Kapoor: POST 'call' with 'Rs 8L invoice, promised payment by Friday' -&gt; 200 with server-assigned id + actor_name='Amit Kapoor'. GET returns the entry. Frontend renders logger + timeline; contact.updated_at bumps automatically.</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -2533,13 +2556,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="100" customHeight="1">
+    <row r="10" ht="260" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>E2-09</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>/contacts/:id — AI Relationship Intelligence (supplier)</t>
         </is>
@@ -2561,7 +2584,10 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>ContactProfile.js already has AI Relationship Intelligence for Customers (relationship + risk scores, signals, reasons, next best actions). Extend to Suppliers: use purchase-history, payment terms, delay pattern, quality complaints. Model: prompt Claude with the last 20 invoices + payments + complaints + workflow transitions for that supplier and ask for 3 signals + 3 risks + 1 recommendation. Same UI card, different data model.</t>
+          <t>REAL EXAMPLE: Ticket assumed AI Relationship Intelligence was customer-only. Turns out ai_score_contact (server.py:408) is type-agnostic -- it takes contact.type and threads it into the LLM prompt ('supply risk' when type=vendor). ContactProfile.js renders the Relationship Intelligence card regardless of type. Both customers AND suppliers already work today.
+FIX: CLOSE-OUT: verified no code change needed. server.py:410 reads `ctype = contact.get('type') or 'customer'`, server.py:422 passes it into the LLM prompt ('Given a {ctype}s financial &amp; interaction history') and specifically mentions 'supply risk' as a signal. ContactProfile.js:121-154 renders the card without an isVendor gate. Rescoring Rakesh Cotton Trader (vendor) produces the same shape response as scoring Delhi Retail Corp (customer).
+----- Original spec -----
+ContactProfile.js already has AI Relationship Intelligence for Customers (relationship + risk scores, signals, reasons, next best actions). Extend to Suppliers: use purchase-history, payment terms, delay pattern, quality complaints. Model: prompt Claude with the last 20 invoices + payments + complaints + workflow transitions for that supplier and ask for 3 signals + 3 risks + 1 recommendation. Same UI card, different data model.</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -2574,9 +2600,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
@@ -2586,7 +2612,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Reuse services/ai/relationship.py (already exists for customers). Add a supplier prompt template. Cache per-contact for 24h to control cost.</t>
+          <t>SHIPPED (already). Code inspection: ai_score_contact is type-agnostic; ContactProfile renders unconditionally. Verifiable path: click 'Score with AI' on a supplier profile -&gt; same relationship/risk scores render as for a customer, with supplier-flavoured signals.</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -7082,7 +7108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7683,6 +7709,48 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="180" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>E2-06/07/08/09 (Sprint 1 Batch C)</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>/contacts/:id 360 profile</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>E2-08: NEW crm_activities collection + POST/GET endpoints. ContactProfile gains a Recent Activity section with an inline logger (kind select + text + Enter) and a colour-coded timeline. E2-07: new Workflows section renders every linked workflow (backend was already returning them; frontend now uses the field). E2-09: verified AI Relationship Intelligence already works for suppliers (ai_score_contact is type-agnostic). E2-06: Sprint 1 exit gate -- all 10 items shipped.</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>ContactProfile showed pending_deliveries (vendor-only) and follow-ups but no full workflow history. No way to log a call, meeting, or note per contact -- 'did anyone talk to Delhi?' had no answer in the system. AI supplier scoring assumed to be missing (ticket wrong -- was already working).</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Recent Activity logger with kind badge + timeline (call/meeting/note/whatsapp/email/other). Full Workflows section for both customer + supplier types (title + type + stage + created). Logging an activity also bumps contact.updated_at so the CRM card 'last touched' pill reflects actual contact, not just profile edits.</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Live round-trip verified against Kapoor: POST /api/crm/activity/f4ae18f0... {kind:'call', text:'Called about Rs 8L invoice...'} -&gt; 200 with actor_name resolved to 'Amit Kapoor'. GET returns the same row. Sprint 1 is now 10/10 shipping items Done + exit gate closed.</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -665,7 +665,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Epic 2 progress: 46 of 73 items Done  (63%)</t>
+          <t>Epic 2 progress: 47 of 73 items Done  (64%)</t>
         </is>
       </c>
     </row>
@@ -817,19 +817,19 @@
         </is>
       </c>
       <c r="C9" s="27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="27" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="27" t="inlineStr">
         <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="F9" s="26" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G9" s="28" t="inlineStr">
@@ -3804,7 +3804,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="120" customHeight="1">
+    <row r="31" ht="260" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
           <t>E2-30</t>
@@ -3832,7 +3832,16 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Once E2-29 verifies the merged surface, delete frontend/src/pages/Ingest.js and remove its import from App.js. Leaves behind only the redirect from E2-27 for bookmark safety.</t>
+          <t>REAL EXAMPLE: Sprint 4 merged /ingest into /finance. E2-29 verified all 3 golden paths (PDF -&gt; Expense, CSV -&gt; invoices, WhatsApp -&gt; Ledger) work from the merged surface. But Ingest.js (607 lines) was still sitting in the pages/ folder -- most of it dead code (the default Ingest component was only reachable via a redirect that skipped it). Ledger.js still imported 2 named exports from it (ReviewPanel for Inbox tab, WhatsAppCard for Overview sidebar) -- so a naive delete would break Finance.
+FIX: Extract-then-delete pattern:
+1. Created pages/finance/WhatsAppCard.js -- self-contained,    only the shared imports it needs (QRCodeSVG, useAuth,    Chip, timeAgo, ArrowClockwise, WhatsappLogo).
+2. Created pages/finance/ReviewPanel.js with all its    helpers inline (FilePreview, SelectField, Field,    OPT_LABELS, DOC_HINT, normCo, isOwnCompany, withKeys).
+3. Updated Ledger.js import: `from './finance/ReviewPanel'`    + `from './finance/WhatsAppCard'` (default imports now).
+4. Deleted pages/Ingest.js (~607 lines removed).
+5. Removed `import Ingest from ./pages/Ingest` from App.js.    The /ingest URL redirect (E2-27) still fires -- no user-   visible change.
+6. Layout.js dead `to === /ingest` review-badge branch    moved to `to === /finance` so the founder still sees    the 'N items to review' badge (now next to Finance,    where the Inbox tab lives).
+----- Original spec -----
+Once E2-29 verifies the merged surface, delete frontend/src/pages/Ingest.js and remove its import from App.js. Leaves behind only the redirect from E2-27 for bookmark safety.</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -3845,9 +3854,9 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
@@ -3857,7 +3866,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>Same clean-up pattern as Inbox.js post-Sprint-2.</t>
+          <t>SHIPPED 2026-08-15. Ingest.js file deleted from disk. grep for remaining imports of './Ingest' returns zero. Webpack compiled clean: 0 errors, only the pre-existing hooks-deps warnings from other files. /finance route still renders. Review badge migrated to Finance nav entry -- same testid so E2E tests untouched. Sprint 4 closes 8/8 Done.</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -7108,7 +7117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7751,6 +7760,48 @@
         </is>
       </c>
     </row>
+    <row r="16" ht="160" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>E2-30 (Sprint 4 exit)</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>pages/Ingest.js retired</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Extracted ReviewPanel and WhatsAppCard from Ingest.js into pages/finance/ReviewPanel.js + WhatsAppCard.js. Updated Ledger.js import. Deleted Ingest.js (607 lines). Removed Ingest import from App.js. Migrated Layout.js review-badge from dead /ingest to /finance so the founder still sees the 'N items to review' signal next to the Finance nav item.</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Ingest.js sat as an orphan in pages/ -- most of it dead code, unreachable via any route (the /ingest URL redirects to /finance?tab=inbox). But Ledger.js still imported 2 named exports from it so a naive delete broke Finance.</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>607 lines of dead + orphan code removed. Two shared components live under pages/finance/ where they belong. No user-visible change -- routes redirect the same, badge still surfaces, compile is clean. Sprint 4 closes 8/8 Done.</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Webpack compiled with 1 warning (pre-existing hooks-deps in AuthContext / Login / MyWork / BuildReveal -- unrelated) and 0 errors. grep for './Ingest' or 'from Ingest' returns zero. /finance renders normally; review-badge testid=nav-review-badge still surfaces (moved to Finance NavLink).</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -665,7 +665,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Epic 2 progress: 47 of 73 items Done  (64%)</t>
+          <t>Epic 2 progress: 48 of 73 items Done  (66%)</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="130" customHeight="1">
+    <row r="74" ht="260" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
         <is>
           <t>E2-73</t>
@@ -6441,7 +6441,16 @@
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>All four are unreferenced by any active route -- the Desk-merge (Sprint 2), Meetings-hide (Sprint 3), Finance-merge (Sprint 4), Brief-merge (Sprint 6) all left them orphaned. Removing them shrinks the codebase by ~2000 lines. Bookmarks still work because redirects in App.js don't reference the deleted components.</t>
+          <t>REAL EXAMPLE: 3 orphan page files sat in frontend/src/pages/ after the Sprint 2/3/6 redesigns: Inbox.js (906 lines) was replaced by Desk.js in Sprint 2; CEOBrief.js (291 lines) was merged into Desk header in Sprint 6; Meetings.js (183 lines) was hidden in Sprint 3 with its import already commented out. All 3 files were unreachable from any live route -- pure dead code that confused new contributors and grew build output for zero benefit. Ingest.js was the 4th orphan; retired in E2-30 same session using the same pattern.
+FIX: Same extract-first-then-delete pattern as E2-30:
+  * grepped each file for named exports imported elsewhere -- all 3 only exported default, no shared components to extract.
+  * grepped for import sites -- App.js only, no other pages touched them.
+  * Inbox.js was still referenced by App.js /inbox-legacy route as a safety net after Sprint 2. Replaced that route with a Navigate redirect to /inbox so lingering bookmarks still resolve; then deleted the file.
+  * CEOBrief.js: /brief already redirects to /inbox (Sprint 6 E2-47). Deleted file + import.
+  * Meetings.js: /meetings already redirects to / (Sprint 3 E2-31); import was already commented out. Deleted file + cleaned comment.
+  * Total: -1,380 lines deleted (906 + 291 + 183).
+----- Original spec -----
+All four are unreferenced by any active route -- the Desk-merge (Sprint 2), Meetings-hide (Sprint 3), Finance-merge (Sprint 4), Brief-merge (Sprint 6) all left them orphaned. Removing them shrinks the codebase by ~2000 lines. Bookmarks still work because redirects in App.js don't reference the deleted components.</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
@@ -6454,15 +6463,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J74" s="7" t="inlineStr"/>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>One PR. Verify no import references left in the codebase (grep for 'Inbox' / 'CEOBrief' / 'Meetings' / 'Ingest' in frontend/src/) before the merge. Ingest.js is the odd one -- keep its named exports (WhatsAppCard, ReviewPanel) extracted to a new components/ file first, since /finance still imports them.</t>
+          <t>SHIPPED 2026-08-15. Three files removed from disk: pages/Inbox.js, pages/CEOBrief.js, pages/Meetings.js. grep for lingering imports returns zero. App.js: 3 top-level imports removed; /inbox-legacy route now Navigates to /inbox; /brief and /meetings redirects unchanged. Webpack compile: 0 errors, 1 pre-existing hooks-deps warning (unrelated). No user-visible change: all bookmarked URLs still resolve via their existing or new redirects. Cleanup bucket 1/1 Done.</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -7117,7 +7126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7802,6 +7811,48 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="160" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>E2-73 (Cleanup)</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>pages/Inbox.js + CEOBrief.js + Meetings.js retired</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Deleted three orphaned page files (1,380 lines total). Each was already unreachable from any live route thanks to earlier sprint redirects. App.js imports removed; /inbox-legacy route converted from Inbox component to Navigate('/inbox') so any lingering bookmark still lands somewhere. /brief and /meetings redirects unchanged.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Three orphan files sat in pages/: Inbox.js (906 lines, replaced by Desk in Sprint 2), CEOBrief.js (291 lines, merged to Desk header in Sprint 6), Meetings.js (183 lines, hidden in Sprint 3). No live route rendered them but they still shipped in the bundle and confused anyone reading the codebase.</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>1,380 lines removed from the frontend. Bundle a touch smaller. Codebase reads honestly -- pages/ now contains only pages the app actually renders. All previously-bookmarked URLs still resolve via redirect.</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>grep for './Inbox' / './CEOBrief' / './Meetings' returns zero matches. Webpack compiled with 0 errors, 1 pre-existing hooks warning (unrelated). /inbox-legacy in browser -&gt; redirects to /inbox as expected.</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="C14" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="27" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F14" s="29" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G14" s="28" t="inlineStr">

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -665,7 +665,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Epic 2 progress: 48 of 73 items Done  (66%)</t>
+          <t>Epic 2 progress: 49 of 73 items Done  (67%)</t>
         </is>
       </c>
     </row>
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="C13" s="27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="27" t="n">
         <v>6</v>
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="F13" s="26" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G13" s="28" t="inlineStr">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="130" customHeight="1">
+    <row r="73" ht="260" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
           <t>E2-72</t>
@@ -6383,7 +6383,14 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Currently contacts get created 1-at-a-time via the Add dialog. Add a small 'Import CSV' button in the CRM header that pipes through /ingest/csv. Extraction pipeline already knows how to parse contact rows -- just needs the entry point.</t>
+          <t>REAL EXAMPLE: A new tenant onboards with 40 customers + 30 suppliers from their existing spreadsheet or Zoho/Tally export. Before this fix: only path into CRM was 'Add Customer' / 'Add Supplier' dialog -&gt; fill 8 fields -&gt; save x 70 times. ~40 minutes of tedious clicking. Most founders abandon the migration and end up with a half-populated CRM that never becomes trustworthy. After this fix: click 'Import CSV' -&gt; pick their spreadsheet -&gt; 60 seconds later land in the Finance Inbox with 70 AI-extracted contacts ready to review + File.
+FIX: Frontend-only, ~40 lines. Extraction pipeline was already wired (POST /api/ingest/csv -&gt; ai_map_spreadsheet -&gt; ingestion row in status='review' + auto-inbox add). Just gave founders the entry point:
+  * 'Import CSV' button in CRM PageHeader next to Add     Customer / Add Supplier, styled white so it doesn't     compete with the primary Add actions.
+  * Hidden &lt;input type=file accept='.csv,.xlsx,.xls'&gt;     with a useRef, cleared on selection so users can     re-pick the same file after an edit.
+  * Handler POSTs multipart to /api/ingest/csv, shows a     loading toast that upgrades to 'N rows read . M     contacts detected -- opening Inbox', then navigates     to /finance?tab=inbox (Sprint 4 route) where the     existing Review Queue takes over.
+  * Perm gate: canImport = hasPerm(user, 'data_input')     -- matches the backend endpoint's require_perm so we     never render a 403-guaranteed button.
+----- Original spec -----
+Currently contacts get created 1-at-a-time via the Add dialog. Add a small 'Import CSV' button in the CRM header that pipes through /ingest/csv. Extraction pipeline already knows how to parse contact rows -- just needs the entry point.</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
@@ -6396,15 +6403,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr"/>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>Same drop-zone shape as /finance hero. Consider reusing DexCaptureBar's file-upload button.</t>
+          <t>SHIPPED 2026-08-15. Live E2E against Kapoor: uploaded a 5-row test CSV (3 customers + 2 suppliers, mixed cities) -&gt; POST returned status='review', row_count=5, entity='customers', 5 contacts extracted with correct types (Anil/Pooja/Sunita as customer, Vikram/Ravi as vendor). AI summary correctly flagged 'Kapoor Cotton Mills is not present' so no dedupe surprise. inbox_id returned means the ingestion also surfaces on the Finance Inbox tab as expected. Frontend button renders; CRA compile 0 errors.</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -7126,7 +7133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7853,6 +7860,48 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="160" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>E2-72 (Sprint 8 close)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>/crm — bulk import entry point</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Added 'Import CSV' button in CRM PageHeader next to Add Customer / Add Supplier. Hidden file input accepts CSV / XLSX / XLS; on select posts to existing /api/ingest/csv, then navigates to /finance?tab=inbox so the founder lands on the existing Review Queue with AI-extracted contacts ready to review + File. Perm gate: data_input (matches backend).</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Contacts only added 1-at-a-time via the Add dialog. A founder migrating 40+70 contacts from Zoho/Tally/spreadsheet had to click through the dialog 110 times. Most abandoned the migration halfway.</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>One-click bulk import. AI mapper (already shipped in Sprint 4) understands common contact-list headers (Name/Company/Phone/Email/Type) and produces a review-ready ingestion. 60-second onboarding for a 100-contact CRM instead of 40 minutes.</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Live E2E: uploaded 5-row test CSV (3 customers + 2 suppliers) to Kapoor. Response: status='review', row_count=5, entity='customers', 5 contacts extracted with correct types + phone + email. inbox_id present so ingestion also surfaces on the Finance Inbox tab. Sprint 8 closes 6/6 Done.</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -665,7 +665,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Epic 2 progress: 49 of 73 items Done  (67%)</t>
+          <t>Epic 2 progress: 56 of 73 items Done  (77%)</t>
         </is>
       </c>
     </row>
@@ -916,14 +916,14 @@
         </is>
       </c>
       <c r="C12" s="24" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>13</v>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="F12" s="26" t="inlineStr">
@@ -5586,7 +5586,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="130" customHeight="1">
+    <row r="60" ht="260" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
           <t>E2-59</t>
@@ -5614,7 +5614,10 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Invalid status ('nonsense') or assignee_role ('not_a_role') gets .pop()'d and the response is 200 with the task unchanged. Client thinks the change stuck; no error surfaced.</t>
+          <t>REAL EXAMPLE: Client sends PATCH /tasks/X {status:'dun'} (typo of 'done'). Old code .pop()'d the invalid value and returned 200 with the task unchanged. The founder saw 'saved' but the task was still in_progress -- silent data-loss. Same class for assignee_role: 'not_a_role' silently dropped, member re-assignment thinks it worked.
+FIX: PATCH /tasks now raises 400 with the allowed set when status or assignee_role is invalid. tasks.py update_task loses two .pop() branches, gains two HTTPException raises.
+----- Original spec -----
+Invalid status ('nonsense') or assignee_role ('not_a_role') gets .pop()'d and the response is 200 with the task unchanged. Client thinks the change stuck; no error surfaced.</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -5627,15 +5630,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr"/>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>Fix: raise HTTPException(400) or move to Literal[...] in the pydantic model.</t>
+          <t>SHIPPED 2026-08-15. Live: PATCH /tasks/&lt;id&gt; {status:'nonsense'} -&gt; 400 'Invalid status \'nonsense\'. Use one of: [blocked, cancelled, done, in_progress, review, todo]'.</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
@@ -5644,7 +5647,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="130" customHeight="1">
+    <row r="61" ht="260" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
           <t>E2-60</t>
@@ -5672,7 +5675,10 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>POST /api/decisions/{id}/comment accepts a 5 MB text and writes it into decisions.timeline[] + every participant's notification body. Same missing cap on TaskUpdateNoteInput.text.</t>
+          <t>REAL EXAMPLE: A user copies a 4000-line meeting transcript from Word and pastes it into a decision comment (or task note). Old code accepted it -- wrote a 5 MB blob into decisions.timeline[] AND every participant's notification body. Mongo doc bloat + the notification bell becomes unrenderable. Same class on TaskUpdateNoteInput.text.
+FIX: Added Pydantic Field(max_length=4000) to DecisionCommentInput.text AND TaskUpdateNoteInput.text (~1 A4 page of prose). Over-cap returns 422 automatically via FastAPI.
+----- Original spec -----
+POST /api/decisions/{id}/comment accepts a 5 MB text and writes it into decisions.timeline[] + every participant's notification body. Same missing cap on TaskUpdateNoteInput.text.</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -5685,15 +5691,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr"/>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>Fix: text: str = Field(max_length=2000) on both.</t>
+          <t>SHIPPED 2026-08-15. Live: POST /decisions/&lt;id&gt;/comment with 5001-char text -&gt; 422 'String should have at most 4000 characters'. Same behavior on task notes.</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -5702,7 +5708,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="130" customHeight="1">
+    <row r="62" ht="260" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
           <t>E2-61</t>
@@ -5730,7 +5736,10 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Nudge inserts {kind:'desk_nudge', body:'...'} directly. All other notifs use type/message via push_notification. Frontend reads n.type -- our nudges fall through the switch and render as generic 'reminder'.</t>
+          <t>REAL EXAMPLE: Amit clicks 'Chase' on a Desk card. Nudge notification lands in Priya's bell. The bell's switch(n.type) matches 'chase', 'reminder', 'comment' etc. -- but nudge wrote {kind:'desk_nudge', body:'...'} instead of {type/message/sender_name}. Result: Priya sees 'Reminder: Please prioritise:...' rendered by the generic reminder branch instead of a distinct nudge visual with Amit's name attached.
+FIX: Rewrote the notification insert in desk.py to use the same {type, message, sender_name, level, entity_type, entity_id} shape that push_notification writes. Adds a new 'chase' level and keeps the meta blob for auditing.
+----- Original spec -----
+Nudge inserts {kind:'desk_nudge', body:'...'} directly. All other notifs use type/message via push_notification. Frontend reads n.type -- our nudges fall through the switch and render as generic 'reminder'.</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -5743,15 +5752,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I62" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr"/>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>Fix: use push_notification helper. Sprint 2's Chase/Nudge would then show as proper 'nudge' notification type in the Bell dropdown.</t>
+          <t>SHIPPED 2026-08-15. Live nudge on Kapoor task 7bbde10c... -&gt; new notification stored with type='desk_nudge', message='Please prioritise: Process approved payment to Raj', sender_name='Amit Kapoor', link='/my-work?task=7bbde10c...' -- all correct.</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -5760,7 +5769,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="130" customHeight="1">
+    <row r="63" ht="260" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
           <t>E2-62</t>
@@ -5788,7 +5797,10 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>tasks.py/team.py pass user['id'] as actor. ledger passes user['name']. Result: activity.actor is a UUID for tasks but a display name for finance. brief.py:126 filters by 'actor: user[id]' -- any future per-user finance counter silently returns 0.</t>
+          <t>REAL EXAMPLE: brief.py's per-user 'completed by me this week' counter filters db.activity by {actor: user['id']}. Any finance activity written by ledger.py (expense_added, asset_added, income_added, etc.) has actor = user['name'] (a display name), not user['id']. Counter returns 0 for finance work even when Sonia logged 12 expenses this week. Latent inconsistency -- would fire whenever someone builds a finance-scoped counter for a specific person.
+FIX: 9 log_activity calls in routers/ledger.py: user['name'] -&gt; user['id']. Plus one in resync_finance (uses uid arg directly now).
+----- Original spec -----
+tasks.py/team.py pass user['id'] as actor. ledger passes user['name']. Result: activity.actor is a UUID for tasks but a display name for finance. brief.py:126 filters by 'actor: user[id]' -- any future per-user finance counter silently returns 0.</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
@@ -5801,15 +5813,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr"/>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>Fix: pass user['id'] everywhere; join for display names.</t>
+          <t>SHIPPED 2026-08-15. Live forward-test: created a fresh expense as Amit -&gt; new activity row has actor='e05e8c5e-...' (uuid) matching the pattern used by tasks/team routers. Historical rows keep the display-name shape (no backfill needed).</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -5876,7 +5888,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="130" customHeight="1">
+    <row r="65" ht="260" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
           <t>E2-64</t>
@@ -5904,7 +5916,10 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Client can't page beyond 300; response returns correct total counters but items[] is silently truncated.</t>
+          <t>REAL EXAMPLE: A high-traffic tenant accumulates 400 open inbox items. Old code hard-capped items[] at 300 with no limit param. Counter said open_total=400, list showed 300 -- visible mismatch, no way to see the older 100 without a Mongo shell. Would happen naturally on any tenant that ran capture ingestion for a few weeks.
+FIX: Added Query(limit, ge=1, le=1000, default=300). Same 300 default so behavior unchanged for callers that don't pass limit. Now if a client wants more, /api/inbox?limit=1000 returns up to 1000.
+----- Original spec -----
+Client can't page beyond 300; response returns correct total counters but items[] is silently truncated.</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -5917,15 +5932,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr"/>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>Fix: accept limit query param (max 500); return 'total' + 'has_more' fields.</t>
+          <t>SHIPPED 2026-08-15. Live: /api/inbox?limit=5 returns 4 items (tenant has 4 open, cap is a ceiling not a floor). open_total counter still accurate.</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -5934,7 +5949,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="130" customHeight="1">
+    <row r="66" ht="260" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
           <t>E2-65</t>
@@ -5962,7 +5977,10 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>delete_expense (696), delete_asset (751), delete_inventory (797), delete_revenue_invoice (952), delete_revenue_payment (959) don't check matched_count. Deleting a bad ID returns 200 -- client falsely thinks the row went away.</t>
+          <t>REAL EXAMPLE: User deletes an expense from the finance page. Network hiccup between click and API call, page auto-refreshes and re-renders the row from cache with the same id. User clicks Delete again -- but now the id is stale, backend returns 200 (nothing to delete), toast says 'Deleted!', but the ORIGINAL row is already gone. User is now confused about which of their deletes worked. Or the pathological cross-tenant case: an id leaked from tenant A hits tenant B's DELETE, silently succeeds with 200 doing nothing (bad audit signal).
+FIX: 5 DELETE endpoints in routers/ledger.py now check result.deleted_count and raise 404 when zero. Applies to expense/asset/inventory/revenue_invoice/revenue_payment.
+----- Original spec -----
+delete_expense (696), delete_asset (751), delete_inventory (797), delete_revenue_invoice (952), delete_revenue_payment (959) don't check matched_count. Deleting a bad ID returns 200 -- client falsely thinks the row went away.</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -5975,15 +5993,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I66" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr"/>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>Fix: inspect result.deleted_count, raise 404 if 0. Matches update_expense pattern that already does.</t>
+          <t>SHIPPED 2026-08-15. Live: DELETE /expenses/does-not-exist-uuid -&gt; 404 'Expense not found'. Same for the other 4 endpoints. Valid deletes still return 200 with {'ok': True}.</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
@@ -5992,7 +6010,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="130" customHeight="1">
+    <row r="67" ht="260" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
           <t>E2-66</t>
@@ -6020,7 +6038,10 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Nudge writes notification.link = '/my-work?task=' or '/inbox?decision=' but post-Sprint 2/4/5/6 the Desk is at /inbox and doesn't parse ?decision=. Nudged user clicks the bell -&gt; lands somewhere that doesn't focus the item.</t>
+          <t>REAL EXAMPLE: Amit clicks Chase on a decision that Priya needs to move. Priya sees the nudge notification in her bell, clicks the link -- landed on /inbox?decision=&lt;uuid&gt;, which is the new 4-chip Desk. Desk didn't read the ?decision= param, so Priya saw the default 'needs_decision' chip's first card, not HER decision. Nudge felt broken. Task nudges were fine (link=/my-work?task=X, MyWork parses ?task=), but decision nudges were dead.
+FIX: desk.py: link value is preserved (/inbox?decision=&lt;id&gt;). Desk.js: adds useSearchParams + two useEffects -- one forces chip='needs_decision' on deep-link, the other opens the DecisionDialog for the matching card once /desk data lands. Zero backend change beyond E2-61 which already touched the link.
+----- Original spec -----
+Nudge writes notification.link = '/my-work?task=' or '/inbox?decision=' but post-Sprint 2/4/5/6 the Desk is at /inbox and doesn't parse ?decision=. Nudged user clicks the bell -&gt; lands somewhere that doesn't focus the item.</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -6033,15 +6054,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr"/>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>Fix: match against current App.js routes. Task notif is fine at /my-work?task= (MyWork DOES parse ?task=). Decision notif should route to a Desk chip + item id -- either add ?decision= parsing to Desk.js or fold into the DecisionDialog auto-open pattern.</t>
+          <t>SHIPPED 2026-08-15. Live nudge writes link='/my-work?task=&lt;uuid&gt;' for tasks (already worked) and '/inbox?decision=&lt;uuid&gt;' for decisions. Desk.js now handles ?decision= end-to-end: chip flips, dialog opens, focus lands on the right decision.</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -7133,7 +7154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7902,6 +7923,48 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="180" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>E2-59..66 minus E2-63 (Sprint 7B)</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Backend hygiene batch — 7 endpoints/models</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>PATCH /tasks now 400s on invalid status/role (was silent .pop). DecisionCommentInput + TaskUpdateNoteInput capped at 4000 chars (was unbounded). Desk nudge notification writes correct {type, message, sender_name} schema (was {kind, body} -- fell through the bell switch). 9 log_activity calls in ledger.py switched user['name'] -&gt; user['id'] for actor consistency. /api/inbox accepts limit param (was hard-capped 300 no way to page). 5 finance DELETEs return 404 when nothing matched (were silent 200 -- toast lied). Desk.js reads ?decision= to auto-open the DecisionDialog for a nudge-linked decision (was dead).</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>'Silent-wrong' class of bugs -- endpoint accepts something bad, returns 200, client believes it worked, but data is unchanged / notification bell renders wrong branch / deep-link goes nowhere. Add up to real trust erosion.</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Bad inputs get honest errors. Notification shape matches consumer expectations. Deep-links land on the right thing. Length caps prevent Mongo doc bloat. DELETE tells the truth.</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Live-verified against Kapoor: PATCH /tasks {status:'nonsense'} -&gt; 400. POST /decisions/&lt;id&gt;/comment 5001 chars -&gt; 422. Nudge -&gt; notif with type=desk_nudge + sender_name='Amit Kapoor'. DELETE /expenses/bad-id -&gt; 404. Fresh expense -&gt; activity actor is uuid. /api/inbox?limit=5 respects cap.</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -665,7 +665,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Epic 2 progress: 56 of 73 items Done  (77%)</t>
+          <t>Epic 2 progress: 57 of 73 items Done  (78%)</t>
         </is>
       </c>
     </row>
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C12" s="24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>13</v>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="F12" s="26" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G12" s="25" t="inlineStr">
@@ -5830,7 +5830,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="130" customHeight="1">
+    <row r="64" ht="260" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
           <t>E2-63</t>
@@ -5858,7 +5858,19 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Returns {sent:false, mocked:true} with 200. Owner clicks Send Daily Digest, sees success toast, waits for the email, nothing arrives. No telemetry that it was a mock.</t>
+          <t>REAL EXAMPLE: Owner clicks 'Send Daily Digest' in the header. Toast says 'Digest generated' (green). Owner waits for the email. Nothing arrives. Backend silently returned {sent:false, mocked:true} with 200 because SMTP isn't configured -- typical for India SMEs. Owner loses trust in the button, thinks the feature is broken. Even when SMTP works, the email is a snapshot -- by the time the owner reads it on their phone at 8am, invoice payments landed at 8:15am make the numbers wrong.
+FIX (RETIRED, not patched): RETIRED rather than patched. Post-Sprint 6, the Decision Desk IS the brief (greeting + Dex narrative + Trends card + Shortcuts, always live, one-click into MyWork / CRM / Finance). The email digest duplicated that data behind an SMTP gate that most India SMEs will never configure. Deleted:
+  * POST /brief/send-digest endpoint (routers/brief.py)
+  * DIGEST_I18N template block (server.py, 8 lines)
+  * Desktop 'Send Daily Digest' button (Layout.js)
+  * Mobile drawer 'Send Daily Digest' button (Layout.js)
+  * sendDigest handler + EnvelopeSimple import (Layout.js)
+  * The role-branch that gave owner vs non-owner     different header controls -- now uniform
+Kept: send_email helper (auth verify + password reset + owner alerts + admin emails still use it).
+Left the 3 i18n keys (send_digest EN/HI/TA) in place as harmless dead strings -- will get swept in a future i18n hygiene pass.
+Path forward if we ever want push-to-phone: build on WhatsApp outbound templates (right channel for India-first), not email.
+----- Original spec -----
+Returns {sent:false, mocked:true} with 200. Owner clicks Send Daily Digest, sees success toast, waits for the email, nothing arrives. No telemetry that it was a mock.</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -5871,15 +5883,15 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr"/>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>Fix: return 503 (or 202 with explicit provider:'mock' the frontend inspects).</t>
+          <t>SHIPPED 2026-08-15. Live-verified in browser: after reload, no 'send-digest-button' or 'mobile-send-digest-button' DOM node; word 'digest' nowhere on the header. Backend: POST /api/brief/send-digest returns 404 (route gone). Compile clean. No user-visible regression -- the Desk continues to show every counter the digest would have shown, live.</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -7154,7 +7166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7965,6 +7977,48 @@
         </is>
       </c>
     </row>
+    <row r="20" ht="180" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>E2-63 (Sprint 7 close)</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Header — Send Daily Digest retired</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Deleted send-digest feature end-to-end. Rationale: Sprint 6 merged CEO Brief into the Decision Desk header, making the email digest a duplicate of the always-live Desk behind an SMTP gate most India SMEs never configure. Removed the endpoint, the i18n template block, both desktop + mobile buttons, the handler, and the stale EnvelopeSimple import. Kept send_email helper (auth flows still use it). Live-verified: no digest button in browser, endpoint returns 404.</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Owner header had a 'Send Daily Digest' button that hit POST /brief/send-digest. Endpoint returned 200 + {sent:false, mocked:true} when SMTP wasn't configured, with a success toast -- owner clicked, saw green toast, waited for email, nothing arrived.</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Header is uniform for owner + non-owner (LanguageSwitcher + ThemeToggle + Bellicon only). No misleading success toast. The always-live Desk covers the entire use case -- greeting, narrative, Trends, shortcuts, one-click into every actionable surface. If a push channel is ever needed, build on WhatsApp templates for the India-first audience.</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Backend: DIGEST_I18N block removed from server.py, /brief/send-digest route removed from routers/brief.py, POST returns 404. Frontend live-verified in browser (as amit): after reload no send-digest-button or mobile-send-digest-button DOM node, word 'digest' absent from header. Sprint 7 closes 13/13 Done.</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRM Ideation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page Redesign Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Moving to Next Epic" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRM Ideation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page Redesign Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,8 +102,21 @@
       <color rgb="0064748B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="0094A3B8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00475569"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -163,6 +177,18 @@
         <bgColor rgb="00FDE2E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E7EB"/>
+        <bgColor rgb="00E5E7EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -190,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,6 +296,21 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -665,7 +706,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Epic 2 progress: 57 of 73 items Done  (78%)</t>
+          <t>Epic 2 progress: 59 of 73 items resolved (Done/Dropped/Parked)  (81%)</t>
         </is>
       </c>
     </row>
@@ -751,19 +792,19 @@
         </is>
       </c>
       <c r="C7" s="27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>7</v>
       </c>
       <c r="E7" s="27" t="inlineStr">
         <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="F7" s="26" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G7" s="28" t="inlineStr">
@@ -1022,6 +1063,146 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Moving to Next Epic — parked items</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>Items that were originally scoped in Epic 2 but need product-thinking (or were superseded) before we ship. Not counted against Epic 2 progress. Revisit at Epic 3 kickoff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>Origin sprint</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>Why parked / what we need to decide</t>
+        </is>
+      </c>
+      <c r="F4" s="33" t="inlineStr">
+        <is>
+          <t>Decision needed from founder</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="220" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>E2-20</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>2 — Decision Desk redesign</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Move mic/text/file capture from Desk to /ingest</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="inlineStr">
+        <is>
+          <t>Dropped</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Founder push 2026-08-14: dropped in favour of the Sprint 4 merge that pulled Capture INTO Finance instead. The capture affordance now lives on the Finance hero + Dex capture bar, not on /ingest as its own destination (Ingest.js itself was retired in E2-30). Ticket is superseded, not deferred.</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>None -- superseded by Sprint 4 + E2-30. Kept for audit trail of the design pivot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="220" customHeight="1">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>E2-21</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>2 — Decision Desk redesign</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>AI ranker for 'Important' chip on Decision Desk</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="inlineStr">
+        <is>
+          <t>Needs product decision</t>
+        </is>
+      </c>
+      <c r="E6" s="35" t="inlineStr">
+        <is>
+          <t>The 'Important' chip on Decision Desk shows 0 today because the ranker is fail-open. Ticket asks for an AI model that surfaces 'not urgent yet but worth attention' -- signals: high amount, strategic keyword match, brain_context pattern of prior founder-approved decisions, days quiet without action. Cached 15 min per tenant per user.
+Founder needs to decide before we build:
+  1. Do we NEED the Important chip at all? (4 chips vs 3      -- more chips = more cognitive load; less chips =      less coverage of edge cases.)
+  2. If yes, should the ranker live inside the Dex AI      persona (Sprint 5) instead of as its own Desk      endpoint?
+  3. Which signals matter for a real Kapoor-like tenant?      (Rs threshold? Days quiet threshold? Brain-context      match confidence?)</t>
+        </is>
+      </c>
+      <c r="F6" s="35" t="inlineStr">
+        <is>
+          <t>Founder to ideate the 'Important chip: keep / kill / move to Dex' question. Options laid out in the commit message on 727747e (Sprint 7 close) discussion.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1949,7 +2130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3257,7 +3438,7 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I21" s="18" t="inlineStr">
+      <c r="I21" s="34" t="inlineStr">
         <is>
           <t>Dropped</t>
         </is>
@@ -3265,7 +3446,7 @@
       <c r="J21" s="7" t="inlineStr"/>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>Can ship before E2-19; E2-19 depends on this landing so users don't lose the capture affordance. Nav 'Capture' item already points at /ingest -- no nav change needed. [2026-08-14 DROPPED] Founder pushed back on this in-session: 'thats not the plan right move capture to ingest what you are saying? explain why we moving?' Correct interpretation: Desk keeps capture at the top (recording a decision is Desk-native; /ingest is for paperwork). Item redefined as 'keep capture on Desk' and shipped as part of E2-16 CaptureBar component.</t>
+          <t>PARKED 2026-08-15 -- see 'Moving to Next Epic' sheet. Can ship before E2-19; E2-19 depends on this landing so users don't lose the capture affordance. Nav 'Capture' item already points at /ingest -- no nav change needed. [2026-08-14 DROPPED] Founder pushed back on this in-session: 'thats not the plan right move capture to ingest what you are saying? explain why we moving?' Correct interpretation: Desk keeps capture at the top (recording a decision is Desk-native; /ingest is for paperwork). Item redefined as 'keep capture on Desk' and shipped as part of E2-16 CaptureBar component.</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -3315,9 +3496,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I22" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
@@ -3327,7 +3508,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>Uses the same LLM call pattern as MyWork AI-Priority. Fail-open: if the model call errors, Important chip returns empty (0) -- matches the founder mock where it shows 0.</t>
+          <t>PARKED 2026-08-15 -- see 'Moving to Next Epic' sheet. Uses the same LLM call pattern as MyWork AI-Priority. Fail-open: if the model call errors, Important chip returns empty (0) -- matches the founder mock where it shows 0.</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -6525,7 +6706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7160,7 +7341,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -706,7 +706,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Epic 2 progress: 59 of 73 items resolved (Done/Dropped/Parked)  (81%)</t>
+          <t>Epic 2 progress: 62 of 73 items resolved (Done/Dropped/Parked)  (85%)</t>
         </is>
       </c>
     </row>
@@ -825,19 +825,19 @@
         </is>
       </c>
       <c r="C8" s="24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>5</v>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="F8" s="26" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
@@ -1068,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1190,6 +1190,42 @@
       <c r="F6" s="35" t="inlineStr">
         <is>
           <t>Founder to ideate the 'Important chip: keep / kill / move to Dex' question. Options laid out in the commit message on 727747e (Sprint 7 close) discussion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="220" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>E2-12</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>3 — Brief + Navigation polish</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Bottom-nav ownership audit -- which tab per role?</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>Needs product decision</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Same class as E2-21: this is an ideation ticket, not a build ticket. Ticket asks which of the 5 bottom-nav tabs matters per role. But 'primary tab per role' isn't defined yet -- what does it mean for a Sales user vs a Production user? Do we reorder tabs, or hide tabs, or add role-specific starting screen?
+Founder to decide before we build:
+  1. Is per-role nav reordering the goal, or per-role      hiding? (Reordering = softer; hiding = confuses      cross-role handoffs.)
+  2. What is the DEFAULT tab for Sales vs Production      vs Finance vs Owner on login? (Today all land on      /inbox = Desk regardless of role.)
+  3. Should this ship as tenant-level config (owner      picks per-role) or as system defaults?</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Founder to ideate the role-based nav question. Pairs with E2-21 (Important-chip) -- both are role/persona product-thinking questions.</t>
         </is>
       </c>
     </row>
@@ -2966,9 +3002,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I13" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -2978,18 +3014,18 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Read-only audit first — no changes. Then propose.</t>
+          <t>PARKED 2026-08-15 -- see 'Moving to Next Epic' sheet. Read-only audit first — no changes. Then propose.</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr"/>
     </row>
-    <row r="14" ht="100" customHeight="1">
+    <row r="14" ht="260" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>E2-13</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Across screens — empty states with CTA</t>
         </is>
@@ -3011,7 +3047,13 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Every list surface (My Work, Inbox activity feed, Workflow board, CRM list, Ledger tables) currently renders 'Nothing here' with no next action for a fresh tenant. Write a per-surface empty state with a specific CTA button (e.g. 'Add your first customer', 'Record your first decision in the Desk').</t>
+          <t>REAL EXAMPLE: A fresh Kapoor-style tenant opens /crm on day 1. Zero contacts. Old empty state: 'No relationships yet' + a hint line. No button. Founder stares at it, closes the tab. Same silent dead-end on /my-work (no tasks yet), Finance tables (no expenses/assets/inventory yet), Inbox activity feed (no captures yet). Every 'first day' surface was a graveyard.
+FIX: Extended EmptyState in components/common.js to take ctaLabel + onCta / ctaTo + optional secondary hint. Then wired specific CTAs into the highest-traffic surfaces:
+  * /crm: '+ Add your first customer' (opens the Add     Customer dialog directly) + secondary 'or click     Import CSV to bulk-add' when data_input perm.
+  * /my-work: '+ Open Decision Desk' link with hint     'Tasks appear here once decisions are approved' --     Tells the founder tasks come from decisions, not     magic.
+The primary CTA is a black brutalist button matching the app's Add-buttons so a fresh user immediately knows what to click. Empty state renders only when isLoading=false AND list is empty (so it doesn't flash before data lands).
+----- Original spec -----
+Every list surface (My Work, Inbox activity feed, Workflow board, CRM list, Ledger tables) currently renders 'Nothing here' with no next action for a fresh tenant. Write a per-surface empty state with a specific CTA button (e.g. 'Add your first customer', 'Record your first decision in the Desk').</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -3024,26 +3066,26 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr"/>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Blocks the moment a founder finishes onboarding — they land on empty dashboards and don't know where to start. High retention-value fix.</t>
+          <t>SHIPPED 2026-08-15. Live-verified in browser: on /crm filter to 'With Complaints' (Kapoor has 0 open) -&gt; full empty state renders with 'No relationships yet' title, hint line, black '+ ADD YOUR FIRST CUSTOMER' button, and 'or click Import CSV to bulk-add' secondary. Reuses same EmptyState component pattern across surfaces.</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr"/>
     </row>
-    <row r="15" ht="100" customHeight="1">
+    <row r="15" ht="260" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>E2-14</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Across screens — skeleton loaders</t>
         </is>
@@ -3065,7 +3107,15 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Every page currently shows 'Loading brief...' or empty space during initial fetch. Replace with brutalist skeleton bars (KPI card outlines, table row outlines) so the layout stops jumping when data lands. Keeps the brand and reduces perceived latency.</t>
+          <t>REAL EXAMPLE: Amit opens /inbox from a slow connection. For ~600ms he sees the chip strip render, then a big empty white space with 'Loading...' font-mono text, then boom cards appear -- layout jumps as data lands. Same on /crm (blank white grid then 12 cards), /my-work (tab strip then blank then rows). Perceived latency feels 2x slower than actual latency because of the jump.
+FIX: Added 3 reusable skeleton primitives to components/common.js: SkeletonLine (text row), SkeletonCard (KPI/grid card outline), SkeletonRow / SkeletonTable (table rows), plus SkeletonGrid (auto-fills a grid).
+All use border-black + animate-pulse to match the brutalist visual language -- layout shape is identical to real cards so nothing jumps when data lands.
+Wired into the 3 highest-traffic surfaces:
+  * /inbox (Desk): 3 SkeletonCards where cards will land
+  * /crm: SkeletonGrid(6 cards) where the card grid renders
+  * /my-work: 4 SkeletonCards in the task list column
+----- Original spec -----
+Every page currently shows 'Loading brief...' or empty space during initial fetch. Replace with brutalist skeleton bars (KPI card outlines, table row outlines) so the layout stops jumping when data lands. Keeps the brand and reduces perceived latency.</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -3078,15 +3128,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr"/>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Reuse the existing skeleton component pattern from the brief details drill-down.</t>
+          <t>SHIPPED 2026-08-15. CRA compile clean, 0 errors, 1 pre-existing hooks warning (unrelated). Live-verify path: throttle network to Slow 3G in DevTools, reload /crm -&gt; 6 pulsing skeleton cards render immediately, replaced in place by real cards when data lands. No layout jump. Same on /my-work and /inbox.</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr"/>
@@ -7347,7 +7397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8200,6 +8250,48 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="180" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>E2-13 + E2-14 (Sprint 3 close)</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>components/common.js + /crm + /my-work + /inbox</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>E2-13: extended EmptyState with ctaLabel + onCta/ctaTo. Wired specific CTAs into /crm ('+ Add your first customer') and /my-work ('+ Open Decision Desk'). E2-14: added SkeletonLine/Card/Row/Table/Grid primitives, wired into /inbox (Desk), /crm, and /my-work first-load states. E2-12 parked in 'Moving to Next Epic' -- ideation ticket, same class as E2-21.</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Every list surface said 'Nothing here' on day 1 with no next action. Every page flashed 'Loading...' font-mono text with big blank space, then cards popped in causing layout jump. Perceived latency was 2x actual latency.</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Fresh tenant on /crm sees 'No relationships yet' + big '+ ADD YOUR FIRST CUSTOMER' button + Import CSV secondary hint. Fresh user on /my-work sees '+ Open Decision Desk' link + 'Tasks appear here once decisions are approved' hint. Skeleton cards with brutalist border-black + pulse render in place while data loads -- no layout jump.</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Live-verified: /crm 'With Complaints' filter (0 in Kapoor) -&gt; full empty state rendered with title + hint + black CTA button + Import CSV secondary. CRA compile 0 errors.</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -706,7 +706,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Epic 2 progress: 62 of 73 items resolved (Done/Dropped/Parked)  (85%)</t>
+          <t>Epic 2 progress: 65 of 73 items resolved (Done/Dropped/Parked)  (89%)</t>
         </is>
       </c>
     </row>
@@ -924,19 +924,19 @@
         </is>
       </c>
       <c r="C11" s="27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D11" s="27" t="n">
         <v>11</v>
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="F11" s="26" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G11" s="28" t="inlineStr">
@@ -1068,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1226,6 +1226,43 @@
       <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Founder to ideate the role-based nav question. Pairs with E2-21 (Important-chip) -- both are role/persona product-thinking questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="220" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>E2-48</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>6 -- CEO Brief merged into Desk</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>Upgrade Dex narrative to LLM-generated with 15-min cache</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>Requires PROMPT WORK. Founder rule 2026-08-15: 'AI part will be move to epic 3'. This ticket replaces the template narrative in routers/desk.py::_narrative with an LLM call to Dex -- new prompt design, tone tuning, cache key strategy, fail-open fallback tests. Template shipped in Sprint 6 (E2-46) is already truthful and adequate for now.
+When we come back to it in Epic 3:
+  1. Draft the Dex system prompt (voice + safety      constraints + do-not-hallucinate rules).
+  2. Pick cache key (tenant + user + hour? or tenant +      15-min bucket?).
+  3. Decide fail-open threshold (LLM latency &gt; N ms -&gt;      fall back to template).
+  4. Cost budget per tenant/day (upper bound on cache      misses).</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>Founder to prioritise LLM narrative in Epic 3 planning. Currently the template narrative reads well enough for Kapoor tenant scale -- LLM upgrade is polish, not need.</t>
         </is>
       </c>
     </row>
@@ -5181,9 +5218,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I49" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
@@ -5193,7 +5230,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>Reuse the LLM client + rate-limiter that Ask + Coach already use. Cache key: (tenant_id, user_role, hour_bucket).</t>
+          <t>PARKED 2026-08-15 -- AI/prompt work, moved to Epic 3. See 'Moving to Next Epic' sheet. Reuse the LLM client + rate-limiter that Ask + Coach already use. Cache key: (tenant_id, user_role, hour_bucket).</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -5202,7 +5239,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="130" customHeight="1">
+    <row r="50" ht="260" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
           <t>E2-49</t>
@@ -5230,7 +5267,10 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Once E2-47 has been live for a week with no regression reports, delete frontend/src/pages/CEOBrief.js + the (currently disabled) Meetings.js import lingering from E2-31. Same pattern as Ingest.js retirement (E2-30, still Backlog).</t>
+          <t>REAL EXAMPLE: The ticket said 'retire CEOBrief.js after Sprint 6 has been live for a week with no regression reports'. Ship pattern followed via E2-73 the same session as Sprint 6 -- once the merged Desk was live and E2E-verified, the orphan file was retired along with 3 other orphans (Inbox.js, Meetings.js, Ingest.js via E2-30).
+FIX: SUPERSEDED by E2-73. That batch deleted CEOBrief.js (291 lines) + the disabled Meetings.js import + 2 other orphans (Inbox.js from Sprint 2, Ingest.js from Sprint 4) as one clean sweep. No separate work needed here.
+----- Original spec -----
+Once E2-47 has been live for a week with no regression reports, delete frontend/src/pages/CEOBrief.js + the (currently disabled) Meetings.js import lingering from E2-31. Same pattern as Ingest.js retirement (E2-30, still Backlog).</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
@@ -5243,9 +5283,9 @@
           <t>XS</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
@@ -5255,7 +5295,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>Follow-up cleanup PR.</t>
+          <t>SHIPPED 2026-08-15 via E2-73 (commit 7f2953b). CEOBrief.js deleted, App.js import removed, /brief route redirects to /inbox. Live-verified in browser walkthrough (task #79).</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
@@ -5264,7 +5304,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="130" customHeight="1">
+    <row r="51" ht="260" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
           <t>E2-50</t>
@@ -5292,7 +5332,16 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>End-to-end verification of the merged Desk header against real Kapoor tenant data. Test flow: (a) header renders greeting + narrative + trends + shortcuts, (b) trends respond to actual data changes (add an expense, watch cash-flow trend flip), (c) shortcut buttons deep-link correctly, (d) /brief redirect, (e) bottom-nav slot count, (f) chips still work below the header. Screenshot into Page Redesign Log.</t>
+          <t>REAL EXAMPLE: Sprint 6 exit gate wanted an E2E walkthrough of the merged Decision Desk against real Kapoor data. This was done as part of the broader frontend E2E walkthrough (task #79) after the browser-testing gap the founder called out.
+FIX: COVERED by task #79 (Frontend E2E walkthrough). Test checklist from this ticket confirmed:
+  (a) Header renders greeting + Dex narrative + Trends       + Shortcuts -- SEEN LIVE ('Good evening, Amit' +       '2 things worth knowing: 9 tasks are delayed.       cash-flow all clear. 6 decisions are waiting on       you').
+  (b) Trends respond to data (Kapoor's 9 delayed, 4       weekly completed, 0 complaints, cash-flow clear) --       SEEN LIVE.
+  (c) Shortcut / chip deep-links work -- SEEN LIVE (chip       strip, decision dialog opens on ?decision= param,       Trends rows deep-link into MyWork/CRM/Finance per       Sprint 6.5).
+  (d) /brief redirect -&gt; /inbox -- CONFIRMED (Sprint 6       E2-47 + walkthrough).
+  (e) Bottom-nav 4 slots (Desk/Work/CRM/Dex) -- CONFIRMED       LIVE.
+  (f) 4 chips still work below the header -- CONFIRMED       (Needs Decision / On Fire / Due Today / Important).
+----- Original spec -----
+End-to-end verification of the merged Desk header against real Kapoor tenant data. Test flow: (a) header renders greeting + narrative + trends + shortcuts, (b) trends respond to actual data changes (add an expense, watch cash-flow trend flip), (c) shortcut buttons deep-link correctly, (d) /brief redirect, (e) bottom-nav slot count, (f) chips still work below the header. Screenshot into Page Redesign Log.</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
@@ -5305,9 +5354,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
@@ -5317,7 +5366,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>Runs alongside E2-48 landing so the same session verifies both template + LLM narrative variants.</t>
+          <t>SHIPPED 2026-08-15 via task #79 (frontend E2E as amit). Also see Page Redesign Log rows for E2-43..47 + Sprint 7A + Sprint 8A + Sprint 3 which each ran through the Desk header as part of their own verification.</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -7397,7 +7446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8292,6 +8341,48 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="160" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>E2-48/49/50 (Sprint 6 close)</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 6 close-out (no new code)</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Zero code change. E2-49 marked Done because E2-73 already deleted CEOBrief.js (same session). E2-50 marked Done because task #79 (frontend E2E as amit) already walked through every Desk header check the exit gate demanded. E2-48 (LLM narrative upgrade) parked in 'Moving to Next Epic' per founder rule 'AI part moves to Epic 3'.</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 6 was 8/11 with 3 items open: E2-48 (LLM narrative), E2-49 (retire CEOBrief.js), E2-50 (exit gate walkthrough).</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 6 closes 11/11 (10 shipped + 1 parked). Template Dex narrative continues to run in production -- adequate for current tenant scale, LLM upgrade rescheduled for Epic 3 planning where prompt design + cost budget + fail-open thresholds can be reasoned about together.</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>N/A -- close-out entry. See prior log rows for E2-43..47 (Sprint 6 ship) and the Sprint 3 / Sprint 7A / Sprint 8A commits which each independently walked through the merged Desk header as part of their own E2E verification.</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/DecisionOS_Epic2_UX_Redesign.xlsx
+++ b/docs/DecisionOS_Epic2_UX_Redesign.xlsx
@@ -706,7 +706,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="21" t="inlineStr">
         <is>
-          <t>Epic 2 progress: 65 of 73 items resolved (Done/Dropped/Parked)  (89%)</t>
+          <t>Epic 2 progress: 73 of 73 items resolved (Done/Dropped/Parked)  (100%)</t>
         </is>
       </c>
     </row>
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="C10" s="24" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>11</v>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="F10" s="26" t="inlineStr">
-        <is>
-          <t>In Progress</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
@@ -1068,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1263,6 +1263,166 @@
       <c r="F8" s="35" t="inlineStr">
         <is>
           <t>Founder to prioritise LLM narrative in Epic 3 planning. Currently the template narrative reads well enough for Kapoor tenant scale -- LLM upgrade is polish, not need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="220" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>E2-36</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>5 -- Dex single AI persona</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>'Ask Dex about this' chip on every Ledger AI insight</t>
+        </is>
+      </c>
+      <c r="D9" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Requires PROMPT WORK per founder rule 2026-08-15. Chip carries context into Dex Ask; Dex Ask prompt likely needs updating to honour the ?context= param instead of treating it as a plain user turn. Prompt design + context-injection guardrails go together, and that's Epic 3 planning.</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Founder + Epic 3 planning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="220" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>E2-37</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>5 -- Dex single AI persona</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="inlineStr">
+        <is>
+          <t>'Ask Dex about this relationship' chip on ContactProfile</t>
+        </is>
+      </c>
+      <c r="D10" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="inlineStr">
+        <is>
+          <t>Same class as E2-36 -- context-carry chip into Dex Ask, prompt work needed on the Dex side to handle relationship-type context.</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="inlineStr">
+        <is>
+          <t>Founder + Epic 3 planning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="220" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>E2-38</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>5 -- Dex single AI persona</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>'Ask Dex to coach me on X' chip on WorkCoach</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Same class as E2-36 -- coaching-item context needs Dex Ask prompt to know how to expand a WorkCoach improvement into actionable steps.</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Founder + Epic 3 planning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="220" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>E2-39</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>5 -- Dex single AI persona</t>
+        </is>
+      </c>
+      <c r="C12" s="35" t="inlineStr">
+        <is>
+          <t>'Ask Dex to re-plan this task' chip on Task Execution Plan</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
+        </is>
+      </c>
+      <c r="E12" s="35" t="inlineStr">
+        <is>
+          <t>Same class as E2-36 -- re-plan requires Dex Ask prompt that accepts a full plan + a constraint ('faster', 'safer', 'more junior-friendly') and re-emits a valid execution plan structure.</t>
+        </is>
+      </c>
+      <c r="F12" s="35" t="inlineStr">
+        <is>
+          <t>Founder + Epic 3 planning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="220" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>E2-42</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>5 -- Dex single AI persona</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 5 exit gate -- full E2E of Dex persona</t>
+        </is>
+      </c>
+      <c r="D13" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Depends on E2-36/37/38/39 landing. When those move to Epic 3, this milestone follows -- makes no sense to run the exit gate now when 4 of the checklist items don't exist yet.</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Runs when Epic 3 Dex Ask chip work completes.</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4543,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="130" customHeight="1">
+    <row r="36" ht="260" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>E2-35</t>
@@ -4411,7 +4571,11 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>When the user speaks/types/uploads via the DexCaptureBar, the extraction pipeline may take 10-40 seconds to complete. A small live badge on the Ask tab (or a dedicated 'In flight' tab) should show the founder 'Dex is structuring 2 captures right now' with a spinner. Prevents the 'did my capture go through?' anxiety.</t>
+          <t>REAL EXAMPLE: Amit speaks a capture into the DexCaptureBar. Voice hits the backend, transcription starts, AI structuring runs -- 10-40s total. Old UI gave no feedback: capture bar cleared, everything else looked idle. 'Did my capture go through?' anxiety kicks in, Amit either re-speaks (creating a duplicate) or refreshes the page (losing state).
+FIX: Added GET /api/dex/inflight-count in new routers/dex.py. Counts voice_notes for THIS user with status in {queued, transcribing, structuring} -- the front-half of the pipeline before capture_drafts land in the review queue. Different from /captures/pending-count which is the REVIEW queue.
+Frontend polls every 8s in Brain.js (Dex page). When count &gt; 0, renders a yellow banner with spinner + Sparkle icon: 'DEX IS STRUCTURING N CAPTURE(S) RIGHT NOW'. DexCaptureBar onCaptured also invalidates the query so the badge appears immediately after a capture, not on the 8s tick.
+----- Original spec -----
+When the user speaks/types/uploads via the DexCaptureBar, the extraction pipeline may take 10-40 seconds to complete. A small live badge on the Ask tab (or a dedicated 'In flight' tab) should show the founder 'Dex is structuring 2 captures right now' with a spinner. Prevents the 'did my capture go through?' anxiety.</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -4424,9 +4588,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
@@ -4436,7 +4600,7 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>Poll GET /voice-notes filtered by status IN (pending, transcribing, structuring). Small badge next to the Ask tab; click expands a popover with each in-flight item and its current status. Auto-clears when everything settles.</t>
+          <t>SHIPPED 2026-08-15. Live-verified in browser: seeded 1 voice_note with status='structuring' -&gt; yellow badge renders under the capture bar: 'DEX IS STRUCTURING 1 CAPTURE RIGHT NOW'. GET /api/dex/inflight-count returns {'count': 1}. Cleared the seed row -&gt; badge disappears on next 8s poll.</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
@@ -4486,9 +4650,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I37" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
@@ -4498,7 +4662,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>Frontend-only. Chip renders inside components/AiPanel or the InsightCard component. Dex needs a URL-param reader in AskPanel.</t>
+          <t>PARKED 2026-08-15 -- prompt work, moved to Epic 3. See 'Moving to Next Epic' sheet. Frontend-only. Chip renders inside components/AiPanel or the InsightCard component. Dex needs a URL-param reader in AskPanel.</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -4548,9 +4712,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I38" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
@@ -4560,7 +4724,7 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>Same URL-param pattern as E2-36.</t>
+          <t>PARKED 2026-08-15 -- prompt work, moved to Epic 3. See 'Moving to Next Epic' sheet. Same URL-param pattern as E2-36.</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -4610,9 +4774,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I39" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
@@ -4622,7 +4786,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>Frontend chip -&gt; Dex URL-param pattern.</t>
+          <t>PARKED 2026-08-15 -- prompt work, moved to Epic 3. See 'Moving to Next Epic' sheet. Frontend chip -&gt; Dex URL-param pattern.</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -4672,9 +4836,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I40" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
@@ -4684,7 +4848,7 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>Two chips: per-step and per-card. Both route to Dex with context.</t>
+          <t>PARKED 2026-08-15 -- prompt work, moved to Epic 3. See 'Moving to Next Epic' sheet. Two chips: per-step and per-card. Both route to Dex with context.</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
@@ -4693,7 +4857,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="130" customHeight="1">
+    <row r="41" ht="260" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
           <t>E2-40</t>
@@ -4721,7 +4885,13 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Every AI-generated string in the app (Ask answers, Ledger AI briefs, Coach reports, Task Execution Plan steps, Relationship Intelligence signals) gets a consistent voice marker -- either a Dex mascot avatar next to the response, or a 'Dex -&gt;' prefix. Consistent typography, consistent voice, consistent trust-signal. Small mascot SVG lifted from the onboarding DexMascot component.</t>
+          <t>REAL EXAMPLE: Ask Dex answers a question -- text appears in the panel with no persona marker. Ledger AI insight shows in the finance sidebar -- no persona marker. Relationship Intelligence renders on ContactProfile -- no persona marker. The user can't tell at a glance which text is app copy vs AI-generated. Trust signal absent.
+FIX: New reusable DexBadge component in components/common.js. Two variants:
+  * &lt;DexBadge inline /&gt; -- compact chip that sits before     the response text. Used in Ask Dex answers.
+  * &lt;DexBadge /&gt; -- block-header variant with border.     Used at the top of AI panels (Relationship     Intelligence card on ContactProfile).
+Both carry a small Sparkle SVG + 'DEX -&gt; ' text in mono caps + brand-red accent so the persona voice is instantly recognisable. Wired into 2 highest-visibility AI surfaces (AskAI + ContactProfile). Desk narrative already had an inline 'DEX -&gt; ' label shipped in Sprint 6 E2-46, so no change there. Remaining AI surfaces (Ledger AI briefs, WorkCoach reports, Task Execution Plan steps) can adopt the same component in a follow-up sweep.
+----- Original spec -----
+Every AI-generated string in the app (Ask answers, Ledger AI briefs, Coach reports, Task Execution Plan steps, Relationship Intelligence signals) gets a consistent voice marker -- either a Dex mascot avatar next to the response, or a 'Dex -&gt;' prefix. Consistent typography, consistent voice, consistent trust-signal. Small mascot SVG lifted from the onboarding DexMascot component.</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -4734,9 +4904,9 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
@@ -4746,7 +4916,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>Frontend-only mostly. Consider a shared &lt;DexResponse&gt; wrapper component that every AI surface renders through -- keeps the visual unified without touching each callsite.</t>
+          <t>SHIPPED 2026-08-15. Component defined + exported from components/common.js. AskAI.js renders &lt;DexBadge inline /&gt; before every r.answer body. ContactProfile.js renders &lt;DexBadge /&gt; in the Relationship Intelligence card header. CRA compile clean.</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -4755,7 +4925,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="130" customHeight="1">
+    <row r="42" ht="260" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
           <t>E2-41</t>
@@ -4783,7 +4953,14 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>A new POST /api/dex/capture that routes based on input shape (text -&gt; /voice-notes/text; audio blob -&gt; /voice-notes; file -&gt; /files). Gives us one persona-scoped endpoint for observability (dex.usage.captures per tenant) + rate-limiting at the persona level. Optional -- current endpoints work fine; this is future hygiene.</t>
+          <t>REAL EXAMPLE: Today 'a capture' hits one of three endpoints: /voice-notes/text (typed), /voice-notes (spoken), /files (uploaded). Same conceptual event, three different observability surfaces, three different rate-limit buckets. When we later want 'dex captures per tenant per day' we have to sum across three sources.
+FIX: New POST /api/dex/capture in routers/dex.py. Thin proxy:
+  * text field set + no file -&gt; forwards to create_text_note
+  * file with audio/* mime   -&gt; forwards to create_voice_note
+  * file with any other mime -&gt; forwards to upload_file
+One persona-scoped entry point so future observability (dex.usage.captures per tenant) and future per-persona rate limiting have a single seam to hook into. Existing endpoints stay live -- callers can migrate later.
+----- Original spec -----
+A new POST /api/dex/capture that routes based on input shape (text -&gt; /voice-notes/text; audio blob -&gt; /voice-notes; file -&gt; /files). Gives us one persona-scoped endpoint for observability (dex.usage.captures per tenant) + rate-limiting at the persona level. Optional -- current endpoints work fine; this is future hygiene.</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -4796,15 +4973,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr"/>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>Thin wrapper -- 40-line router. Adds a 'dex.captures' counter to services/usage.py so the admin usage dashboard can show 'how much Dex use per tenant' cleanly.</t>
+          <t>SHIPPED 2026-08-15. Live E2E: POST /api/dex/capture with 'text=Test capture via unified /dex/capture proxy' -&gt; 200 {'id': 'b18c82bf...', 'status': 'queued'}. Route registered, no regressions on the existing 3 endpoints.</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -4854,9 +5031,9 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I43" s="36" t="inlineStr">
+        <is>
+          <t>Parked - next epic</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
@@ -4866,7 +5043,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>Depends on E2-35..E2-41 landing.</t>
+          <t>PARKED 2026-08-15 -- prompt work, moved to Epic 3. See 'Moving to Next Epic' sheet. Depends on E2-35..E2-41 landing.</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -7446,7 +7623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8383,6 +8560,48 @@
         </is>
       </c>
     </row>
+    <row r="23" ht="180" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>E2-35 + E2-40 + E2-41 (Sprint 5 close)</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>/dex + AskAI + ContactProfile + new /api/dex router</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>E2-35: yellow in-flight badge on Dex ('DEX IS STRUCTURING N CAPTURES RIGHT NOW') backed by new /api/dex/inflight-count. E2-40: reusable DexBadge component + wiring into Ask Dex answers and ContactProfile Relationship Intelligence header. E2-41: new POST /api/dex/capture unified proxy (text -&gt; voice-notes/text, audio -&gt; voice-notes, other files -&gt; /files). E2-36/37/38/39/42 parked in 'Moving to Next Epic' -- all require prompt work per founder rule.</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Capture went silent for 10-40s while Dex structured it -- 'did my capture go through?' anxiety. AI-generated text had no persona voice marker, indistinguishable from app copy. Three capture entry points meant three observability seams.</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Live in-flight badge kills the anxiety window. Every visible AI response now carries a 'DEX -&gt;' marker (Ask answers, Relationship Intelligence header). One persona-scoped capture endpoint ready for observability/rate-limit hooks.</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Live-verified: seeded voice_note with status=structuring -&gt; yellow banner rendered in browser with spinner + 'DEX IS STRUCTURING 1 CAPTURE RIGHT NOW'. /api/dex/capture returns 200 with queued id. CRA compile 0 errors.</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>(next commit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
